--- a/mentor data/laith 3-talaria-adapted.xlsx
+++ b/mentor data/laith 3-talaria-adapted.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ149"/>
+  <dimension ref="A1:EJ150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54336, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780214837689_dadcbb47252bc38add089de0849ef168.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215631805_a9a39dd79aba692729afc21d50b18a23.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54336, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780214837689_dadcbb47252bc38add089de0849ef168.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215631805_a9a39dd79aba692729afc21d50b18a23.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2263.145, "sourceLowPrice": 2251.889}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK2" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782554141670</v>
+        <v>1782575759964</v>
       </c>
       <c r="BM2" t="n">
         <v>2258.541</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54337, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187599379_b873e8fcf6c42f2aaa85a89a0b7f30d3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187756133_ff4438c3f6bf2bb967f72e5a4fbf2c00.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54337, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187599379_b873e8fcf6c42f2aaa85a89a0b7f30d3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187756133_ff4438c3f6bf2bb967f72e5a4fbf2c00.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07917, "sourceLowPrice": 1.07688}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK3" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782554141670</v>
+        <v>1782575759965</v>
       </c>
       <c r="BM3" t="n">
         <v>1.07938</v>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54338, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215784438_3983a074813184da3081dcc7bd9877d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215856014_76a86be691f407e4df6155fa80aa39e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54338, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215784438_3983a074813184da3081dcc7bd9877d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215856014_76a86be691f407e4df6155fa80aa39e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2258.45, "sourceLowPrice": 2250.21}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK4" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782554141670</v>
+        <v>1782575759965</v>
       </c>
       <c r="BM4" t="n">
         <v>2255.359</v>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54339, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188056673_448a100c575e03238ea4033bba7e9106.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188142564_aae8b084cb5dbcce5ffcb945b5fa7b74.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54339, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188056673_448a100c575e03238ea4033bba7e9106.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188142564_aae8b084cb5dbcce5ffcb945b5fa7b74.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07813, "sourceLowPrice": 1.07596}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK5" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782554141670</v>
+        <v>1782575759966</v>
       </c>
       <c r="BM5" t="n">
         <v>1.07846</v>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54340, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216391858_5e87f92f328437534c0dc625b9b534c3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216617040_ab38abf9510f6e548b9c32831d4ac1c6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54340, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216391858_5e87f92f328437534c0dc625b9b534c3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216617040_ab38abf9510f6e548b9c32831d4ac1c6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2276.937, "sourceLowPrice": 2233.82}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK6" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782554141671</v>
+        <v>1782575759967</v>
       </c>
       <c r="BM6" t="n">
         <v>2227.494</v>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54341, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188508620_e89ed1e80d22f649985df63ca84f5fed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188582602_14d62524d5aeb9b028492ac247879a1a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54341, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188508620_e89ed1e80d22f649985df63ca84f5fed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188582602_14d62524d5aeb9b028492ac247879a1a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07264}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK7" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782554141671</v>
+        <v>1782575759967</v>
       </c>
       <c r="BM7" t="n">
         <v>1.0744</v>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54342, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512298411_060252c1f3dc083d0e285f060c888682.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512311937_c559503a7c4f8c46aa9bc24f7176f8cf.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54342, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512298411_060252c1f3dc083d0e285f060c888682.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512311937_c559503a7c4f8c46aa9bc24f7176f8cf.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2275.411, "sourceLowPrice": 2256.03}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK8" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782554141671</v>
+        <v>1782575759968</v>
       </c>
       <c r="BM8" t="n">
         <v>2252.439</v>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54343, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222070329_b7dae3f6df7b2979bc221fc62537c2ef.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222214466_7a5d4e60a6ffd1f975ce2cde7f35024d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54343, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222070329_b7dae3f6df7b2979bc221fc62537c2ef.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222214466_7a5d4e60a6ffd1f975ce2cde7f35024d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2290.027, "sourceLowPrice": 2254.22}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK9" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782554141671</v>
+        <v>1782575759968</v>
       </c>
       <c r="BM9" t="n">
         <v>2249.866</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54344, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597397119_c30cb4d3d55075052763814cc9cfdcc2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597409048_a22cd62af0284a5fd91e652324dbd238.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54344, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597397119_c30cb4d3d55075052763814cc9cfdcc2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597409048_a22cd62af0284a5fd91e652324dbd238.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2274.55, "sourceLowPrice": 2265.51}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK10" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782554141672</v>
+        <v>1782575759968</v>
       </c>
       <c r="BM10" t="n">
         <v>2267.89</v>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="DQ10" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR10" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS10" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54345, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189148218_8386f58ae538d92f591d49f8b2a9669a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189234568_2e8ecdc821200259b3a301449f275013.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54345, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189148218_8386f58ae538d92f591d49f8b2a9669a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189234568_2e8ecdc821200259b3a301449f275013.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08015, "sourceLowPrice": 1.0773}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6069,13 +6069,13 @@
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK11" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782554141672</v>
+        <v>1782575759969</v>
       </c>
       <c r="BM11" t="n">
         <v>1.0788</v>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54346, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223471552_ea5b3c4daa45de163941d2e923418632.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223916207_89c71be4de0025b4b0663640a081f90a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54346, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223471552_ea5b3c4daa45de163941d2e923418632.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223916207_89c71be4de0025b4b0663640a081f90a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2304.99, "sourceLowPrice": 2280.79}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6593,13 +6593,13 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK12" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782554141672</v>
+        <v>1782575759970</v>
       </c>
       <c r="BM12" t="n">
         <v>2273.238</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS12" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54347, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232061584_b58d9305d377b61c85645d1bbeef2d88.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232164427_538eb12558140b5c26863d9d8a9f3e07.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54347, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232061584_b58d9305d377b61c85645d1bbeef2d88.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232164427_538eb12558140b5c26863d9d8a9f3e07.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2297.45, "sourceLowPrice": 2293.035}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="BJ13" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK13" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782554141672</v>
+        <v>1782575759970</v>
       </c>
       <c r="BM13" t="n">
         <v>2294.065</v>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS13" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54348, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189555937_3254a1775090dcd0bd1a1724f0ee83b6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189616066_72d73c9c963777d903869b76ec2d6df7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54348, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189555937_3254a1775090dcd0bd1a1724f0ee83b6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189616066_72d73c9c963777d903869b76ec2d6df7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08656, "sourceLowPrice": 1.08509}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK14" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782554141673</v>
+        <v>1782575759970</v>
       </c>
       <c r="BM14" t="n">
         <v>1.08604</v>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS14" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54349, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233182736_aef339eb5a70fc2de99b7c935fbb8960.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233324509_4f2def2ba4749f41f441e7f623fe0dfc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54349, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233182736_aef339eb5a70fc2de99b7c935fbb8960.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233324509_4f2def2ba4749f41f441e7f623fe0dfc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2284.776}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK15" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782554141673</v>
+        <v>1782575759971</v>
       </c>
       <c r="BM15" t="n">
         <v>2281.682</v>
@@ -8373,12 +8373,12 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS15" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54350, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780580933913_38d2b56a5e34032f16fd75b5796b4f4b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581006293_dc78a12d872cd90b623ef9d1ab023e84.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54350, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780580933913_38d2b56a5e34032f16fd75b5796b4f4b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581006293_dc78a12d872cd90b623ef9d1ab023e84.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2290.88}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK16" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782554141673</v>
+        <v>1782575759972</v>
       </c>
       <c r="BM16" t="n">
         <v>2288.195</v>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS16" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54351, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304127248_b1419143e3c987dfd7aec4bd6523ac69.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304248886_ae0b55e7c9057366870c357893cf1427.png", "notes": "small smt (entry)", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54351, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304127248_b1419143e3c987dfd7aec4bd6523ac69.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304248886_ae0b55e7c9057366870c357893cf1427.png", "notes": "small smt (entry)", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2295.045, "sourceLowPrice": 2293.035}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="BJ17" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK17" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782554141673</v>
+        <v>1782575759972</v>
       </c>
       <c r="BM17" t="n">
         <v>2291.604</v>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS17" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54352, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952356811_703f322d8fa6f5e4cb90e5418c3cf190.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952418281_8f40d5331d136e2abda911b922109ee3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54352, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952356811_703f322d8fa6f5e4cb90e5418c3cf190.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952418281_8f40d5331d136e2abda911b922109ee3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18349.908, "sourceLowPrice": 18286.354}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9737,13 +9737,13 @@
         </is>
       </c>
       <c r="BJ18" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK18" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782554141674</v>
+        <v>1782575759973</v>
       </c>
       <c r="BM18" t="n">
         <v>18275.021</v>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR18" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS18" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54353, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200857906_aea70e79daf33522ba08c8e954aaafbd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200935735_c41282483de9220a41581f2c0908bd96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54353, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200857906_aea70e79daf33522ba08c8e954aaafbd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200935735_c41282483de9220a41581f2c0908bd96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08464, "sourceLowPrice": 1.08362}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10261,13 +10261,13 @@
         </is>
       </c>
       <c r="BJ19" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK19" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782554141674</v>
+        <v>1782575759974</v>
       </c>
       <c r="BM19" t="n">
         <v>1.08436</v>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR19" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS19" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54354, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780309638914_ac2e31c72d3f5cb986eb15da78225c7e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578150837_befeaacd72c27452901de4b30361f190.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54354, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780309638914_ac2e31c72d3f5cb986eb15da78225c7e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578150837_befeaacd72c27452901de4b30361f190.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2296.27, "sourceLowPrice": 2280.43}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="BJ20" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK20" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782554141674</v>
+        <v>1782575759974</v>
       </c>
       <c r="BM20" t="n">
         <v>2283.915</v>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR20" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS20" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54356, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952850659_76b40ca6ae337217380de3b1dbb6cb42.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953341925_174222affd81bd74f3237a5c9925a546.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54356, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952850659_76b40ca6ae337217380de3b1dbb6cb42.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953341925_174222affd81bd74f3237a5c9925a546.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5224.327, "sourceLowPrice": 5156.077}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="BJ21" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK21" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782554141674</v>
+        <v>1782575759975</v>
       </c>
       <c r="BM21" t="n">
         <v>5150.273</v>
@@ -11517,12 +11517,12 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR21" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS21" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54357, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578359260_42ad39ab25230e308cd195d91e82e07f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780310988059_57088f2016a876bb381800417d3db597.png", "notes": "T", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54357, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578359260_42ad39ab25230e308cd195d91e82e07f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780310988059_57088f2016a876bb381800417d3db597.png", "notes": "T", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.162, "sourceLowPrice": 2284.575}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="BJ22" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK22" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782554141674</v>
+        <v>1782575759975</v>
       </c>
       <c r="BM22" t="n">
         <v>2279.434</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="DQ22" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR22" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS22" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54358, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581279902_21fba9078090cf8d3c7923e985d6f4f8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581413420_9aa89f6c989a5df372958d96e9d7e11f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54358, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581279902_21fba9078090cf8d3c7923e985d6f4f8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581413420_9aa89f6c989a5df372958d96e9d7e11f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.743, "sourceLowPrice": 2292.04}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12357,13 +12357,13 @@
         </is>
       </c>
       <c r="BJ23" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK23" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782554141674</v>
+        <v>1782575759976</v>
       </c>
       <c r="BM23" t="n">
         <v>2286.615</v>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="DQ23" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR23" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS23" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54359, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953441461_82d2852988ea1ea79669518c3c24a138.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953521457_02d25584d8efa212b6a43629a1f6f438.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54359, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953441461_82d2852988ea1ea79669518c3c24a138.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953521457_02d25584d8efa212b6a43629a1f6f438.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5209.528, "sourceLowPrice": 5168.689}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12881,13 +12881,13 @@
         </is>
       </c>
       <c r="BJ24" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK24" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782554141675</v>
+        <v>1782575759976</v>
       </c>
       <c r="BM24" t="n">
         <v>5166.201</v>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="DQ24" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR24" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS24" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54360, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953640796_a975d89fb3da0cd76554693d7fbbfccb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953691339_d1bf2089c2c5b544f33520cedb5b2d24.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54360, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953640796_a975d89fb3da0cd76554693d7fbbfccb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953691339_d1bf2089c2c5b544f33520cedb5b2d24.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5210.34, "sourceLowPrice": 5181.824}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13405,13 +13405,13 @@
         </is>
       </c>
       <c r="BJ25" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK25" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782554141675</v>
+        <v>1782575759976</v>
       </c>
       <c r="BM25" t="n">
         <v>5175.666</v>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="DQ25" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR25" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54361, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201634282_e9c4a9ee9c43b78b438fcf7fc95dcdc7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201824752_d787e06430318250bd53ad5e1c3c0dde.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54361, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201634282_e9c4a9ee9c43b78b438fcf7fc95dcdc7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201824752_d787e06430318250bd53ad5e1c3c0dde.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08379, "sourceLowPrice": 1.08209}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13929,13 +13929,13 @@
         </is>
       </c>
       <c r="BJ26" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK26" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782554141675</v>
+        <v>1782575759977</v>
       </c>
       <c r="BM26" t="n">
         <v>1.08397</v>
@@ -14137,12 +14137,12 @@
       </c>
       <c r="DQ26" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR26" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS26" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54362, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578571747_36d3cb7663754c1635a8856256c5cb95.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578680127_cb12c4e66b73628d4ae8acbe9b9a2e88.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54362, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578571747_36d3cb7663754c1635a8856256c5cb95.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578680127_cb12c4e66b73628d4ae8acbe9b9a2e88.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2334.27}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14453,13 +14453,13 @@
         </is>
       </c>
       <c r="BJ27" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK27" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782554141675</v>
+        <v>1782575759978</v>
       </c>
       <c r="BM27" t="n">
         <v>2332.393</v>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="DQ27" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR27" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS27" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54364, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581790944_dcd909716c23339e3d6dea636ace482b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581920247_201982bca0d602d69c07bc0a0c2c35fc.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54364, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581790944_dcd909716c23339e3d6dea636ace482b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581920247_201982bca0d602d69c07bc0a0c2c35fc.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2336.32}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14977,13 +14977,13 @@
         </is>
       </c>
       <c r="BJ28" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK28" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782554141676</v>
+        <v>1782575759978</v>
       </c>
       <c r="BM28" t="n">
         <v>2334.715</v>
@@ -15185,12 +15185,12 @@
       </c>
       <c r="DQ28" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR28" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS28" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54365, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582022486_55870726c5b5304fb0bef711e1598c74.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582078461_6a1bdafdfef1ac03cd8ecb1f65b9306c.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54365, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582022486_55870726c5b5304fb0bef711e1598c74.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582078461_6a1bdafdfef1ac03cd8ecb1f65b9306c.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2338.59}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="BJ29" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK29" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782554141676</v>
+        <v>1782575759979</v>
       </c>
       <c r="BM29" t="n">
         <v>2335.82</v>
@@ -15709,12 +15709,12 @@
       </c>
       <c r="DQ29" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR29" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54368, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589525290_f066e0de38aade84091fe91b724d0ce0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589574499_3061ea78ecb86c34650bb6fea54556b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54368, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589525290_f066e0de38aade84091fe91b724d0ce0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589574499_3061ea78ecb86c34650bb6fea54556b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.68, "sourceLowPrice": 2347.36}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16025,13 +16025,13 @@
         </is>
       </c>
       <c r="BJ30" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK30" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782554141676</v>
+        <v>1782575759979</v>
       </c>
       <c r="BM30" t="n">
         <v>2344.8</v>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="DQ30" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR30" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS30" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54369, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319288614_eae04019ac0871ad32c227dbfda6ccb0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319419799_c321f26bf3e5869b78fffccf1680e494.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54369, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319288614_eae04019ac0871ad32c227dbfda6ccb0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319419799_c321f26bf3e5869b78fffccf1680e494.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2350.81, "sourceLowPrice": 2333.81}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16549,13 +16549,13 @@
         </is>
       </c>
       <c r="BJ31" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK31" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782554141676</v>
+        <v>1782575759980</v>
       </c>
       <c r="BM31" t="n">
         <v>2343.983</v>
@@ -16757,12 +16757,12 @@
       </c>
       <c r="DQ31" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR31" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS31" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54370, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267051732_fb71fcb1a5d548bddb4717127ec86683.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267134800_6f8a0d38c808933c1ded8f21d03fddca.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54370, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267051732_fb71fcb1a5d548bddb4717127ec86683.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267134800_6f8a0d38c808933c1ded8f21d03fddca.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0865, "sourceLowPrice": 1.08376}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17073,13 +17073,13 @@
         </is>
       </c>
       <c r="BJ32" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK32" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782554141676</v>
+        <v>1782575759981</v>
       </c>
       <c r="BM32" t="n">
         <v>1.08676</v>
@@ -17281,12 +17281,12 @@
       </c>
       <c r="DQ32" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR32" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS32" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54371, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319745725_3730419349b0045a2192a5272858e91f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54371, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319745725_3730419349b0045a2192a5272858e91f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2325.75}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17597,13 +17597,13 @@
         </is>
       </c>
       <c r="BJ33" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK33" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782554141677</v>
+        <v>1782575759981</v>
       </c>
       <c r="BM33" t="n">
         <v>2318.414</v>
@@ -17805,12 +17805,12 @@
       </c>
       <c r="DQ33" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR33" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS33" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54372, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954611652_bcd3e4125ec981c2ded35719d37afe59.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954713560_2e27dd67171dc45971edbfd0e165706b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54372, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954611652_bcd3e4125ec981c2ded35719d37afe59.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954713560_2e27dd67171dc45971edbfd0e165706b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18048.519, "sourceLowPrice": 17966.886}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="BJ34" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK34" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782554141677</v>
+        <v>1782575759982</v>
       </c>
       <c r="BM34" t="n">
         <v>18023.946</v>
@@ -18329,12 +18329,12 @@
       </c>
       <c r="DQ34" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR34" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS34" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54373, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590264461_8ecec747d0c6cad9187e309bbea368b0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54373, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590264461_8ecec747d0c6cad9187e309bbea368b0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2333.709}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18645,13 +18645,13 @@
         </is>
       </c>
       <c r="BJ35" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK35" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782554141677</v>
+        <v>1782575759982</v>
       </c>
       <c r="BM35" t="n">
         <v>2339.965</v>
@@ -18853,12 +18853,12 @@
       </c>
       <c r="DQ35" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR35" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS35" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54374, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320728308_5c7ff7b32f02827cdcb24cda6e49d519.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320821403_bb1586d62d9d3e1f545d3c01bf1f81b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54374, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320728308_5c7ff7b32f02827cdcb24cda6e49d519.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320821403_bb1586d62d9d3e1f545d3c01bf1f81b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.83, "sourceLowPrice": 2325.91}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19169,13 +19169,13 @@
         </is>
       </c>
       <c r="BJ36" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK36" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782554141677</v>
+        <v>1782575759983</v>
       </c>
       <c r="BM36" t="n">
         <v>2329.145</v>
@@ -19377,12 +19377,12 @@
       </c>
       <c r="DQ36" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR36" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS36" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54375, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267426711_d68e22288378664d1fe52fc460250401.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267498180_a84b21be21b42d95df0bd9c646b8241e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54375, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267426711_d68e22288378664d1fe52fc460250401.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267498180_a84b21be21b42d95df0bd9c646b8241e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07444, "sourceLowPrice": 1.0715}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19693,13 +19693,13 @@
         </is>
       </c>
       <c r="BJ37" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK37" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782554141677</v>
+        <v>1782575759984</v>
       </c>
       <c r="BM37" t="n">
         <v>1.07509</v>
@@ -19901,12 +19901,12 @@
       </c>
       <c r="DQ37" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR37" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS37" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54376, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780321321815_fa7926ee732c0828557974939b4356af.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590991194_5305bb220f87935173ed6daf99d2ce80.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54376, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780321321815_fa7926ee732c0828557974939b4356af.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590991194_5305bb220f87935173ed6daf99d2ce80.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.71, "sourceLowPrice": 2328.43}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20217,13 +20217,13 @@
         </is>
       </c>
       <c r="BJ38" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK38" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782554141678</v>
+        <v>1782575759984</v>
       </c>
       <c r="BM38" t="n">
         <v>2324.744</v>
@@ -20425,12 +20425,12 @@
       </c>
       <c r="DQ38" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR38" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS38" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54377, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590762975_3102d6bce697c8b83c967d5065bbdad2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590864856_21b99a8638fe3b118c2a5c1abc851f87.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54377, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590762975_3102d6bce697c8b83c967d5065bbdad2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590864856_21b99a8638fe3b118c2a5c1abc851f87.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.53, "sourceLowPrice": 2332.61}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20741,13 +20741,13 @@
         </is>
       </c>
       <c r="BJ39" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK39" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782554141678</v>
+        <v>1782575759985</v>
       </c>
       <c r="BM39" t="n">
         <v>2331.31</v>
@@ -20949,12 +20949,12 @@
       </c>
       <c r="DQ39" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR39" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS39" t="inlineStr">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54380, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338124221_d61fa2e41baa09a0e338b6edc9b7d22f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338307430_ac14cb004870aaa3e064a2acf187a458.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54380, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338124221_d61fa2e41baa09a0e338b6edc9b7d22f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338307430_ac14cb004870aaa3e064a2acf187a458.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2404.463, "sourceLowPrice": 2386.9}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21265,13 +21265,13 @@
         </is>
       </c>
       <c r="BJ40" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK40" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782554141678</v>
+        <v>1782575759985</v>
       </c>
       <c r="BM40" t="n">
         <v>2383.79</v>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="DQ40" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR40" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS40" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54381, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591417759_7f395f3a859f6c1a679cd1aefc7dcf27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591501149_7fcdec701bdabac643789abb57e3eb9b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54381, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591417759_7f395f3a859f6c1a679cd1aefc7dcf27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591501149_7fcdec701bdabac643789abb57e3eb9b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2399.931, "sourceLowPrice": 2391.55}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21789,13 +21789,13 @@
         </is>
       </c>
       <c r="BJ41" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK41" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782554141678</v>
+        <v>1782575759986</v>
       </c>
       <c r="BM41" t="n">
         <v>2390.235</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="DQ41" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR41" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS41" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54382, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338474113_9d83c277e7d56f7407aad0a07a7adabb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338712544_98d780d16910a003d755c4e7a35b10f0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54382, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338474113_9d83c277e7d56f7407aad0a07a7adabb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338712544_98d780d16910a003d755c4e7a35b10f0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2400.73, "sourceLowPrice": 2390.44}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22313,13 +22313,13 @@
         </is>
       </c>
       <c r="BJ42" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK42" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782554141678</v>
+        <v>1782575759986</v>
       </c>
       <c r="BM42" t="n">
         <v>2391.883</v>
@@ -22521,12 +22521,12 @@
       </c>
       <c r="DQ42" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR42" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS42" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54383, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339104546_e889a3b2180090b2a9352366ae701c70.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339368388_2aa1f18a2700eda2691e07387763895a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54383, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339104546_e889a3b2180090b2a9352366ae701c70.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339368388_2aa1f18a2700eda2691e07387763895a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.071, "sourceLowPrice": 2391.59}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22837,13 +22837,13 @@
         </is>
       </c>
       <c r="BJ43" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK43" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782554141678</v>
+        <v>1782575759987</v>
       </c>
       <c r="BM43" t="n">
         <v>2389.438</v>
@@ -23045,12 +23045,12 @@
       </c>
       <c r="DQ43" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR43" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS43" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54384, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267931057_538062c282463f33370f88570c7f5f84.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267985598_6ecf0abcb85090fb96bf94e144eb7855.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54384, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267931057_538062c282463f33370f88570c7f5f84.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267985598_6ecf0abcb85090fb96bf94e144eb7855.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06556, "sourceLowPrice": 1.06228}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23361,13 +23361,13 @@
         </is>
       </c>
       <c r="BJ44" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK44" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782554141679</v>
+        <v>1782575759987</v>
       </c>
       <c r="BM44" t="n">
         <v>1.06604</v>
@@ -23569,12 +23569,12 @@
       </c>
       <c r="DQ44" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR44" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS44" t="inlineStr">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54389, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268357399_61876d40ecb889f51c6b37261b9e65c9.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268554956_e74684e0075c44f26dc4625496b368ef.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54389, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268357399_61876d40ecb889f51c6b37261b9e65c9.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268554956_e74684e0075c44f26dc4625496b368ef.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06653, "sourceLowPrice": 1.0631}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23885,13 +23885,13 @@
         </is>
       </c>
       <c r="BJ45" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK45" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782554141679</v>
+        <v>1782575759988</v>
       </c>
       <c r="BM45" t="n">
         <v>1.0666</v>
@@ -24093,12 +24093,12 @@
       </c>
       <c r="DQ45" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR45" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS45" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54390, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010234777_9225504a87a97d760fa3466ce407a207.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010307215_1c13c41407edec90ebf1f1b636f6e7f5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54390, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010234777_9225504a87a97d760fa3466ce407a207.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010307215_1c13c41407edec90ebf1f1b636f6e7f5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5170.132, "sourceLowPrice": 5162.614}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24409,13 +24409,13 @@
         </is>
       </c>
       <c r="BJ46" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK46" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782554141679</v>
+        <v>1782575759988</v>
       </c>
       <c r="BM46" t="n">
         <v>5169.481</v>
@@ -24617,12 +24617,12 @@
       </c>
       <c r="DQ46" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR46" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS46" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54391, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010504893_faf3b60862176067de33a46fa3e251b3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010620073_dcc5b7a295e0efc967e909758efb4304.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54391, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010504893_faf3b60862176067de33a46fa3e251b3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010620073_dcc5b7a295e0efc967e909758efb4304.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18177.354, "sourceLowPrice": 18066.682}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24933,13 +24933,13 @@
         </is>
       </c>
       <c r="BJ47" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK47" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782554141679</v>
+        <v>1782575759989</v>
       </c>
       <c r="BM47" t="n">
         <v>18188.686</v>
@@ -25141,12 +25141,12 @@
       </c>
       <c r="DQ47" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR47" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS47" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54392, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010841873_eda18716561afc5dfddc0d7caccf2f14.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010990277_2f2bd4f7a881c2433f498feeae5be5b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54392, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010841873_eda18716561afc5dfddc0d7caccf2f14.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010990277_2f2bd4f7a881c2433f498feeae5be5b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18040.386, "sourceLowPrice": 17987.12}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25457,13 +25457,13 @@
         </is>
       </c>
       <c r="BJ48" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK48" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782554141679</v>
+        <v>1782575759989</v>
       </c>
       <c r="BM48" t="n">
         <v>18077.865</v>
@@ -25665,12 +25665,12 @@
       </c>
       <c r="DQ48" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR48" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS48" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54393, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011137421_8cf0d420b280475328a584276a1bc137.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011150440_c29a79485c653b6e3c029d88ef8d65c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54393, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011137421_8cf0d420b280475328a584276a1bc137.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011150440_c29a79485c653b6e3c029d88ef8d65c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18053.964, "sourceLowPrice": 17987.12}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25981,13 +25981,13 @@
         </is>
       </c>
       <c r="BJ49" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK49" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782554141680</v>
+        <v>1782575759990</v>
       </c>
       <c r="BM49" t="n">
         <v>18026.132</v>
@@ -26189,12 +26189,12 @@
       </c>
       <c r="DQ49" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR49" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS49" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54394, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268891505_6aebb65ffaac9757d774d1cc767686ee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268946963_f35cfb5e413ebc5e7e2d0ca3f28a3d5d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54394, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268891505_6aebb65ffaac9757d774d1cc767686ee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268946963_f35cfb5e413ebc5e7e2d0ca3f28a3d5d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06229, "sourceLowPrice": 1.06024}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26505,13 +26505,13 @@
         </is>
       </c>
       <c r="BJ50" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK50" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782554141680</v>
+        <v>1782575759990</v>
       </c>
       <c r="BM50" t="n">
         <v>1.06216</v>
@@ -26713,12 +26713,12 @@
       </c>
       <c r="DQ50" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR50" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS50" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54395, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381490958_209d973e2fdd4bbd0d1599bf1aa32c80.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381587541_b0b4aac638fe0e056d080296d6807248.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54395, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381490958_209d973e2fdd4bbd0d1599bf1aa32c80.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381587541_b0b4aac638fe0e056d080296d6807248.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2375.31, "sourceLowPrice": 2363.06}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27029,13 +27029,13 @@
         </is>
       </c>
       <c r="BJ51" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK51" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782554141680</v>
+        <v>1782575759991</v>
       </c>
       <c r="BM51" t="n">
         <v>2367.715</v>
@@ -27237,12 +27237,12 @@
       </c>
       <c r="DQ51" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR51" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS51" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54396, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024250905_75f5048276946756f26081b7fce75954.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024319121_483fcc9eb15b7df7c44c8e3f97b359d8.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54396, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024250905_75f5048276946756f26081b7fce75954.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024319121_483fcc9eb15b7df7c44c8e3f97b359d8.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17746.643, "sourceLowPrice": 17702.498}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="BJ52" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK52" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782554141680</v>
+        <v>1782575759991</v>
       </c>
       <c r="BM52" t="n">
         <v>17726.642</v>
@@ -27761,12 +27761,12 @@
       </c>
       <c r="DQ52" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR52" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS52" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54402, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595139798_ff7f5995d5acee2bfff69fbe25341b63.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595310612_6f903b16326071d0e43f454f87e549d4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54402, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595139798_ff7f5995d5acee2bfff69fbe25341b63.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595310612_6f903b16326071d0e43f454f87e549d4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2394.38, "sourceLowPrice": 2378.0}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28077,13 +28077,13 @@
         </is>
       </c>
       <c r="BJ53" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK53" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782554141680</v>
+        <v>1782575759991</v>
       </c>
       <c r="BM53" t="n">
         <v>2371.755</v>
@@ -28285,12 +28285,12 @@
       </c>
       <c r="DQ53" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR53" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS53" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54403, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780389742774_ec6b57838fcd0d65b4a1f6b01f08d62e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390228080_2a70338c8625db934448dfcbfa1c7b09.png", "notes": "u have to look at xag maybe there is a add(test)\n\nmorelossading", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54403, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780389742774_ec6b57838fcd0d65b4a1f6b01f08d62e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390228080_2a70338c8625db934448dfcbfa1c7b09.png", "notes": "u have to look at xag maybe there is a add(test)\n\nmorelossading", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2390.41, "sourceLowPrice": 2384.59}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28601,13 +28601,13 @@
         </is>
       </c>
       <c r="BJ54" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK54" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782554141680</v>
+        <v>1782575759992</v>
       </c>
       <c r="BM54" t="n">
         <v>2384.082</v>
@@ -28809,12 +28809,12 @@
       </c>
       <c r="DQ54" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR54" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS54" t="inlineStr">
@@ -29077,7 +29077,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54404, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269593392_30df0756429eda87952ec8ac301a2c1b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269657332_f84740c78b4af74cd126d365773455b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54404, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269593392_30df0756429eda87952ec8ac301a2c1b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269657332_f84740c78b4af74cd126d365773455b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06529, "sourceLowPrice": 1.06316}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29126,13 +29126,13 @@
         </is>
       </c>
       <c r="BJ55" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK55" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782554141681</v>
+        <v>1782575759994</v>
       </c>
       <c r="BM55" t="n">
         <v>1.06502</v>
@@ -29334,12 +29334,12 @@
       </c>
       <c r="DQ55" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR55" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS55" t="inlineStr">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54405, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390413043_8d5f6c2991cb08d9a633a0c7043a7362.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390479011_a43c0a023eeb6b07bdfea338ffc57068.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54405, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390413043_8d5f6c2991cb08d9a633a0c7043a7362.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390479011_a43c0a023eeb6b07bdfea338ffc57068.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2386.21, "sourceLowPrice": 2383.15}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29650,13 +29650,13 @@
         </is>
       </c>
       <c r="BJ56" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK56" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782554141681</v>
+        <v>1782575759994</v>
       </c>
       <c r="BM56" t="n">
         <v>2383.41</v>
@@ -29858,12 +29858,12 @@
       </c>
       <c r="DQ56" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR56" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS56" t="inlineStr">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54406, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390697068_a6aba69394a8022b793614132c3dd1bb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596004419_5e766d5cb3ef169b7789ede0e739cb1f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54406, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390697068_a6aba69394a8022b793614132c3dd1bb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596004419_5e766d5cb3ef169b7789ede0e739cb1f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2382.99}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30174,13 +30174,13 @@
         </is>
       </c>
       <c r="BJ57" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK57" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782554141681</v>
+        <v>1782575759995</v>
       </c>
       <c r="BM57" t="n">
         <v>2377.353</v>
@@ -30382,12 +30382,12 @@
       </c>
       <c r="DQ57" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR57" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS57" t="inlineStr">
@@ -30649,7 +30649,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54407, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595652278_719d5357aceed6d9a634d5951164c776.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595929387_d9a3494f27f529ea6c9ddb89c413b834.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54407, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595652278_719d5357aceed6d9a634d5951164c776.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595929387_d9a3494f27f529ea6c9ddb89c413b834.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2385.45}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30698,13 +30698,13 @@
         </is>
       </c>
       <c r="BJ58" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK58" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782554141682</v>
+        <v>1782575759996</v>
       </c>
       <c r="BM58" t="n">
         <v>2384.91</v>
@@ -30906,12 +30906,12 @@
       </c>
       <c r="DQ58" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR58" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS58" t="inlineStr">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54408, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596175887_f528b35e645890efc4685722435e5e82.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596269061_9990ab4e8c6b3a0ae9a1577a07bcd87a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54408, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596175887_f528b35e645890efc4685722435e5e82.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596269061_9990ab4e8c6b3a0ae9a1577a07bcd87a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2386.19}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31222,13 +31222,13 @@
         </is>
       </c>
       <c r="BJ59" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK59" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782554141682</v>
+        <v>1782575759996</v>
       </c>
       <c r="BM59" t="n">
         <v>2386.02</v>
@@ -31430,12 +31430,12 @@
       </c>
       <c r="DQ59" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR59" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS59" t="inlineStr">
@@ -31697,7 +31697,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54410, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780392162560_35a16921edfb8c26cf6241d2e0b208aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596721094_721488dbd9c11944d78625cf41a4489e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54410, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780392162560_35a16921edfb8c26cf6241d2e0b208aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596721094_721488dbd9c11944d78625cf41a4489e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.095}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31746,13 +31746,13 @@
         </is>
       </c>
       <c r="BJ60" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK60" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782554141682</v>
+        <v>1782575759996</v>
       </c>
       <c r="BM60" t="n">
         <v>2374.009</v>
@@ -31954,12 +31954,12 @@
       </c>
       <c r="DQ60" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR60" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS60" t="inlineStr">
@@ -32221,7 +32221,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54411, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596564193_331854573e6172b2cd18b757187b2550.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596650921_3cd5b8fbf645dad05d68659f71e15b9f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54411, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596564193_331854573e6172b2cd18b757187b2550.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596650921_3cd5b8fbf645dad05d68659f71e15b9f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.29}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32270,13 +32270,13 @@
         </is>
       </c>
       <c r="BJ61" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK61" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782554141682</v>
+        <v>1782575759997</v>
       </c>
       <c r="BM61" t="n">
         <v>2377.7</v>
@@ -32478,12 +32478,12 @@
       </c>
       <c r="DQ61" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR61" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS61" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54412, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269864242_9a11874377d2f800f00c8fb6cf0c68e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269927741_5cac49b0e7f70b8482c8b77d4e70fb53.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54412, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269864242_9a11874377d2f800f00c8fb6cf0c68e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269927741_5cac49b0e7f70b8482c8b77d4e70fb53.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06797, "sourceLowPrice": 1.06496}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32794,13 +32794,13 @@
         </is>
       </c>
       <c r="BJ62" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK62" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782554141682</v>
+        <v>1782575759997</v>
       </c>
       <c r="BM62" t="n">
         <v>1.06801</v>
@@ -33002,12 +33002,12 @@
       </c>
       <c r="DQ62" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR62" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS62" t="inlineStr">
@@ -33269,7 +33269,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54413, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026834280_a20e85d8c00c40de0fb411e57a5a27ea.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026942673_18b9d1c5fc559062f1d5d248450a22b6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54413, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026834280_a20e85d8c00c40de0fb411e57a5a27ea.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026942673_18b9d1c5fc559062f1d5d248450a22b6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17559.787, "sourceLowPrice": 17501.462}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33318,13 +33318,13 @@
         </is>
       </c>
       <c r="BJ63" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK63" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782554141682</v>
+        <v>1782575759998</v>
       </c>
       <c r="BM63" t="n">
         <v>17569.399</v>
@@ -33526,12 +33526,12 @@
       </c>
       <c r="DQ63" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR63" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS63" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54414, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393461953_5280432bc7ab04977c1644c3f8bbd1f0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393771935_41e7d6369a93b829dd3e4308ec8b03d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54414, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393461953_5280432bc7ab04977c1644c3f8bbd1f0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393771935_41e7d6369a93b829dd3e4308ec8b03d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2392.86, "sourceLowPrice": 2380.77}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33842,13 +33842,13 @@
         </is>
       </c>
       <c r="BJ64" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK64" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782554141683</v>
+        <v>1782575759998</v>
       </c>
       <c r="BM64" t="n">
         <v>2378.057</v>
@@ -34050,12 +34050,12 @@
       </c>
       <c r="DQ64" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR64" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS64" t="inlineStr">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54415, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027167660_fc2d6f206b84ec8115f8b2060648fd39.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027387610_9fb91223f21055c2e3b1f84f1d6f62a5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54415, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027167660_fc2d6f206b84ec8115f8b2060648fd39.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027387610_9fb91223f21055c2e3b1f84f1d6f62a5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17535.709, "sourceLowPrice": 17449.895}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34366,13 +34366,13 @@
         </is>
       </c>
       <c r="BJ65" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK65" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782554141683</v>
+        <v>1782575759998</v>
       </c>
       <c r="BM65" t="n">
         <v>17547.399</v>
@@ -34574,12 +34574,12 @@
       </c>
       <c r="DQ65" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR65" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS65" t="inlineStr">
@@ -34841,7 +34841,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54416, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475215419_a413cc291367f1c13e80144a54293631.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597229374_a263da44cab5cda5a67defecfd2aa40b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54416, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475215419_a413cc291367f1c13e80144a54293631.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597229374_a263da44cab5cda5a67defecfd2aa40b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2393.92, "sourceLowPrice": 2372.91}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34890,13 +34890,13 @@
         </is>
       </c>
       <c r="BJ66" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK66" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782554141683</v>
+        <v>1782575759999</v>
       </c>
       <c r="BM66" t="n">
         <v>2377.735</v>
@@ -35098,12 +35098,12 @@
       </c>
       <c r="DQ66" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR66" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS66" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54417, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475829519_a10c747effe8730da723db2c68b446d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475941444_93bfd6b36159c37273b1bc1eafdf6263.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54417, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475829519_a10c747effe8730da723db2c68b446d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475941444_93bfd6b36159c37273b1bc1eafdf6263.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.49, "sourceLowPrice": 2372.91}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35414,13 +35414,13 @@
         </is>
       </c>
       <c r="BJ67" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK67" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782554141683</v>
+        <v>1782575760000</v>
       </c>
       <c r="BM67" t="n">
         <v>2378.966</v>
@@ -35622,12 +35622,12 @@
       </c>
       <c r="DQ67" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR67" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS67" t="inlineStr">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54418, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028261141_363434f7d1729ba2a54b88eb60df9a15.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028501115_02e09b779fd55a78b821d30c814e030e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54418, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028261141_363434f7d1729ba2a54b88eb60df9a15.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028501115_02e09b779fd55a78b821d30c814e030e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17313.443, "sourceLowPrice": 17051.323}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35938,13 +35938,13 @@
         </is>
       </c>
       <c r="BJ68" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK68" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782554141684</v>
+        <v>1782575760000</v>
       </c>
       <c r="BM68" t="n">
         <v>17369.62</v>
@@ -36146,12 +36146,12 @@
       </c>
       <c r="DQ68" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR68" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS68" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54419, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028596115_d290c96261982b8726740e00a9e4f65d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028668580_8986819606d157293db8fe4ed1fb8465.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54419, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028596115_d290c96261982b8726740e00a9e4f65d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028668580_8986819606d157293db8fe4ed1fb8465.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17262.421, "sourceLowPrice": 17101.947}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36462,13 +36462,13 @@
         </is>
       </c>
       <c r="BJ69" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK69" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782554141684</v>
+        <v>1782575760001</v>
       </c>
       <c r="BM69" t="n">
         <v>17275.186</v>
@@ -36670,12 +36670,12 @@
       </c>
       <c r="DQ69" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR69" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS69" t="inlineStr">
@@ -36937,7 +36937,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54420, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028734449_33fe9e9868ceaff3f8ed3fb9097046ec.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028795892_f6b0db224cb5a8c3f06af0e1d513b8bd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54420, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028734449_33fe9e9868ceaff3f8ed3fb9097046ec.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028795892_f6b0db224cb5a8c3f06af0e1d513b8bd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17225.197, "sourceLowPrice": 17139.087}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36986,13 +36986,13 @@
         </is>
       </c>
       <c r="BJ70" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK70" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782554141684</v>
+        <v>1782575760002</v>
       </c>
       <c r="BM70" t="n">
         <v>17240.521</v>
@@ -37194,12 +37194,12 @@
       </c>
       <c r="DQ70" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR70" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS70" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54421, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270824983_d03598517881d9f399d7f9aa75d1d307.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270912286_d91f6bdfceeaafb50571a4cc13bc6c2d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54421, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270824983_d03598517881d9f399d7f9aa75d1d307.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270912286_d91f6bdfceeaafb50571a4cc13bc6c2d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06552, "sourceLowPrice": 1.0624}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37510,13 +37510,13 @@
         </is>
       </c>
       <c r="BJ71" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK71" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782554141684</v>
+        <v>1782575760002</v>
       </c>
       <c r="BM71" t="n">
         <v>1.06634</v>
@@ -37718,12 +37718,12 @@
       </c>
       <c r="DQ71" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR71" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS71" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54422, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030298318_522b6f63ee28c8a9acbef0b01c18318e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030409417_4f02383121693aead3ece77c0c61cd8e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54422, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030298318_522b6f63ee28c8a9acbef0b01c18318e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030409417_4f02383121693aead3ece77c0c61cd8e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17152.521, "sourceLowPrice": 17103.543}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="BJ72" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK72" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782554141684</v>
+        <v>1782575760003</v>
       </c>
       <c r="BM72" t="n">
         <v>17163.598</v>
@@ -38242,12 +38242,12 @@
       </c>
       <c r="DQ72" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR72" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS72" t="inlineStr">
@@ -38509,7 +38509,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54423, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030765617_8cd264a1bc581c6873d1e82e0c17c4cc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030920133_890abe4a36216c3671bfb3052b056e18.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54423, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030765617_8cd264a1bc581c6873d1e82e0c17c4cc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030920133_890abe4a36216c3671bfb3052b056e18.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17187.476, "sourceLowPrice": 17121.975}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38558,13 +38558,13 @@
         </is>
       </c>
       <c r="BJ73" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK73" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782554141684</v>
+        <v>1782575760003</v>
       </c>
       <c r="BM73" t="n">
         <v>17168.708</v>
@@ -38766,12 +38766,12 @@
       </c>
       <c r="DQ73" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR73" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS73" t="inlineStr">
@@ -39033,7 +39033,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54424, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031085466_ef867640abb85cca497c0d4fc3dc7828.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031254620_e673e9c4fde5934dc7872511c80f4878.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54424, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031085466_ef867640abb85cca497c0d4fc3dc7828.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031254620_e673e9c4fde5934dc7872511c80f4878.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17171.054, "sourceLowPrice": 17005.92}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39082,13 +39082,13 @@
         </is>
       </c>
       <c r="BJ74" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK74" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782554141685</v>
+        <v>1782575760004</v>
       </c>
       <c r="BM74" t="n">
         <v>17188.665</v>
@@ -39290,12 +39290,12 @@
       </c>
       <c r="DQ74" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR74" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS74" t="inlineStr">
@@ -39557,7 +39557,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54425, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031327010_e719a7c46e7e7f61c564abef0a058b7d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031338997_74cac452534fcfbfbd51b1039a57179d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54425, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031327010_e719a7c46e7e7f61c564abef0a058b7d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031338997_74cac452534fcfbfbd51b1039a57179d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17134.265, "sourceLowPrice": 17025.775}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39606,13 +39606,13 @@
         </is>
       </c>
       <c r="BJ75" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK75" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782554141685</v>
+        <v>1782575760004</v>
       </c>
       <c r="BM75" t="n">
         <v>17154.776</v>
@@ -39814,12 +39814,12 @@
       </c>
       <c r="DQ75" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR75" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS75" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54427, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650581590_ce383b6e5d95442047eb77b65e90717a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650799344_20000e43a55cd1d064aa49ca6aed9add.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54427, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650581590_ce383b6e5d95442047eb77b65e90717a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650799344_20000e43a55cd1d064aa49ca6aed9add.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2304.73}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40130,13 +40130,13 @@
         </is>
       </c>
       <c r="BJ76" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK76" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782554141685</v>
+        <v>1782575760005</v>
       </c>
       <c r="BM76" t="n">
         <v>2297.925</v>
@@ -40338,12 +40338,12 @@
       </c>
       <c r="DQ76" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR76" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS76" t="inlineStr">
@@ -40605,7 +40605,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54428, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650934614_eb9c46b9329f2561fc9f6795009021fa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780651004593_afeebeac9e810a0166b07afe7ffef5dc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54428, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650934614_eb9c46b9329f2561fc9f6795009021fa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780651004593_afeebeac9e810a0166b07afe7ffef5dc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2305.76}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40654,13 +40654,13 @@
         </is>
       </c>
       <c r="BJ77" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK77" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782554141685</v>
+        <v>1782575760005</v>
       </c>
       <c r="BM77" t="n">
         <v>2308.285</v>
@@ -40862,12 +40862,12 @@
       </c>
       <c r="DQ77" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR77" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS77" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54429, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271232715_8829ebd89086dbf79c7137d930575416.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271361041_2ac8e5993f9c95012c237877365ce28f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54429, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271232715_8829ebd89086dbf79c7137d930575416.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271361041_2ac8e5993f9c95012c237877365ce28f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06828, "sourceLowPrice": 1.06532}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41178,13 +41178,13 @@
         </is>
       </c>
       <c r="BJ78" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK78" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782554141685</v>
+        <v>1782575760006</v>
       </c>
       <c r="BM78" t="n">
         <v>1.06964</v>
@@ -41386,12 +41386,12 @@
       </c>
       <c r="DQ78" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR78" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS78" t="inlineStr">
@@ -41653,7 +41653,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54430, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271479924_f3d0b05ace36fca84780275bc1d0bada.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271495525_1c0a85c474439df78657c65f49681fb1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54430, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271479924_f3d0b05ace36fca84780275bc1d0bada.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271495525_1c0a85c474439df78657c65f49681fb1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0678, "sourceLowPrice": 1.06646}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41702,13 +41702,13 @@
         </is>
       </c>
       <c r="BJ79" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK79" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782554141685</v>
+        <v>1782575760007</v>
       </c>
       <c r="BM79" t="n">
         <v>1.06732</v>
@@ -41910,12 +41910,12 @@
       </c>
       <c r="DQ79" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR79" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS79" t="inlineStr">
@@ -42177,7 +42177,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54431, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271681549_e3eafb5aa23e7edb3a547ee814de1fd4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271757981_58680a436fed6273a7c0371ac37dcae9.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54431, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271681549_e3eafb5aa23e7edb3a547ee814de1fd4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271757981_58680a436fed6273a7c0371ac37dcae9.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06912, "sourceLowPrice": 1.06601}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42226,13 +42226,13 @@
         </is>
       </c>
       <c r="BJ80" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK80" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782554141686</v>
+        <v>1782575760007</v>
       </c>
       <c r="BM80" t="n">
         <v>1.0679</v>
@@ -42434,12 +42434,12 @@
       </c>
       <c r="DQ80" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR80" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS80" t="inlineStr">
@@ -42701,7 +42701,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54433, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652206083_2d5f7e526d714b914aa041666679b662.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652457354_0d4530fc93baf439513bc55f9316a8a1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54433, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652206083_2d5f7e526d714b914aa041666679b662.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652457354_0d4530fc93baf439513bc55f9316a8a1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.547, "sourceLowPrice": 2312.17}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42750,13 +42750,13 @@
         </is>
       </c>
       <c r="BJ81" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK81" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782554141686</v>
+        <v>1782575760009</v>
       </c>
       <c r="BM81" t="n">
         <v>2310.815</v>
@@ -42958,12 +42958,12 @@
       </c>
       <c r="DQ81" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR81" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS81" t="inlineStr">
@@ -43225,7 +43225,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54434, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087598526_e9800cac8c13a5575c017835074459d2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087684329_79cbd1ee8e1ce5f5bcd8963e36aa3738.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54434, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087598526_e9800cac8c13a5575c017835074459d2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087684329_79cbd1ee8e1ce5f5bcd8963e36aa3738.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17615.199, "sourceLowPrice": 17576.042}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43274,13 +43274,13 @@
         </is>
       </c>
       <c r="BJ82" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK82" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782554141686</v>
+        <v>1782575760009</v>
       </c>
       <c r="BM82" t="n">
         <v>17597.899</v>
@@ -43482,12 +43482,12 @@
       </c>
       <c r="DQ82" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR82" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS82" t="inlineStr">
@@ -43749,7 +43749,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54435, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087800905_e90d9fb19261e3d8e941171d3d6a1bf5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088027067_a8b2c70f766de65966200150eaca161f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54435, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087800905_e90d9fb19261e3d8e941171d3d6a1bf5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088027067_a8b2c70f766de65966200150eaca161f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5089.307, "sourceLowPrice": 5046.48}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43798,13 +43798,13 @@
         </is>
       </c>
       <c r="BJ83" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK83" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782554141686</v>
+        <v>1782575760010</v>
       </c>
       <c r="BM83" t="n">
         <v>5089.687</v>
@@ -44006,12 +44006,12 @@
       </c>
       <c r="DQ83" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR83" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS83" t="inlineStr">
@@ -44273,7 +44273,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54436, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652605436_e7ceaa6e87b5983d03cb170921a0dbcb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652740475_ce8974483039dbf9c11c7fab479fe18a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54436, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652605436_e7ceaa6e87b5983d03cb170921a0dbcb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652740475_ce8974483039dbf9c11c7fab479fe18a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.04, "sourceLowPrice": 2316.07}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44322,13 +44322,13 @@
         </is>
       </c>
       <c r="BJ84" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK84" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782554141686</v>
+        <v>1782575760010</v>
       </c>
       <c r="BM84" t="n">
         <v>2316.37</v>
@@ -44530,12 +44530,12 @@
       </c>
       <c r="DQ84" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR84" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS84" t="inlineStr">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54437, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271986636_df37733a22627ee14b3bc05156272aed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272089738_257f9b3c4ad58e59b53f6572e7ad2154.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54437, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271986636_df37733a22627ee14b3bc05156272aed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272089738_257f9b3c4ad58e59b53f6572e7ad2154.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07067, "sourceLowPrice": 1.0681}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44846,13 +44846,13 @@
         </is>
       </c>
       <c r="BJ85" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK85" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782554141687</v>
+        <v>1782575760011</v>
       </c>
       <c r="BM85" t="n">
         <v>1.07036</v>
@@ -45054,12 +45054,12 @@
       </c>
       <c r="DQ85" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR85" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS85" t="inlineStr">
@@ -45321,7 +45321,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54438, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652931887_4b483900e26428d7b97b7f208b109418.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653108005_519113c47c608e272dab49cc54566372.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54438, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652931887_4b483900e26428d7b97b7f208b109418.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653108005_519113c47c608e272dab49cc54566372.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2333.597, "sourceLowPrice": 2318.44}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45370,13 +45370,13 @@
         </is>
       </c>
       <c r="BJ86" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK86" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782554141687</v>
+        <v>1782575760012</v>
       </c>
       <c r="BM86" t="n">
         <v>2315.93</v>
@@ -45578,12 +45578,12 @@
       </c>
       <c r="DQ86" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR86" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS86" t="inlineStr">
@@ -45845,7 +45845,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54439, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272239600_91f7b1ae937bf84ac635af31fe3c9664.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272340133_88bb568d8e1b5f1f20dc68342fdfbbb7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54439, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272239600_91f7b1ae937bf84ac635af31fe3c9664.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272340133_88bb568d8e1b5f1f20dc68342fdfbbb7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07299, "sourceLowPrice": 1.07141}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45894,13 +45894,13 @@
         </is>
       </c>
       <c r="BJ87" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK87" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782554141687</v>
+        <v>1782575760013</v>
       </c>
       <c r="BM87" t="n">
         <v>1.0732</v>
@@ -46102,12 +46102,12 @@
       </c>
       <c r="DQ87" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR87" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS87" t="inlineStr">
@@ -46369,7 +46369,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54440, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653723310_7474e526ff82ba41ed6994c16f9e10fe.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654198888_6c29d1e86372b8a9dde1984ff82b5063.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54440, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653723310_7474e526ff82ba41ed6994c16f9e10fe.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654198888_6c29d1e86372b8a9dde1984ff82b5063.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.81, "sourceLowPrice": 2312.87}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46418,13 +46418,13 @@
         </is>
       </c>
       <c r="BJ88" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK88" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782554141687</v>
+        <v>1782575760013</v>
       </c>
       <c r="BM88" t="n">
         <v>2322.33</v>
@@ -46626,12 +46626,12 @@
       </c>
       <c r="DQ88" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR88" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS88" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54441, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654291066_05ad6513f960d539f4dc94e22ce687c4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654527488_bde191c96a4a9b3e56d142dfa2e9a10a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54441, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654291066_05ad6513f960d539f4dc94e22ce687c4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654527488_bde191c96a4a9b3e56d142dfa2e9a10a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.366, "sourceLowPrice": 2315.07}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46942,13 +46942,13 @@
         </is>
       </c>
       <c r="BJ89" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK89" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782554141688</v>
+        <v>1782575760014</v>
       </c>
       <c r="BM89" t="n">
         <v>2311.87</v>
@@ -47150,12 +47150,12 @@
       </c>
       <c r="DQ89" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR89" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS89" t="inlineStr">
@@ -47417,7 +47417,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54442, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088443425_a24cf5b1d46b4b0b88b1d6670ada8ee5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088575298_da8f3b9cdcce0bbd1d82d1fd1e4604d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54442, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088443425_a24cf5b1d46b4b0b88b1d6670ada8ee5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088575298_da8f3b9cdcce0bbd1d82d1fd1e4604d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5022.673, "sourceLowPrice": 4988.411}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47466,13 +47466,13 @@
         </is>
       </c>
       <c r="BJ90" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK90" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782554141688</v>
+        <v>1782575760014</v>
       </c>
       <c r="BM90" t="n">
         <v>5008.429</v>
@@ -47674,12 +47674,12 @@
       </c>
       <c r="DQ90" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR90" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS90" t="inlineStr">
@@ -47941,7 +47941,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54443, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654609188_c2764965275ac78be910d14d43c40613.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654676062_c6b33018c028cb050c1c31d1ec69e0cd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54443, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654609188_c2764965275ac78be910d14d43c40613.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654676062_c6b33018c028cb050c1c31d1ec69e0cd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.935, "sourceLowPrice": 2317.07}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47990,13 +47990,13 @@
         </is>
       </c>
       <c r="BJ91" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK91" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782554141688</v>
+        <v>1782575760015</v>
       </c>
       <c r="BM91" t="n">
         <v>2316.09</v>
@@ -48198,12 +48198,12 @@
       </c>
       <c r="DQ91" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR91" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS91" t="inlineStr">
@@ -48465,7 +48465,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54444, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663010173_d983f1a0c9e0968dce85c1860bfad3b5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663144425_30881a904ad57e3e4358dfe603f74b0f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54444, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663010173_d983f1a0c9e0968dce85c1860bfad3b5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663144425_30881a904ad57e3e4358dfe603f74b0f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.12, "sourceLowPrice": 2345.83}</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -48514,13 +48514,13 @@
         </is>
       </c>
       <c r="BJ92" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK92" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL92" t="n">
-        <v>1782554141688</v>
+        <v>1782575760015</v>
       </c>
       <c r="BM92" t="n">
         <v>2346.24</v>
@@ -48722,12 +48722,12 @@
       </c>
       <c r="DQ92" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR92" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS92" t="inlineStr">
@@ -48989,7 +48989,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54445, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663391228_336c5b531cb51dfbe77807bff564c92b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663472599_40fc0c7e06f8dd6e9d62150d618e55c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54445, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663391228_336c5b531cb51dfbe77807bff564c92b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663472599_40fc0c7e06f8dd6e9d62150d618e55c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.0, "sourceLowPrice": 2342.16}</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -49038,13 +49038,13 @@
         </is>
       </c>
       <c r="BJ93" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK93" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL93" t="n">
-        <v>1782554141688</v>
+        <v>1782575760016</v>
       </c>
       <c r="BM93" t="n">
         <v>2342.47</v>
@@ -49246,12 +49246,12 @@
       </c>
       <c r="DQ93" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR93" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS93" t="inlineStr">
@@ -49513,7 +49513,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54446, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663583916_3b5098ae6bc5ebd3644c779723841484.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663652178_cfa0665487306c4c6fd6f12ab4c6c7af.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54446, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663583916_3b5098ae6bc5ebd3644c779723841484.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663652178_cfa0665487306c4c6fd6f12ab4c6c7af.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.65, "sourceLowPrice": 2342.52}</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -49562,13 +49562,13 @@
         </is>
       </c>
       <c r="BJ94" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK94" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL94" t="n">
-        <v>1782554141688</v>
+        <v>1782575760016</v>
       </c>
       <c r="BM94" t="n">
         <v>2341.16</v>
@@ -49770,12 +49770,12 @@
       </c>
       <c r="DQ94" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR94" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS94" t="inlineStr">
@@ -50037,7 +50037,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54447, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088957273_a7ae1924cffd0e49af829845fc8c72a0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781089151908_42a13b50e584dcc081573f10e79e6f93.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54447, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088957273_a7ae1924cffd0e49af829845fc8c72a0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781089151908_42a13b50e584dcc081573f10e79e6f93.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5122.379, "sourceLowPrice": 5072.157}</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -50086,13 +50086,13 @@
         </is>
       </c>
       <c r="BJ95" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK95" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL95" t="n">
-        <v>1782554141689</v>
+        <v>1782575760017</v>
       </c>
       <c r="BM95" t="n">
         <v>5108.242</v>
@@ -50294,12 +50294,12 @@
       </c>
       <c r="DQ95" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR95" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS95" t="inlineStr">
@@ -50561,7 +50561,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54448, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663875354_66e26edf5b46fc87a72866617b889a21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663971393_5d27b51fb3f0b2a304aa8a0eb38e4d4b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54448, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663875354_66e26edf5b46fc87a72866617b889a21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663971393_5d27b51fb3f0b2a304aa8a0eb38e4d4b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.32, "sourceLowPrice": 2328.77}</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -50610,13 +50610,13 @@
         </is>
       </c>
       <c r="BJ96" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK96" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL96" t="n">
-        <v>1782554141689</v>
+        <v>1782575760017</v>
       </c>
       <c r="BM96" t="n">
         <v>2335.98</v>
@@ -50818,12 +50818,12 @@
       </c>
       <c r="DQ96" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR96" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS96" t="inlineStr">
@@ -51085,7 +51085,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54449, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664081884_cb45e3cc4388dad70df15536aa081829.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664188275_b2b1c07e9becfb5172ac1be5424c8db4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54449, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664081884_cb45e3cc4388dad70df15536aa081829.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664188275_b2b1c07e9becfb5172ac1be5424c8db4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.38, "sourceLowPrice": 2328.77}</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -51134,13 +51134,13 @@
         </is>
       </c>
       <c r="BJ97" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK97" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL97" t="n">
-        <v>1782554141689</v>
+        <v>1782575760018</v>
       </c>
       <c r="BM97" t="n">
         <v>2330.895</v>
@@ -51342,12 +51342,12 @@
       </c>
       <c r="DQ97" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR97" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS97" t="inlineStr">
@@ -51609,7 +51609,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54451, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668025077_3d99263fbe62b8a71cd37f6df2075963.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668264554_736bc8b9d2defb6d7a67d32d67c3e595.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54451, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668025077_3d99263fbe62b8a71cd37f6df2075963.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668264554_736bc8b9d2defb6d7a67d32d67c3e595.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2330.07}</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -51658,13 +51658,13 @@
         </is>
       </c>
       <c r="BJ98" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK98" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL98" t="n">
-        <v>1782554141689</v>
+        <v>1782575760018</v>
       </c>
       <c r="BM98" t="n">
         <v>2326.515</v>
@@ -51866,12 +51866,12 @@
       </c>
       <c r="DQ98" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR98" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS98" t="inlineStr">
@@ -52133,7 +52133,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54452, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668351989_d6bf445a2fdff06f5d0ee351d6463fee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668445344_5fc1984f8afaf054f18c2436f81fa635.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54452, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668351989_d6bf445a2fdff06f5d0ee351d6463fee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668445344_5fc1984f8afaf054f18c2436f81fa635.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2332.21}</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -52182,13 +52182,13 @@
         </is>
       </c>
       <c r="BJ99" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK99" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL99" t="n">
-        <v>1782554141689</v>
+        <v>1782575760019</v>
       </c>
       <c r="BM99" t="n">
         <v>2330.977</v>
@@ -52390,12 +52390,12 @@
       </c>
       <c r="DQ99" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR99" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS99" t="inlineStr">
@@ -52657,7 +52657,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54455, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780669739101_0fca517685f5e96886202a2fea57c110.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780670004542_2e3e8971b4d5c8b0cb854df1d3509b8b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54455, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780669739101_0fca517685f5e96886202a2fea57c110.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780670004542_2e3e8971b4d5c8b0cb854df1d3509b8b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.22, "sourceLowPrice": 2310.479}</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -52706,13 +52706,13 @@
         </is>
       </c>
       <c r="BJ100" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK100" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL100" t="n">
-        <v>1782554141689</v>
+        <v>1782575760020</v>
       </c>
       <c r="BM100" t="n">
         <v>2318.26</v>
@@ -52914,12 +52914,12 @@
       </c>
       <c r="DQ100" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR100" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS100" t="inlineStr">
@@ -53181,7 +53181,7 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54456, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274729984_e4830aa863fe9ddf79840f9909e0f87a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274878983_7479f0db39fc8974304d0741fbb3edd6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54456, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274729984_e4830aa863fe9ddf79840f9909e0f87a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274878983_7479f0db39fc8974304d0741fbb3edd6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07296, "sourceLowPrice": 1.06749}</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
@@ -53230,13 +53230,13 @@
         </is>
       </c>
       <c r="BJ101" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK101" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL101" t="n">
-        <v>1782554141690</v>
+        <v>1782575760020</v>
       </c>
       <c r="BM101" t="n">
         <v>1.07365</v>
@@ -53438,12 +53438,12 @@
       </c>
       <c r="DQ101" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR101" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS101" t="inlineStr">
@@ -53705,7 +53705,7 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54457, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275007177_63fd6c85e0de519219fbef360c9df16a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275029549_85819c0a9f978e2e9a4ccce4283888e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54457, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275007177_63fd6c85e0de519219fbef360c9df16a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275029549_85819c0a9f978e2e9a4ccce4283888e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0724, "sourceLowPrice": 1.06813}</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
@@ -53754,13 +53754,13 @@
         </is>
       </c>
       <c r="BJ102" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK102" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL102" t="n">
-        <v>1782554141690</v>
+        <v>1782575760021</v>
       </c>
       <c r="BM102" t="n">
         <v>1.07298</v>
@@ -53962,12 +53962,12 @@
       </c>
       <c r="DQ102" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR102" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS102" t="inlineStr">
@@ -54229,7 +54229,7 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54460, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303685923_e409fc5fea77876cb76f943c77fc41ad.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303850406_b1db16e9494b4bbfa1009d8177c98939.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54460, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303685923_e409fc5fea77876cb76f943c77fc41ad.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303850406_b1db16e9494b4bbfa1009d8177c98939.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2865.095, "sourceLowPrice": 2859.0}</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
@@ -54278,13 +54278,13 @@
         </is>
       </c>
       <c r="BJ103" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK103" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL103" t="n">
-        <v>1782554141690</v>
+        <v>1782575760021</v>
       </c>
       <c r="BM103" t="n">
         <v>2859.825</v>
@@ -54486,12 +54486,12 @@
       </c>
       <c r="DQ103" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR103" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS103" t="inlineStr">
@@ -54753,7 +54753,7 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54461, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304291666_93f30a6e9557eeca95c6f6a984492655.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304556954_6aec2831ce8ce5ff589863e918f6b7de.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54461, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304291666_93f30a6e9557eeca95c6f6a984492655.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304556954_6aec2831ce8ce5ff589863e918f6b7de.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2863.9}</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
@@ -54802,13 +54802,13 @@
         </is>
       </c>
       <c r="BJ104" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK104" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL104" t="n">
-        <v>1782554141690</v>
+        <v>1782575760022</v>
       </c>
       <c r="BM104" t="n">
         <v>2858</v>
@@ -55010,12 +55010,12 @@
       </c>
       <c r="DQ104" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR104" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS104" t="inlineStr">
@@ -55277,7 +55277,7 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54462, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304656708_551d250f69dcc0c5de738454c9756589.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304729790_697c446b79b5764885f38cb71821c2f7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54462, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304656708_551d250f69dcc0c5de738454c9756589.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304729790_697c446b79b5764885f38cb71821c2f7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2864.375}</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
@@ -55326,13 +55326,13 @@
         </is>
       </c>
       <c r="BJ105" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK105" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL105" t="n">
-        <v>1782554141690</v>
+        <v>1782575760023</v>
       </c>
       <c r="BM105" t="n">
         <v>2866.72</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="DQ105" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR105" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS105" t="inlineStr">
@@ -55801,7 +55801,7 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54463, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304874760_768304f93f6241d6e2a795362ef340b4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305110232_ce7d27e554c668843c6c376b9ca0506c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54463, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304874760_768304f93f6241d6e2a795362ef340b4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305110232_ce7d27e554c668843c6c376b9ca0506c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2881.075, "sourceLowPrice": 2866.915}</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
@@ -55850,13 +55850,13 @@
         </is>
       </c>
       <c r="BJ106" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK106" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL106" t="n">
-        <v>1782554141691</v>
+        <v>1782575760023</v>
       </c>
       <c r="BM106" t="n">
         <v>2863.375</v>
@@ -56058,12 +56058,12 @@
       </c>
       <c r="DQ106" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR106" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS106" t="inlineStr">
@@ -56325,7 +56325,7 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54464, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305427085_a81f92769d7821925e3f2754f3a6fcfc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305558509_e91c3b2a1d99505bd249ec61bcb3c9be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54464, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305427085_a81f92769d7821925e3f2754f3a6fcfc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305558509_e91c3b2a1d99505bd249ec61bcb3c9be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2877.775, "sourceLowPrice": 2868.76}</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
@@ -56374,13 +56374,13 @@
         </is>
       </c>
       <c r="BJ107" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK107" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL107" t="n">
-        <v>1782554141691</v>
+        <v>1782575760024</v>
       </c>
       <c r="BM107" t="n">
         <v>2868.07</v>
@@ -56582,12 +56582,12 @@
       </c>
       <c r="DQ107" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR107" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS107" t="inlineStr">
@@ -56849,7 +56849,7 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54465, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305619233_eef8ed7bb4cf6796f8352152c1d8b395.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305666161_0f56886c8dd4977d54df3cf8f2fe61fa.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54465, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305619233_eef8ed7bb4cf6796f8352152c1d8b395.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305666161_0f56886c8dd4977d54df3cf8f2fe61fa.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2875.871, "sourceLowPrice": 2871.39}</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
@@ -56898,13 +56898,13 @@
         </is>
       </c>
       <c r="BJ108" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK108" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL108" t="n">
-        <v>1782554141691</v>
+        <v>1782575760025</v>
       </c>
       <c r="BM108" t="n">
         <v>2870.59</v>
@@ -57106,12 +57106,12 @@
       </c>
       <c r="DQ108" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR108" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS108" t="inlineStr">
@@ -57373,7 +57373,7 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54467, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301281883_8d43596df4708f26a26d2cc1c92902e3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301493516_66fcf7fa768b576b421e1b56fb018471.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54467, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301281883_8d43596df4708f26a26d2cc1c92902e3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301493516_66fcf7fa768b576b421e1b56fb018471.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05606, "sourceLowPrice": 1.04863}</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
@@ -57422,13 +57422,13 @@
         </is>
       </c>
       <c r="BJ109" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK109" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL109" t="n">
-        <v>1782554141691</v>
+        <v>1782575760025</v>
       </c>
       <c r="BM109" t="n">
         <v>1.048</v>
@@ -57630,12 +57630,12 @@
       </c>
       <c r="DQ109" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR109" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS109" t="inlineStr">
@@ -57897,7 +57897,7 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54468, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308656903_f7f106061695d7aa63fcc1098329b31d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308798367_b8c6a3c55b4c764b55aa235c0c986202.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54468, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308656903_f7f106061695d7aa63fcc1098329b31d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308798367_b8c6a3c55b4c764b55aa235c0c986202.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.416, "sourceLowPrice": 2896.785}</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
@@ -57946,13 +57946,13 @@
         </is>
       </c>
       <c r="BJ110" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK110" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL110" t="n">
-        <v>1782554141691</v>
+        <v>1782575760026</v>
       </c>
       <c r="BM110" t="n">
         <v>2895.39</v>
@@ -58154,12 +58154,12 @@
       </c>
       <c r="DQ110" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR110" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS110" t="inlineStr">
@@ -58421,7 +58421,7 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54477, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310320388_334bed17f36e063a5fa84c0ba7ea4974.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310496527_40f2c80c8f92c717bba5c2090b675388.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54477, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310320388_334bed17f36e063a5fa84c0ba7ea4974.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310496527_40f2c80c8f92c717bba5c2090b675388.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2917.375, "sourceLowPrice": 2913.05}</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
@@ -58470,13 +58470,13 @@
         </is>
       </c>
       <c r="BJ111" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK111" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL111" t="n">
-        <v>1782554141692</v>
+        <v>1782575760027</v>
       </c>
       <c r="BM111" t="n">
         <v>2913.745</v>
@@ -58678,12 +58678,12 @@
       </c>
       <c r="DQ111" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR111" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS111" t="inlineStr">
@@ -58945,7 +58945,7 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54478, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310715203_d1d361b5382d819ccf102ce5b800c271.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310946254_223ec4e1f4785bd7d517e1fd2bd2ecd2.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54478, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310715203_d1d361b5382d819ccf102ce5b800c271.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310946254_223ec4e1f4785bd7d517e1fd2bd2ecd2.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2915.86}</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
@@ -58994,13 +58994,13 @@
         </is>
       </c>
       <c r="BJ112" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK112" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL112" t="n">
-        <v>1782554141692</v>
+        <v>1782575760027</v>
       </c>
       <c r="BM112" t="n">
         <v>2912.05</v>
@@ -59202,12 +59202,12 @@
       </c>
       <c r="DQ112" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR112" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS112" t="inlineStr">
@@ -59469,7 +59469,7 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54479, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311020369_4e4750c0fe61cecdf8a5c7f9b09709b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311068841_5167c77814071dff66806aae9d95e09c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54479, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311020369_4e4750c0fe61cecdf8a5c7f9b09709b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311068841_5167c77814071dff66806aae9d95e09c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2913.44}</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
@@ -59518,13 +59518,13 @@
         </is>
       </c>
       <c r="BJ113" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK113" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL113" t="n">
-        <v>1782554141692</v>
+        <v>1782575760028</v>
       </c>
       <c r="BM113" t="n">
         <v>2916.755</v>
@@ -59726,12 +59726,12 @@
       </c>
       <c r="DQ113" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR113" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS113" t="inlineStr">
@@ -59993,7 +59993,7 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54480, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311281758_de9959ba074d8227db5f7b9db39b3e30.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311511444_a583ee11be73a1a9c146d4d45b32f991.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54480, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311281758_de9959ba074d8227db5f7b9db39b3e30.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311511444_a583ee11be73a1a9c146d4d45b32f991.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2919.39, "sourceLowPrice": 2912.055}</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
@@ -60042,13 +60042,13 @@
         </is>
       </c>
       <c r="BJ114" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK114" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL114" t="n">
-        <v>1782554141692</v>
+        <v>1782575760028</v>
       </c>
       <c r="BM114" t="n">
         <v>2908.1</v>
@@ -60250,12 +60250,12 @@
       </c>
       <c r="DQ114" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR114" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS114" t="inlineStr">
@@ -60517,7 +60517,7 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54481, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302282070_ed72ec542d8415e414a82f33aeb2958f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302387524_4b21a6fcaef3ea710f246778e309ec73.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54481, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302282070_ed72ec542d8415e414a82f33aeb2958f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302387524_4b21a6fcaef3ea710f246778e309ec73.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07925, "sourceLowPrice": 1.06869}</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="BJ115" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK115" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL115" t="n">
-        <v>1782554141692</v>
+        <v>1782575760029</v>
       </c>
       <c r="BM115" t="n">
         <v>1.06754</v>
@@ -60774,12 +60774,12 @@
       </c>
       <c r="DQ115" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR115" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS115" t="inlineStr">
@@ -61041,7 +61041,7 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54482, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311576830_70d737a01840fe66c82325d95910d5d0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311678638_3c62b2e9efebf3c270124585058f64b0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54482, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311576830_70d737a01840fe66c82325d95910d5d0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311678638_3c62b2e9efebf3c270124585058f64b0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.1, "sourceLowPrice": 2912.677}</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
@@ -61090,13 +61090,13 @@
         </is>
       </c>
       <c r="BJ116" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK116" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL116" t="n">
-        <v>1782554141692</v>
+        <v>1782575760030</v>
       </c>
       <c r="BM116" t="n">
         <v>2915.84</v>
@@ -61298,12 +61298,12 @@
       </c>
       <c r="DQ116" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR116" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS116" t="inlineStr">
@@ -61565,7 +61565,7 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54483, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302441555_439642e81a2a2872d4d12eccb0b33f27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302489069_7df53640835f86ba82ae7c2735d3538d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54483, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302441555_439642e81a2a2872d4d12eccb0b33f27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302489069_7df53640835f86ba82ae7c2735d3538d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07216}</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
@@ -61614,13 +61614,13 @@
         </is>
       </c>
       <c r="BJ117" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK117" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL117" t="n">
-        <v>1782554141693</v>
+        <v>1782575760030</v>
       </c>
       <c r="BM117" t="n">
         <v>1.07032</v>
@@ -61822,12 +61822,12 @@
       </c>
       <c r="DQ117" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR117" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS117" t="inlineStr">
@@ -62089,7 +62089,7 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54484, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353421941_79cff43a6102b1b4cc2c846c3ecf1fa5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353568638_05bda76c68d69fe954c3d756ce6812e0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54484, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353421941_79cff43a6102b1b4cc2c846c3ecf1fa5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353568638_05bda76c68d69fe954c3d756ce6812e0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5795.614, "sourceLowPrice": 5742.079}</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
@@ -62138,13 +62138,13 @@
         </is>
       </c>
       <c r="BJ118" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK118" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL118" t="n">
-        <v>1782554141693</v>
+        <v>1782575760031</v>
       </c>
       <c r="BM118" t="n">
         <v>5807.915</v>
@@ -62346,12 +62346,12 @@
       </c>
       <c r="DQ118" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR118" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS118" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54485, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353671315_1d99b670749f74056ab256517c04a7d7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353704848_7de0729f6a46fae04d6442e7fb78b0be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54485, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353671315_1d99b670749f74056ab256517c04a7d7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353704848_7de0729f6a46fae04d6442e7fb78b0be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5786.506, "sourceLowPrice": 5742.079}</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
@@ -62662,13 +62662,13 @@
         </is>
       </c>
       <c r="BJ119" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK119" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL119" t="n">
-        <v>1782554141693</v>
+        <v>1782575760032</v>
       </c>
       <c r="BM119" t="n">
         <v>5763.529</v>
@@ -62870,12 +62870,12 @@
       </c>
       <c r="DQ119" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR119" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS119" t="inlineStr">
@@ -63137,7 +63137,7 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54486, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439233487_eef0a14a0519a9d53a79bbc0bb8c309e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440657327_fb9733aa9156f595e9d557c7660d15fb.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54486, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439233487_eef0a14a0519a9d53a79bbc0bb8c309e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440657327_fb9733aa9156f595e9d557c7660d15fb.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.35, "sourceLowPrice": 4382.975}</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
@@ -63186,13 +63186,13 @@
         </is>
       </c>
       <c r="BJ120" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK120" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL120" t="n">
-        <v>1782554141693</v>
+        <v>1782575760032</v>
       </c>
       <c r="BM120" t="n">
         <v>4397.31</v>
@@ -63394,12 +63394,12 @@
       </c>
       <c r="DQ120" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR120" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS120" t="inlineStr">
@@ -63661,7 +63661,7 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54487, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440776187_b62d86c09e3090b0d7bf4349bb031182.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440803044_33bc271976b402786bf7d6071f190a0b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54487, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440776187_b62d86c09e3090b0d7bf4349bb031182.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440803044_33bc271976b402786bf7d6071f190a0b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.145, "sourceLowPrice": 4386.49}</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
@@ -63710,13 +63710,13 @@
         </is>
       </c>
       <c r="BJ121" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK121" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL121" t="n">
-        <v>1782554141693</v>
+        <v>1782575760033</v>
       </c>
       <c r="BM121" t="n">
         <v>4393.75</v>
@@ -63918,12 +63918,12 @@
       </c>
       <c r="DQ121" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR121" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS121" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54488, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439760945_a0606e9630178667f056606da8cff8e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439834992_c39ac848d91414524a2bf7943e4d849b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54488, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439760945_a0606e9630178667f056606da8cff8e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439834992_c39ac848d91414524a2bf7943e4d849b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4404.33, "sourceLowPrice": 4389.8}</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
@@ -64234,13 +64234,13 @@
         </is>
       </c>
       <c r="BJ122" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK122" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL122" t="n">
-        <v>1782554141693</v>
+        <v>1782575760033</v>
       </c>
       <c r="BM122" t="n">
         <v>4400.195</v>
@@ -64442,12 +64442,12 @@
       </c>
       <c r="DQ122" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR122" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS122" t="inlineStr">
@@ -64709,7 +64709,7 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54491, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441037891_89af802c88456c34499420a0ce8e0235.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441105819_299be3609ea9f2d7f36d97f51845bda0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54491, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441037891_89af802c88456c34499420a0ce8e0235.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441105819_299be3609ea9f2d7f36d97f51845bda0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4526.2, "sourceLowPrice": 4510.695}</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
@@ -64758,13 +64758,13 @@
         </is>
       </c>
       <c r="BJ123" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK123" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL123" t="n">
-        <v>1782554141694</v>
+        <v>1782575760034</v>
       </c>
       <c r="BM123" t="n">
         <v>4525.09</v>
@@ -64966,12 +64966,12 @@
       </c>
       <c r="DQ123" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR123" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS123" t="inlineStr">
@@ -65233,7 +65233,7 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54492, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/GvACQjVR/", "exitScreenshotUrl": "https://www.tradingview.com/x/8Xr8vSkG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54492, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/GvACQjVR/", "exitScreenshotUrl": "https://www.tradingview.com/x/8Xr8vSkG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30369.42, "sourceLowPrice": 30261.36}</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
@@ -65282,13 +65282,13 @@
         </is>
       </c>
       <c r="BJ124" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK124" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL124" t="n">
-        <v>1782554141694</v>
+        <v>1782575760034</v>
       </c>
       <c r="BM124" t="n">
         <v>30247.61</v>
@@ -65490,12 +65490,12 @@
       </c>
       <c r="DQ124" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR124" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS124" t="inlineStr">
@@ -65757,7 +65757,7 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54493, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KnYLbmBZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/AcWYB0Cv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54493, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KnYLbmBZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/AcWYB0Cv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30399.27, "sourceLowPrice": 30243.44}</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
@@ -65806,13 +65806,13 @@
         </is>
       </c>
       <c r="BJ125" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK125" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL125" t="n">
-        <v>1782554141694</v>
+        <v>1782575760035</v>
       </c>
       <c r="BM125" t="n">
         <v>30220.89</v>
@@ -66014,12 +66014,12 @@
       </c>
       <c r="DQ125" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR125" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS125" t="inlineStr">
@@ -66281,7 +66281,7 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54494, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441839312_1d39c529782c85841d6aa8e067bc16bd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781442000674_37114c4f1d119bd74bd377f01e745201.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54494, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441839312_1d39c529782c85841d6aa8e067bc16bd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781442000674_37114c4f1d119bd74bd377f01e745201.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4511.08, "sourceLowPrice": 4483.035}</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
@@ -66330,13 +66330,13 @@
         </is>
       </c>
       <c r="BJ126" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK126" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL126" t="n">
-        <v>1782554141694</v>
+        <v>1782575760036</v>
       </c>
       <c r="BM126" t="n">
         <v>4514.08</v>
@@ -66538,12 +66538,12 @@
       </c>
       <c r="DQ126" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR126" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS126" t="inlineStr">
@@ -66805,7 +66805,7 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54495, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OWR3I5Ua/", "exitScreenshotUrl": "https://www.tradingview.com/x/cnxCjKvH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54495, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OWR3I5Ua/", "exitScreenshotUrl": "https://www.tradingview.com/x/cnxCjKvH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7607.64, "sourceLowPrice": 7594.78}</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
@@ -66854,13 +66854,13 @@
         </is>
       </c>
       <c r="BJ127" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK127" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL127" t="n">
-        <v>1782554141694</v>
+        <v>1782575760036</v>
       </c>
       <c r="BM127" t="n">
         <v>7599.05</v>
@@ -67062,12 +67062,12 @@
       </c>
       <c r="DQ127" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR127" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS127" t="inlineStr">
@@ -67329,7 +67329,7 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54496, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460606718_ae635194e7ab72a81f01abd021934e20.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460685557_fc8014807b37edbe8dc47be018eec600.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54496, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460606718_ae635194e7ab72a81f01abd021934e20.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460685557_fc8014807b37edbe8dc47be018eec600.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4472.375, "sourceLowPrice": 4455.39}</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
@@ -67378,13 +67378,13 @@
         </is>
       </c>
       <c r="BJ128" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK128" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL128" t="n">
-        <v>1782554141694</v>
+        <v>1782575760037</v>
       </c>
       <c r="BM128" t="n">
         <v>4472.06</v>
@@ -67586,12 +67586,12 @@
       </c>
       <c r="DQ128" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR128" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS128" t="inlineStr">
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54497, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461047997_211ed43f16c631c32fb4184e946e5c6b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461109260_e0bce7b2f349723b4f894f8a96301d0e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54497, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461047997_211ed43f16c631c32fb4184e946e5c6b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461109260_e0bce7b2f349723b4f894f8a96301d0e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.05, "sourceLowPrice": 4440.365}</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
@@ -67902,13 +67902,13 @@
         </is>
       </c>
       <c r="BJ129" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK129" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL129" t="n">
-        <v>1782554141695</v>
+        <v>1782575760038</v>
       </c>
       <c r="BM129" t="n">
         <v>4460.495</v>
@@ -68110,12 +68110,12 @@
       </c>
       <c r="DQ129" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR129" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS129" t="inlineStr">
@@ -68377,7 +68377,7 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54498, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461204254_b8345ba0f02eb80b55dac9630715d877.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461373812_5645374331f7bc2d7c84176cebaef940.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54498, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461204254_b8345ba0f02eb80b55dac9630715d877.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461373812_5645374331f7bc2d7c84176cebaef940.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.19, "sourceLowPrice": 4439.09}</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
@@ -68426,13 +68426,13 @@
         </is>
       </c>
       <c r="BJ130" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK130" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL130" t="n">
-        <v>1782554141695</v>
+        <v>1782575760038</v>
       </c>
       <c r="BM130" t="n">
         <v>4460.135</v>
@@ -68634,12 +68634,12 @@
       </c>
       <c r="DQ130" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR130" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS130" t="inlineStr">
@@ -68901,7 +68901,7 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54499, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461544247_84d71b024e8873288004ad42d22923b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461949380_d1a9f53372902615cb3ee9567ea2d577.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54499, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461544247_84d71b024e8873288004ad42d22923b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461949380_d1a9f53372902615cb3ee9567ea2d577.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.745, "sourceLowPrice": 4424.019}</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
@@ -68950,13 +68950,13 @@
         </is>
       </c>
       <c r="BJ131" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK131" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL131" t="n">
-        <v>1782554141695</v>
+        <v>1782575760039</v>
       </c>
       <c r="BM131" t="n">
         <v>4468.255</v>
@@ -69158,12 +69158,12 @@
       </c>
       <c r="DQ131" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR131" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS131" t="inlineStr">
@@ -69425,7 +69425,7 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54500, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/k9ad4cJg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S4wBBKKA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54500, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/k9ad4cJg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S4wBBKKA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7589.67, "sourceLowPrice": 7573.45}</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
@@ -69474,13 +69474,13 @@
         </is>
       </c>
       <c r="BJ132" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK132" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL132" t="n">
-        <v>1782554141695</v>
+        <v>1782575760040</v>
       </c>
       <c r="BM132" t="n">
         <v>7593.41</v>
@@ -69682,12 +69682,12 @@
       </c>
       <c r="DQ132" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR132" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS132" t="inlineStr">
@@ -69949,7 +69949,7 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54501, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461999378_831cbaea472990c4075d3dd84326969b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462052555_260d88a4c58804ca85bc3d6732b3144b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54501, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461999378_831cbaea472990c4075d3dd84326969b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462052555_260d88a4c58804ca85bc3d6732b3144b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4452.32, "sourceLowPrice": 4424.019}</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
@@ -69998,13 +69998,13 @@
         </is>
       </c>
       <c r="BJ133" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK133" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL133" t="n">
-        <v>1782554141696</v>
+        <v>1782575760040</v>
       </c>
       <c r="BM133" t="n">
         <v>4452.68</v>
@@ -70206,12 +70206,12 @@
       </c>
       <c r="DQ133" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR133" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS133" t="inlineStr">
@@ -70473,7 +70473,7 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54502, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462412304_f70b2896e8123a6776dc55ce41c87e1f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462560066_9ce2ef58a5ec31f69c33594b63777e03.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54502, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462412304_f70b2896e8123a6776dc55ce41c87e1f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462560066_9ce2ef58a5ec31f69c33594b63777e03.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4482.976, "sourceLowPrice": 4461.035}</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
@@ -70522,13 +70522,13 @@
         </is>
       </c>
       <c r="BJ134" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK134" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL134" t="n">
-        <v>1782554141696</v>
+        <v>1782575760041</v>
       </c>
       <c r="BM134" t="n">
         <v>4470.595</v>
@@ -70730,12 +70730,12 @@
       </c>
       <c r="DQ134" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR134" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS134" t="inlineStr">
@@ -70997,7 +70997,7 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54503, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462693805_09f7cd07274089cdd38058211e9a1f1e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462787684_f531a0924f42c85131a928a281c27b3c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54503, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462693805_09f7cd07274089cdd38058211e9a1f1e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462787684_f531a0924f42c85131a928a281c27b3c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4488.354, "sourceLowPrice": 4473.54}</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
@@ -71046,13 +71046,13 @@
         </is>
       </c>
       <c r="BJ135" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK135" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL135" t="n">
-        <v>1782554141696</v>
+        <v>1782575760042</v>
       </c>
       <c r="BM135" t="n">
         <v>4479.87</v>
@@ -71254,12 +71254,12 @@
       </c>
       <c r="DQ135" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR135" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS135" t="inlineStr">
@@ -71521,7 +71521,7 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54509, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463536745_df3c43117506f308a7366417a5cada9c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463632349_eed7dd4e351b3048fa194c6331403a3d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54509, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463536745_df3c43117506f308a7366417a5cada9c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463632349_eed7dd4e351b3048fa194c6331403a3d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4469.465, "sourceLowPrice": 4458.895}</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
@@ -71570,13 +71570,13 @@
         </is>
       </c>
       <c r="BJ136" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK136" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL136" t="n">
-        <v>1782554141696</v>
+        <v>1782575760042</v>
       </c>
       <c r="BM136" t="n">
         <v>4469.355</v>
@@ -71778,12 +71778,12 @@
       </c>
       <c r="DQ136" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR136" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS136" t="inlineStr">
@@ -72045,7 +72045,7 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54510, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463742050_14e6e5e9265b43ec082f402286e39772.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463858899_dc421abe368df463fc04b493778f9d4e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54510, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463742050_14e6e5e9265b43ec082f402286e39772.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463858899_dc421abe368df463fc04b493778f9d4e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.96, "sourceLowPrice": 4459.305}</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
@@ -72094,13 +72094,13 @@
         </is>
       </c>
       <c r="BJ137" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK137" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL137" t="n">
-        <v>1782554141696</v>
+        <v>1782575760043</v>
       </c>
       <c r="BM137" t="n">
         <v>4470.465</v>
@@ -72302,12 +72302,12 @@
       </c>
       <c r="DQ137" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR137" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS137" t="inlineStr">
@@ -72569,7 +72569,7 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54511, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781464006050_b9ae9fb4af1afcee05d47506273aa74f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781465195928_dab8a5991bec66ac4117372bbffa7a10.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54511, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781464006050_b9ae9fb4af1afcee05d47506273aa74f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781465195928_dab8a5991bec66ac4117372bbffa7a10.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4475.885, "sourceLowPrice": 4458.28}</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
@@ -72618,13 +72618,13 @@
         </is>
       </c>
       <c r="BJ138" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK138" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL138" t="n">
-        <v>1782554141697</v>
+        <v>1782575760043</v>
       </c>
       <c r="BM138" t="n">
         <v>4469.315</v>
@@ -72826,12 +72826,12 @@
       </c>
       <c r="DQ138" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR138" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS138" t="inlineStr">
@@ -73093,7 +73093,7 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54512, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qnI0VDAP/", "exitScreenshotUrl": "https://www.tradingview.com/x/WLDhKg3O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54512, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qnI0VDAP/", "exitScreenshotUrl": "https://www.tradingview.com/x/WLDhKg3O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30061.68, "sourceLowPrice": 29706.99}</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
@@ -73142,13 +73142,13 @@
         </is>
       </c>
       <c r="BJ139" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK139" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL139" t="n">
-        <v>1782554141697</v>
+        <v>1782575760044</v>
       </c>
       <c r="BM139" t="n">
         <v>30098.03</v>
@@ -73350,12 +73350,12 @@
       </c>
       <c r="DQ139" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR139" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS139" t="inlineStr">
@@ -73617,7 +73617,7 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54513, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468059676_dc1d99e33491dee5977740e2247c93eb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468158740_09157e1f0c23533d5d77db299724ece6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54513, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468059676_dc1d99e33491dee5977740e2247c93eb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468158740_09157e1f0c23533d5d77db299724ece6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4311.956, "sourceLowPrice": 4273.165}</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
@@ -73666,13 +73666,13 @@
         </is>
       </c>
       <c r="BJ140" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK140" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL140" t="n">
-        <v>1782554141697</v>
+        <v>1782575760044</v>
       </c>
       <c r="BM140" t="n">
         <v>4294.92</v>
@@ -73874,12 +73874,12 @@
       </c>
       <c r="DQ140" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR140" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS140" t="inlineStr">
@@ -74141,7 +74141,7 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54514, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469193286_5651542d75ebb45a455417ddd3003a1c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469307424_656b525bab889df9df912874b80def96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54514, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469193286_5651542d75ebb45a455417ddd3003a1c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469307424_656b525bab889df9df912874b80def96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4319.498, "sourceLowPrice": 4296.92}</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
@@ -74190,13 +74190,13 @@
         </is>
       </c>
       <c r="BJ141" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK141" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL141" t="n">
-        <v>1782554141697</v>
+        <v>1782575760044</v>
       </c>
       <c r="BM141" t="n">
         <v>4306.941</v>
@@ -74398,12 +74398,12 @@
       </c>
       <c r="DQ141" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR141" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS141" t="inlineStr">
@@ -74665,7 +74665,7 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54516, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781472975283_121987fb8605c81036be6bbb977b3e6f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473145242_1cdabbf45d8dc46c735f8cd01c78fa28.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54516, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781472975283_121987fb8605c81036be6bbb977b3e6f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473145242_1cdabbf45d8dc46c735f8cd01c78fa28.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4324.19}</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
@@ -74714,13 +74714,13 @@
         </is>
       </c>
       <c r="BJ142" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK142" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL142" t="n">
-        <v>1782554141697</v>
+        <v>1782575760045</v>
       </c>
       <c r="BM142" t="n">
         <v>4338.02</v>
@@ -74922,12 +74922,12 @@
       </c>
       <c r="DQ142" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR142" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS142" t="inlineStr">
@@ -75189,7 +75189,7 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54517, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473295670_21d74969f3059f574d9eaf694d0e904f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473366648_57617edc0ef6a366982cf12aee3c9476.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54517, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473295670_21d74969f3059f574d9eaf694d0e904f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473366648_57617edc0ef6a366982cf12aee3c9476.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4337.475}</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
@@ -75238,13 +75238,13 @@
         </is>
       </c>
       <c r="BJ143" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK143" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL143" t="n">
-        <v>1782554141697</v>
+        <v>1782575760045</v>
       </c>
       <c r="BM143" t="n">
         <v>4341.965</v>
@@ -75446,12 +75446,12 @@
       </c>
       <c r="DQ143" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR143" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS143" t="inlineStr">
@@ -75713,7 +75713,7 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54520, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533495202_896f7d04ccac2c18b6902075aaeeba21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533678012_ec07648d6ac856da3ef339f487803e44.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54520, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533495202_896f7d04ccac2c18b6902075aaeeba21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533678012_ec07648d6ac856da3ef339f487803e44.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4209.88, "sourceLowPrice": 4144.268}</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
@@ -75762,13 +75762,13 @@
         </is>
       </c>
       <c r="BJ144" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK144" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL144" t="n">
-        <v>1782554141698</v>
+        <v>1782575760046</v>
       </c>
       <c r="BM144" t="n">
         <v>4223.005</v>
@@ -75970,12 +75970,12 @@
       </c>
       <c r="DQ144" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR144" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS144" t="inlineStr">
@@ -76237,7 +76237,7 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54521, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533714542_589108ab73f44f8e09e5815fa031e759.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533806485_ffc6f911a10f0ef0bbb65a53de36e311.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54521, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533714542_589108ab73f44f8e09e5815fa031e759.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533806485_ffc6f911a10f0ef0bbb65a53de36e311.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4195.31, "sourceLowPrice": 4157.248}</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
@@ -76286,13 +76286,13 @@
         </is>
       </c>
       <c r="BJ145" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK145" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL145" t="n">
-        <v>1782554141698</v>
+        <v>1782575760047</v>
       </c>
       <c r="BM145" t="n">
         <v>4197.77</v>
@@ -76494,12 +76494,12 @@
       </c>
       <c r="DQ145" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR145" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS145" t="inlineStr">
@@ -76761,7 +76761,7 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54524, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781539972331_048e65ca18a8b4f52e31d6068683e140.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540125579_109f267fc4807e8215a5dd009208713f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54524, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781539972331_048e65ca18a8b4f52e31d6068683e140.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540125579_109f267fc4807e8215a5dd009208713f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4096.07, "sourceLowPrice": 4062.767}</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
@@ -76810,13 +76810,13 @@
         </is>
       </c>
       <c r="BJ146" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK146" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL146" t="n">
-        <v>1782554141698</v>
+        <v>1782575760047</v>
       </c>
       <c r="BM146" t="n">
         <v>4097.54</v>
@@ -77018,12 +77018,12 @@
       </c>
       <c r="DQ146" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR146" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS146" t="inlineStr">
@@ -77285,7 +77285,7 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54525, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540198593_182059ebb741237b006a35e9d228d3aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540209654_2bf1f13802938b902ca280b4a63c624b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54525, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540198593_182059ebb741237b006a35e9d228d3aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540209654_2bf1f13802938b902ca280b4a63c624b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4086.68, "sourceLowPrice": 4067.638}</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
@@ -77334,13 +77334,13 @@
         </is>
       </c>
       <c r="BJ147" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK147" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL147" t="n">
-        <v>1782554141698</v>
+        <v>1782575760048</v>
       </c>
       <c r="BM147" t="n">
         <v>4088.54</v>
@@ -77542,12 +77542,12 @@
       </c>
       <c r="DQ147" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR147" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS147" t="inlineStr">
@@ -77809,7 +77809,7 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54526, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540400171_440149fe2263f6ee7d3aba448a8e8ca6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540570241_112727011df2180cc462d7cde1804b89.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54526, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540400171_440149fe2263f6ee7d3aba448a8e8ca6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540570241_112727011df2180cc462d7cde1804b89.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4092.92, "sourceLowPrice": 4067.285}</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
@@ -77858,13 +77858,13 @@
         </is>
       </c>
       <c r="BJ148" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK148" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL148" t="n">
-        <v>1782554141698</v>
+        <v>1782575760049</v>
       </c>
       <c r="BM148" t="n">
         <v>4086.325</v>
@@ -78066,12 +78066,12 @@
       </c>
       <c r="DQ148" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR148" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS148" t="inlineStr">
@@ -78333,7 +78333,7 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54527, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9SgUNL9j/", "exitScreenshotUrl": "https://www.tradingview.com/x/ypgXv0qj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54527, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9SgUNL9j/", "exitScreenshotUrl": "https://www.tradingview.com/x/ypgXv0qj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30301.65, "sourceLowPrice": 30225.28}</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
@@ -78382,13 +78382,13 @@
         </is>
       </c>
       <c r="BJ149" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BK149" t="n">
-        <v>945138</v>
+        <v>37</v>
       </c>
       <c r="BL149" t="n">
-        <v>1782554141699</v>
+        <v>1782575760049</v>
       </c>
       <c r="BM149" t="n">
         <v>30255.28</v>
@@ -78590,12 +78590,12 @@
       </c>
       <c r="DQ149" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DR149" t="inlineStr">
         <is>
-          <t>journalAccount:945138</t>
+          <t>journalAccount:59</t>
         </is>
       </c>
       <c r="DS149" t="inlineStr">
@@ -78666,6 +78666,530 @@
         </is>
       </c>
       <c r="EJ149" t="inlineStr">
+        <is>
+          <t>Prop</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>54528</v>
+      </c>
+      <c r="B150" t="n">
+        <v>54528</v>
+      </c>
+      <c r="C150" t="n">
+        <v>149</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>mentor-laith 3-54528</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>54528</v>
+      </c>
+      <c r="F150" t="n">
+        <v>149</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Mentor · laith 3</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Fibonacci Confluence Swing</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>1781517000000</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1781517000000</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>2026-06-15T09:50:00.000Z</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U150" t="n">
+        <v>1781529180000</v>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-06-15T13:13:00.000Z</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>2026-06-15T13:13:00.000Z</t>
+        </is>
+      </c>
+      <c r="X150" t="n">
+        <v>4359.065</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>4359.065</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>4370.085</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>126</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>126</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>126</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2.5177</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>2.5177</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>203</v>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AP150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>4370.085</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>2.5177</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.5177</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>4370.085</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>{"mentorImport": true, "mentorTradeId": 54528, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gTtR53lU/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkjiCYeO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": true, "excursionSanitizeReason": "missing_high_low", "sourceHighPrice": 4369.665, "sourceLowPrice": null}</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>["adding: No", "dol: LRLR", "entry: MSS+BOS", "n: Above PDH", "pda: HTF-KL", "reversal: Yes", "rr: 2", "smt: Swings", "taken: PDH", "time: LnDc"]</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>["Outcome review: Yes", "Win"]</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>["adding: No", "dol: LRLR", "entry: MSS+BOS", "n: Above PDH", "pda: HTF-KL", "reversal: Yes", "rr: 2", "smt: Swings", "taken: PDH", "time: LnDc", "Outcome review: Yes", "Win"]</t>
+        </is>
+      </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>[{"id": "adding", "name": "adding", "vtype": "multi", "value": "No"}, {"id": "dol", "name": "dol", "vtype": "multi", "value": "LRLR"}, {"id": "entry", "name": "entry", "vtype": "multi", "value": "MSS+BOS"}, {"id": "n", "name": "n", "vtype": "multi", "value": "Above PDH"}, {"id": "pda", "name": "pda", "vtype": "multi", "value": "HTF-KL"}, {"id": "reversal", "name": "reversal", "vtype": "multi", "value": "Yes"}, {"id": "rr", "name": "rr", "vtype": "multi", "value": "2"}, {"id": "smt", "name": "smt", "vtype": "multi", "value": "Swings"}, {"id": "taken", "name": "taken", "vtype": "multi", "value": "PDH"}, {"id": "time", "name": "time", "vtype": "multi", "value": "LnDc"}]</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>[{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}]</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/x/gTtR53lU/</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/x/AkjiCYeO/</t>
+        </is>
+      </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BJ150" t="n">
+        <v>37</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>37</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1782575760050</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>4370.085</v>
+      </c>
+      <c r="BN150" t="inlineStr">
+        <is>
+          <t>[{"price": 4331.32, "percentage": 100, "hit": true}]</t>
+        </is>
+      </c>
+      <c r="BO150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BQ150" t="n">
+        <v>4359.065</v>
+      </c>
+      <c r="BR150" t="n">
+        <v>15668.68</v>
+      </c>
+      <c r="BS150" t="n">
+        <v>15794.68</v>
+      </c>
+      <c r="BT150" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0629, 0.1259, 0.1888, 0.2518, 0.3147, 0.3777, 0.4406, 0.5035, 0.5665, 0.6294, 0.6924, 0.7553, 0.8183, 0.8812, 0.9441, 1.0071, 1.07, 1.133, 1.1959, 1.2588, 1.3218, 1.3847, 1.4477, 1.5106, 1.5736, 1.6365, 1.6994, 1.7624, 1.8253, 1.8883, 1.9512, 2.0142, 2.0771, 2.14, 2.203, 2.2659, 2.3289, 2.3918, 2.4548, 2.5177]</t>
+        </is>
+      </c>
+      <c r="BU150" t="inlineStr">
+        <is>
+          <t>[0.0, 0.2267, 0.4439, 0.6509, 0.8469, 1.0313, 1.2035, 1.3631, 1.5098, 1.6436, 1.7644, 1.8722, 1.9672, 2.0499, 2.1206, 2.1798, 2.2283, 2.2665, 2.2955, 2.316, 2.3289, 2.3352, 2.3359, 2.3321, 2.3247, 2.315, 2.3039, 2.2925, 2.2818, 2.2728, 2.2666, 2.2639, 2.2657, 2.2728, 2.2858, 2.3054, 2.3321, 2.3663, 2.4085, 2.459, 2.5177]</t>
+        </is>
+      </c>
+      <c r="BV150" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0079, 0.0238, 0.0471, 0.077, 0.1129, 0.154, 0.1992, 0.2477, 0.2983, 0.3499, 0.4015, 0.4518, 0.4995, 0.5435, 0.5826, 0.6154, 0.6409, 0.6577, 0.6649, 0.6612, 0.6456, 0.6173, 0.5754, 0.519, 0.4475, 0.3603, 0.257, 0.1372, 0.0008, -0.1523, -0.3221, -0.5082, -0.7105, -0.9283, -1.1611, -1.4081, -1.6683, -1.9408, -2.2244, -2.5177]</t>
+        </is>
+      </c>
+      <c r="BW150" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="BX150" t="n">
+        <v>149</v>
+      </c>
+      <c r="BY150" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="BZ150" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA150" t="n">
+        <v>1781517000000</v>
+      </c>
+      <c r="CB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC150" t="b">
+        <v>1</v>
+      </c>
+      <c r="CD150" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="CE150" t="n">
+        <v>126</v>
+      </c>
+      <c r="CF150" t="n">
+        <v>41</v>
+      </c>
+      <c r="CG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH150" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI150" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="CJ150" t="n">
+        <v>3.3833</v>
+      </c>
+      <c r="CK150" t="n">
+        <v>12180000</v>
+      </c>
+      <c r="CL150" t="n">
+        <v>9</v>
+      </c>
+      <c r="CM150" t="n">
+        <v>13</v>
+      </c>
+      <c r="CN150" t="n">
+        <v>4370.085</v>
+      </c>
+      <c r="CO150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="CP150" t="b">
+        <v>0</v>
+      </c>
+      <c r="CQ150" t="b">
+        <v>0</v>
+      </c>
+      <c r="CR150" t="n">
+        <v>1781528580000</v>
+      </c>
+      <c r="CS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT150" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="CU150" t="n">
+        <v>1781523090000</v>
+      </c>
+      <c r="CV150" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="CW150" t="inlineStr">
+        <is>
+          <t>[4331.32]</t>
+        </is>
+      </c>
+      <c r="CX150" t="n">
+        <v>126</v>
+      </c>
+      <c r="CY150" t="n">
+        <v>50</v>
+      </c>
+      <c r="CZ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA150" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB150" t="n">
+        <v>4359.065</v>
+      </c>
+      <c r="DC150" t="n">
+        <v>2.5177</v>
+      </c>
+      <c r="DD150" t="n">
+        <v>4331.32</v>
+      </c>
+      <c r="DE150" t="n">
+        <v>0.3191</v>
+      </c>
+      <c r="DF150" t="n">
+        <v>126</v>
+      </c>
+      <c r="DG150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH150" t="n">
+        <v>1781529180000</v>
+      </c>
+      <c r="DI150" t="inlineStr">
+        <is>
+          <t>[2.4988, 2.4799, 2.461, 2.4422, 2.4233, 2.4044, 2.3855, 2.3666, 2.3478, 2.3289, 2.31, 2.2911, 2.2722, 2.2533, 2.2345, 2.2156, 2.1967, 2.1778, 2.1589, 2.14]</t>
+        </is>
+      </c>
+      <c r="DJ150" t="inlineStr">
+        <is>
+          <t>[2.4988, 2.4799, 2.461, 2.4422, 2.4233, 2.4044, 2.3855, 2.3666, 2.3478, 2.3289, 2.31, 2.2911, 2.2722, 2.2533, 2.2345, 2.2156, 2.1967, 2.1778, 2.1589, 2.14]</t>
+        </is>
+      </c>
+      <c r="DK150" t="inlineStr">
+        <is>
+          <t>[-2.4988, -2.4799, -2.461, -2.4422, -2.4233, -2.4044, -2.3855, -2.3666, -2.3478, -2.3289, -2.31, -2.2911, -2.2722, -2.2533, -2.2345, -2.2156, -2.1967, -2.1778, -2.1589, -2.14]</t>
+        </is>
+      </c>
+      <c r="DL150" t="inlineStr">
+        <is>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+        </is>
+      </c>
+      <c r="DM150" t="b">
+        <v>1</v>
+      </c>
+      <c r="DN150" t="inlineStr">
+        <is>
+          <t>Journal</t>
+        </is>
+      </c>
+      <c r="DO150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ150" t="inlineStr">
+        <is>
+          <t>journalAccount:59</t>
+        </is>
+      </c>
+      <c r="DR150" t="inlineStr">
+        <is>
+          <t>journalAccount:59</t>
+        </is>
+      </c>
+      <c r="DS150" t="inlineStr">
+        <is>
+          <t>Mentor · laith 3</t>
+        </is>
+      </c>
+      <c r="DT150" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="DU150" t="inlineStr"/>
+      <c r="DV150" t="inlineStr"/>
+      <c r="DW150" t="inlineStr"/>
+      <c r="DX150" t="inlineStr">
+        <is>
+          <t>Fibonacci Confluence Swing</t>
+        </is>
+      </c>
+      <c r="DY150" t="n">
+        <v>41</v>
+      </c>
+      <c r="DZ150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EA150" t="inlineStr">
+        <is>
+          <t>["Outcome review: Yes", "Win"]</t>
+        </is>
+      </c>
+      <c r="EB150" t="inlineStr">
+        <is>
+          <t>Imported from mentor (laith 3.xlsx, id=54528)</t>
+        </is>
+      </c>
+      <c r="EC150" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="EE150" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="EF150" t="inlineStr">
+        <is>
+          <t>according-to-plan</t>
+        </is>
+      </c>
+      <c r="EG150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EH150" t="inlineStr">
+        <is>
+          <t>mentor_import_live</t>
+        </is>
+      </c>
+      <c r="EI150" t="inlineStr">
+        <is>
+          <t>prop_live_journal</t>
+        </is>
+      </c>
+      <c r="EJ150" t="inlineStr">
         <is>
           <t>Prop</t>
         </is>

--- a/mentor data/laith 3-talaria-adapted.xlsx
+++ b/mentor data/laith 3-talaria-adapted.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54336, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780214837689_dadcbb47252bc38add089de0849ef168.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215631805_a9a39dd79aba692729afc21d50b18a23.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2263.145, "sourceLowPrice": 2251.889}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54336, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780214837689_dadcbb47252bc38add089de0849ef168.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215631805_a9a39dd79aba692729afc21d50b18a23.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2263.145, "sourceLowPrice": 2251.889, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>37</v>
       </c>
       <c r="BL2" t="n">
-        <v>1782575759964</v>
+        <v>1782579163428</v>
       </c>
       <c r="BM2" t="n">
         <v>2258.541</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54337, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187599379_b873e8fcf6c42f2aaa85a89a0b7f30d3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187756133_ff4438c3f6bf2bb967f72e5a4fbf2c00.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07917, "sourceLowPrice": 1.07688}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54337, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187599379_b873e8fcf6c42f2aaa85a89a0b7f30d3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781187756133_ff4438c3f6bf2bb967f72e5a4fbf2c00.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07917, "sourceLowPrice": 1.07688, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>37</v>
       </c>
       <c r="BL3" t="n">
-        <v>1782575759965</v>
+        <v>1782579163428</v>
       </c>
       <c r="BM3" t="n">
         <v>1.07938</v>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54338, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215784438_3983a074813184da3081dcc7bd9877d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215856014_76a86be691f407e4df6155fa80aa39e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2258.45, "sourceLowPrice": 2250.21}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54338, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215784438_3983a074813184da3081dcc7bd9877d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780215856014_76a86be691f407e4df6155fa80aa39e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2258.45, "sourceLowPrice": 2250.21, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2407,7 +2407,7 @@
         <v>37</v>
       </c>
       <c r="BL4" t="n">
-        <v>1782575759965</v>
+        <v>1782579163428</v>
       </c>
       <c r="BM4" t="n">
         <v>2255.359</v>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2255.359, "new": 2254.873, "at": 1711947960000}]</t>
         </is>
       </c>
       <c r="DP4" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54339, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188056673_448a100c575e03238ea4033bba7e9106.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188142564_aae8b084cb5dbcce5ffcb945b5fa7b74.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07813, "sourceLowPrice": 1.07596}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54339, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188056673_448a100c575e03238ea4033bba7e9106.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188142564_aae8b084cb5dbcce5ffcb945b5fa7b74.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07813, "sourceLowPrice": 1.07596, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2931,7 +2931,7 @@
         <v>37</v>
       </c>
       <c r="BL5" t="n">
-        <v>1782575759966</v>
+        <v>1782579163428</v>
       </c>
       <c r="BM5" t="n">
         <v>1.07846</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54340, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216391858_5e87f92f328437534c0dc625b9b534c3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216617040_ab38abf9510f6e548b9c32831d4ac1c6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2276.937, "sourceLowPrice": 2233.82}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54340, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216391858_5e87f92f328437534c0dc625b9b534c3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780216617040_ab38abf9510f6e548b9c32831d4ac1c6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2276.937, "sourceLowPrice": 2233.82, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -3455,7 +3455,7 @@
         <v>37</v>
       </c>
       <c r="BL6" t="n">
-        <v>1782575759967</v>
+        <v>1782579163429</v>
       </c>
       <c r="BM6" t="n">
         <v>2227.494</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54341, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188508620_e89ed1e80d22f649985df63ca84f5fed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188582602_14d62524d5aeb9b028492ac247879a1a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07264}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54341, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188508620_e89ed1e80d22f649985df63ca84f5fed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781188582602_14d62524d5aeb9b028492ac247879a1a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07264, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3979,7 +3979,7 @@
         <v>37</v>
       </c>
       <c r="BL7" t="n">
-        <v>1782575759967</v>
+        <v>1782579163429</v>
       </c>
       <c r="BM7" t="n">
         <v>1.0744</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54342, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512298411_060252c1f3dc083d0e285f060c888682.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512311937_c559503a7c4f8c46aa9bc24f7176f8cf.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2275.411, "sourceLowPrice": 2256.03}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54342, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512298411_060252c1f3dc083d0e285f060c888682.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780512311937_c559503a7c4f8c46aa9bc24f7176f8cf.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2275.411, "sourceLowPrice": 2256.03, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4503,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="BL8" t="n">
-        <v>1782575759968</v>
+        <v>1782579163429</v>
       </c>
       <c r="BM8" t="n">
         <v>2252.439</v>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54343, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222070329_b7dae3f6df7b2979bc221fc62537c2ef.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222214466_7a5d4e60a6ffd1f975ce2cde7f35024d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2290.027, "sourceLowPrice": 2254.22}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54343, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222070329_b7dae3f6df7b2979bc221fc62537c2ef.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780222214466_7a5d4e60a6ffd1f975ce2cde7f35024d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2290.027, "sourceLowPrice": 2254.22, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -5027,7 +5027,7 @@
         <v>37</v>
       </c>
       <c r="BL9" t="n">
-        <v>1782575759968</v>
+        <v>1782579163429</v>
       </c>
       <c r="BM9" t="n">
         <v>2249.866</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54344, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597397119_c30cb4d3d55075052763814cc9cfdcc2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597409048_a22cd62af0284a5fd91e652324dbd238.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2274.55, "sourceLowPrice": 2265.51}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54344, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597397119_c30cb4d3d55075052763814cc9cfdcc2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597409048_a22cd62af0284a5fd91e652324dbd238.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2274.55, "sourceLowPrice": 2265.51, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -5551,7 +5551,7 @@
         <v>37</v>
       </c>
       <c r="BL10" t="n">
-        <v>1782575759968</v>
+        <v>1782579163430</v>
       </c>
       <c r="BM10" t="n">
         <v>2267.89</v>
@@ -5732,11 +5732,11 @@
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="EC10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED10" t="n">
         <v>2024</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54345, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189148218_8386f58ae538d92f591d49f8b2a9669a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189234568_2e8ecdc821200259b3a301449f275013.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08015, "sourceLowPrice": 1.0773}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54345, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189148218_8386f58ae538d92f591d49f8b2a9669a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189234568_2e8ecdc821200259b3a301449f275013.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08015, "sourceLowPrice": 1.0773, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6075,7 +6075,7 @@
         <v>37</v>
       </c>
       <c r="BL11" t="n">
-        <v>1782575759969</v>
+        <v>1782579163430</v>
       </c>
       <c r="BM11" t="n">
         <v>1.0788</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54346, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223471552_ea5b3c4daa45de163941d2e923418632.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223916207_89c71be4de0025b4b0663640a081f90a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2304.99, "sourceLowPrice": 2280.79}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54346, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223471552_ea5b3c4daa45de163941d2e923418632.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780223916207_89c71be4de0025b4b0663640a081f90a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2304.99, "sourceLowPrice": 2280.79, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -6599,7 +6599,7 @@
         <v>37</v>
       </c>
       <c r="BL12" t="n">
-        <v>1782575759970</v>
+        <v>1782579163430</v>
       </c>
       <c r="BM12" t="n">
         <v>2273.238</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="BP12" t="n">
         <v>2</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54347, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232061584_b58d9305d377b61c85645d1bbeef2d88.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232164427_538eb12558140b5c26863d9d8a9f3e07.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2297.45, "sourceLowPrice": 2293.035}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54347, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232061584_b58d9305d377b61c85645d1bbeef2d88.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780232164427_538eb12558140b5c26863d9d8a9f3e07.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2297.45, "sourceLowPrice": 2293.035, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -7123,7 +7123,7 @@
         <v>37</v>
       </c>
       <c r="BL13" t="n">
-        <v>1782575759970</v>
+        <v>1782579163431</v>
       </c>
       <c r="BM13" t="n">
         <v>2294.065</v>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54348, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189555937_3254a1775090dcd0bd1a1724f0ee83b6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189616066_72d73c9c963777d903869b76ec2d6df7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08656, "sourceLowPrice": 1.08509}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54348, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189555937_3254a1775090dcd0bd1a1724f0ee83b6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781189616066_72d73c9c963777d903869b76ec2d6df7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08656, "sourceLowPrice": 1.08509, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -7647,7 +7647,7 @@
         <v>37</v>
       </c>
       <c r="BL14" t="n">
-        <v>1782575759970</v>
+        <v>1782579163431</v>
       </c>
       <c r="BM14" t="n">
         <v>1.08604</v>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54349, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233182736_aef339eb5a70fc2de99b7c935fbb8960.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233324509_4f2def2ba4749f41f441e7f623fe0dfc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2284.776}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54349, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233182736_aef339eb5a70fc2de99b7c935fbb8960.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780233324509_4f2def2ba4749f41f441e7f623fe0dfc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2284.776, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>37</v>
       </c>
       <c r="BL15" t="n">
-        <v>1782575759971</v>
+        <v>1782579163431</v>
       </c>
       <c r="BM15" t="n">
         <v>2281.682</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54350, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780580933913_38d2b56a5e34032f16fd75b5796b4f4b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581006293_dc78a12d872cd90b623ef9d1ab023e84.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2290.88}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54350, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780580933913_38d2b56a5e34032f16fd75b5796b4f4b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581006293_dc78a12d872cd90b623ef9d1ab023e84.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2299.52, "sourceLowPrice": 2290.88, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -8695,7 +8695,7 @@
         <v>37</v>
       </c>
       <c r="BL16" t="n">
-        <v>1782575759972</v>
+        <v>1782579163431</v>
       </c>
       <c r="BM16" t="n">
         <v>2288.195</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54351, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304127248_b1419143e3c987dfd7aec4bd6523ac69.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304248886_ae0b55e7c9057366870c357893cf1427.png", "notes": "small smt (entry)", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2295.045, "sourceLowPrice": 2293.035}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54351, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304127248_b1419143e3c987dfd7aec4bd6523ac69.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780304248886_ae0b55e7c9057366870c357893cf1427.png", "notes": "small smt (entry)", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2295.045, "sourceLowPrice": 2293.035, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -9219,7 +9219,7 @@
         <v>37</v>
       </c>
       <c r="BL17" t="n">
-        <v>1782575759972</v>
+        <v>1782579163432</v>
       </c>
       <c r="BM17" t="n">
         <v>2291.604</v>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54352, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952356811_703f322d8fa6f5e4cb90e5418c3cf190.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952418281_8f40d5331d136e2abda911b922109ee3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18349.908, "sourceLowPrice": 18286.354}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54352, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952356811_703f322d8fa6f5e4cb90e5418c3cf190.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952418281_8f40d5331d136e2abda911b922109ee3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18349.908, "sourceLowPrice": 18286.354, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -9743,7 +9743,7 @@
         <v>37</v>
       </c>
       <c r="BL18" t="n">
-        <v>1782575759973</v>
+        <v>1782579163432</v>
       </c>
       <c r="BM18" t="n">
         <v>18275.021</v>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54353, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200857906_aea70e79daf33522ba08c8e954aaafbd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200935735_c41282483de9220a41581f2c0908bd96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08464, "sourceLowPrice": 1.08362}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54353, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200857906_aea70e79daf33522ba08c8e954aaafbd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781200935735_c41282483de9220a41581f2c0908bd96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08464, "sourceLowPrice": 1.08362, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10267,7 +10267,7 @@
         <v>37</v>
       </c>
       <c r="BL19" t="n">
-        <v>1782575759974</v>
+        <v>1782579163432</v>
       </c>
       <c r="BM19" t="n">
         <v>1.08436</v>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54354, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780309638914_ac2e31c72d3f5cb986eb15da78225c7e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578150837_befeaacd72c27452901de4b30361f190.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2296.27, "sourceLowPrice": 2280.43}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54354, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780309638914_ac2e31c72d3f5cb986eb15da78225c7e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578150837_befeaacd72c27452901de4b30361f190.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2296.27, "sourceLowPrice": 2280.43, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>37</v>
       </c>
       <c r="BL20" t="n">
-        <v>1782575759974</v>
+        <v>1782579163432</v>
       </c>
       <c r="BM20" t="n">
         <v>2283.915</v>
@@ -10972,11 +10972,11 @@
       </c>
       <c r="DL20" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="inlineStr">
         <is>
@@ -11050,12 +11050,12 @@
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 31, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-04-05T08:31:00.000Z"}, {"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 31, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-04-05T08:31:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH20" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54356, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952850659_76b40ca6ae337217380de3b1dbb6cb42.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953341925_174222affd81bd74f3237a5c9925a546.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5224.327, "sourceLowPrice": 5156.077}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54356, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780952850659_76b40ca6ae337217380de3b1dbb6cb42.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953341925_174222affd81bd74f3237a5c9925a546.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5224.327, "sourceLowPrice": 5156.077, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -11315,7 +11315,7 @@
         <v>37</v>
       </c>
       <c r="BL21" t="n">
-        <v>1782575759975</v>
+        <v>1782579163432</v>
       </c>
       <c r="BM21" t="n">
         <v>5150.273</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54357, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578359260_42ad39ab25230e308cd195d91e82e07f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780310988059_57088f2016a876bb381800417d3db597.png", "notes": "T", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.162, "sourceLowPrice": 2284.575}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54357, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578359260_42ad39ab25230e308cd195d91e82e07f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780310988059_57088f2016a876bb381800417d3db597.png", "notes": "T", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2309.162, "sourceLowPrice": 2284.575, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -11839,7 +11839,7 @@
         <v>37</v>
       </c>
       <c r="BL22" t="n">
-        <v>1782575759975</v>
+        <v>1782579163433</v>
       </c>
       <c r="BM22" t="n">
         <v>2279.434</v>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54358, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581279902_21fba9078090cf8d3c7923e985d6f4f8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581413420_9aa89f6c989a5df372958d96e9d7e11f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.743, "sourceLowPrice": 2292.04}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54358, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581279902_21fba9078090cf8d3c7923e985d6f4f8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581413420_9aa89f6c989a5df372958d96e9d7e11f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.743, "sourceLowPrice": 2292.04, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>37</v>
       </c>
       <c r="BL23" t="n">
-        <v>1782575759976</v>
+        <v>1782579163433</v>
       </c>
       <c r="BM23" t="n">
         <v>2286.615</v>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54359, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953441461_82d2852988ea1ea79669518c3c24a138.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953521457_02d25584d8efa212b6a43629a1f6f438.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5209.528, "sourceLowPrice": 5168.689}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54359, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953441461_82d2852988ea1ea79669518c3c24a138.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953521457_02d25584d8efa212b6a43629a1f6f438.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5209.528, "sourceLowPrice": 5168.689, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -12887,7 +12887,7 @@
         <v>37</v>
       </c>
       <c r="BL24" t="n">
-        <v>1782575759976</v>
+        <v>1782579163433</v>
       </c>
       <c r="BM24" t="n">
         <v>5166.201</v>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="BO24" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="BP24" t="n">
         <v>6</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54360, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953640796_a975d89fb3da0cd76554693d7fbbfccb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953691339_d1bf2089c2c5b544f33520cedb5b2d24.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5210.34, "sourceLowPrice": 5181.824}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54360, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953640796_a975d89fb3da0cd76554693d7fbbfccb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780953691339_d1bf2089c2c5b544f33520cedb5b2d24.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5210.34, "sourceLowPrice": 5181.824, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -13411,7 +13411,7 @@
         <v>37</v>
       </c>
       <c r="BL25" t="n">
-        <v>1782575759976</v>
+        <v>1782579163433</v>
       </c>
       <c r="BM25" t="n">
         <v>5175.666</v>
@@ -13592,11 +13592,11 @@
       </c>
       <c r="DL25" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN25" t="inlineStr">
         <is>
@@ -13670,12 +13670,12 @@
       </c>
       <c r="EF25" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "early_exit", "label": "Early Exit", "source": "auto", "state": "detected", "cost_R": 2.3, "cost_$": 115, "evidence": "Closed before the planned target without a rule-based trigger.", "detected_at": "2024-04-05T10:57:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54361, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201634282_e9c4a9ee9c43b78b438fcf7fc95dcdc7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201824752_d787e06430318250bd53ad5e1c3c0dde.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08379, "sourceLowPrice": 1.08209}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54361, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201634282_e9c4a9ee9c43b78b438fcf7fc95dcdc7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781201824752_d787e06430318250bd53ad5e1c3c0dde.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.08379, "sourceLowPrice": 1.08209, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -13935,7 +13935,7 @@
         <v>37</v>
       </c>
       <c r="BL26" t="n">
-        <v>1782575759977</v>
+        <v>1782579163433</v>
       </c>
       <c r="BM26" t="n">
         <v>1.08397</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54362, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578571747_36d3cb7663754c1635a8856256c5cb95.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578680127_cb12c4e66b73628d4ae8acbe9b9a2e88.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2334.27}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54362, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578571747_36d3cb7663754c1635a8856256c5cb95.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780578680127_cb12c4e66b73628d4ae8acbe9b9a2e88.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2334.27, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -14459,7 +14459,7 @@
         <v>37</v>
       </c>
       <c r="BL27" t="n">
-        <v>1782575759978</v>
+        <v>1782579163434</v>
       </c>
       <c r="BM27" t="n">
         <v>2332.393</v>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54364, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581790944_dcd909716c23339e3d6dea636ace482b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581920247_201982bca0d602d69c07bc0a0c2c35fc.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2336.32}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54364, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581790944_dcd909716c23339e3d6dea636ace482b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780581920247_201982bca0d602d69c07bc0a0c2c35fc.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2336.32, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -14983,7 +14983,7 @@
         <v>37</v>
       </c>
       <c r="BL28" t="n">
-        <v>1782575759978</v>
+        <v>1782579163434</v>
       </c>
       <c r="BM28" t="n">
         <v>2334.715</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54365, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582022486_55870726c5b5304fb0bef711e1598c74.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582078461_6a1bdafdfef1ac03cd8ecb1f65b9306c.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2338.59}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54365, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582022486_55870726c5b5304fb0bef711e1598c74.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780582078461_6a1bdafdfef1ac03cd8ecb1f65b9306c.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2343.64, "sourceLowPrice": 2338.59, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -15507,7 +15507,7 @@
         <v>37</v>
       </c>
       <c r="BL29" t="n">
-        <v>1782575759979</v>
+        <v>1782579163434</v>
       </c>
       <c r="BM29" t="n">
         <v>2335.82</v>
@@ -15688,11 +15688,11 @@
       </c>
       <c r="DL29" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN29" t="inlineStr">
         <is>
@@ -15766,12 +15766,12 @@
       </c>
       <c r="EF29" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.24, "cost_$": 35, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-04-08T06:33:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54368, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589525290_f066e0de38aade84091fe91b724d0ce0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589574499_3061ea78ecb86c34650bb6fea54556b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.68, "sourceLowPrice": 2347.36}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54368, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589525290_f066e0de38aade84091fe91b724d0ce0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780589574499_3061ea78ecb86c34650bb6fea54556b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2357.68, "sourceLowPrice": 2347.36, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -16031,7 +16031,7 @@
         <v>37</v>
       </c>
       <c r="BL30" t="n">
-        <v>1782575759979</v>
+        <v>1782579163434</v>
       </c>
       <c r="BM30" t="n">
         <v>2344.8</v>
@@ -16212,11 +16212,11 @@
       </c>
       <c r="DL30" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN30" t="inlineStr">
         <is>
@@ -16290,12 +16290,12 @@
       </c>
       <c r="EF30" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 58, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2024-04-09T09:07:00.000Z"}, {"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 58, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-04-09T09:07:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54369, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319288614_eae04019ac0871ad32c227dbfda6ccb0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319419799_c321f26bf3e5869b78fffccf1680e494.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2350.81, "sourceLowPrice": 2333.81}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54369, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319288614_eae04019ac0871ad32c227dbfda6ccb0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319419799_c321f26bf3e5869b78fffccf1680e494.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2350.81, "sourceLowPrice": 2333.81, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -16555,7 +16555,7 @@
         <v>37</v>
       </c>
       <c r="BL31" t="n">
-        <v>1782575759980</v>
+        <v>1782579163434</v>
       </c>
       <c r="BM31" t="n">
         <v>2343.983</v>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54370, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267051732_fb71fcb1a5d548bddb4717127ec86683.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267134800_6f8a0d38c808933c1ded8f21d03fddca.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0865, "sourceLowPrice": 1.08376}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54370, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267051732_fb71fcb1a5d548bddb4717127ec86683.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267134800_6f8a0d38c808933c1ded8f21d03fddca.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0865, "sourceLowPrice": 1.08376, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -17079,7 +17079,7 @@
         <v>37</v>
       </c>
       <c r="BL32" t="n">
-        <v>1782575759981</v>
+        <v>1782579163435</v>
       </c>
       <c r="BM32" t="n">
         <v>1.08676</v>
@@ -17260,11 +17260,11 @@
       </c>
       <c r="DL32" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN32" t="inlineStr">
         <is>
@@ -17338,12 +17338,12 @@
       </c>
       <c r="EF32" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "early_exit", "label": "Early Exit", "source": "auto", "state": "detected", "cost_R": 2.5, "cost_$": 125, "evidence": "Closed before the planned target without a rule-based trigger.", "detected_at": "2024-04-10T08:35:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH32" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54371, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319745725_3730419349b0045a2192a5272858e91f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2325.75}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54371, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780319745725_3730419349b0045a2192a5272858e91f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2325.75, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -17603,7 +17603,7 @@
         <v>37</v>
       </c>
       <c r="BL33" t="n">
-        <v>1782575759981</v>
+        <v>1782579163435</v>
       </c>
       <c r="BM33" t="n">
         <v>2318.414</v>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54372, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954611652_bcd3e4125ec981c2ded35719d37afe59.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954713560_2e27dd67171dc45971edbfd0e165706b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18048.519, "sourceLowPrice": 17966.886}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54372, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954611652_bcd3e4125ec981c2ded35719d37afe59.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780954713560_2e27dd67171dc45971edbfd0e165706b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18048.519, "sourceLowPrice": 17966.886, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -18127,7 +18127,7 @@
         <v>37</v>
       </c>
       <c r="BL34" t="n">
-        <v>1782575759982</v>
+        <v>1782579163435</v>
       </c>
       <c r="BM34" t="n">
         <v>18023.946</v>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54373, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590264461_8ecec747d0c6cad9187e309bbea368b0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2333.709}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54373, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590264461_8ecec747d0c6cad9187e309bbea368b0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590091102_37fdeca168c2be183f5e0ea2fe6e9240.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2352.47, "sourceLowPrice": 2333.709, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -18651,7 +18651,7 @@
         <v>37</v>
       </c>
       <c r="BL35" t="n">
-        <v>1782575759982</v>
+        <v>1782579163435</v>
       </c>
       <c r="BM35" t="n">
         <v>2339.965</v>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54374, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320728308_5c7ff7b32f02827cdcb24cda6e49d519.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320821403_bb1586d62d9d3e1f545d3c01bf1f81b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.83, "sourceLowPrice": 2325.91}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54374, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320728308_5c7ff7b32f02827cdcb24cda6e49d519.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780320821403_bb1586d62d9d3e1f545d3c01bf1f81b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2341.83, "sourceLowPrice": 2325.91, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -19175,7 +19175,7 @@
         <v>37</v>
       </c>
       <c r="BL36" t="n">
-        <v>1782575759983</v>
+        <v>1782579163435</v>
       </c>
       <c r="BM36" t="n">
         <v>2329.145</v>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54375, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267426711_d68e22288378664d1fe52fc460250401.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267498180_a84b21be21b42d95df0bd9c646b8241e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07444, "sourceLowPrice": 1.0715}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54375, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267426711_d68e22288378664d1fe52fc460250401.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267498180_a84b21be21b42d95df0bd9c646b8241e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07444, "sourceLowPrice": 1.0715, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -19699,7 +19699,7 @@
         <v>37</v>
       </c>
       <c r="BL37" t="n">
-        <v>1782575759984</v>
+        <v>1782579163436</v>
       </c>
       <c r="BM37" t="n">
         <v>1.07509</v>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54376, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780321321815_fa7926ee732c0828557974939b4356af.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590991194_5305bb220f87935173ed6daf99d2ce80.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.71, "sourceLowPrice": 2328.43}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54376, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780321321815_fa7926ee732c0828557974939b4356af.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590991194_5305bb220f87935173ed6daf99d2ce80.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.71, "sourceLowPrice": 2328.43, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -20223,7 +20223,7 @@
         <v>37</v>
       </c>
       <c r="BL38" t="n">
-        <v>1782575759984</v>
+        <v>1782579163436</v>
       </c>
       <c r="BM38" t="n">
         <v>2324.744</v>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54377, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590762975_3102d6bce697c8b83c967d5065bbdad2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590864856_21b99a8638fe3b118c2a5c1abc851f87.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.53, "sourceLowPrice": 2332.61}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54377, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590762975_3102d6bce697c8b83c967d5065bbdad2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780590864856_21b99a8638fe3b118c2a5c1abc851f87.png", "notes": "check", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2347.53, "sourceLowPrice": 2332.61, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -20747,7 +20747,7 @@
         <v>37</v>
       </c>
       <c r="BL39" t="n">
-        <v>1782575759985</v>
+        <v>1782579163436</v>
       </c>
       <c r="BM39" t="n">
         <v>2331.31</v>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54380, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338124221_d61fa2e41baa09a0e338b6edc9b7d22f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338307430_ac14cb004870aaa3e064a2acf187a458.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2404.463, "sourceLowPrice": 2386.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54380, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338124221_d61fa2e41baa09a0e338b6edc9b7d22f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338307430_ac14cb004870aaa3e064a2acf187a458.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2404.463, "sourceLowPrice": 2386.9, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v>37</v>
       </c>
       <c r="BL40" t="n">
-        <v>1782575759985</v>
+        <v>1782579163436</v>
       </c>
       <c r="BM40" t="n">
         <v>2383.79</v>
@@ -21452,11 +21452,11 @@
       </c>
       <c r="DL40" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN40" t="inlineStr">
         <is>
@@ -21530,12 +21530,12 @@
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "manual", "state": "confirmed", "cost_R": 2.0, "cost_$": 66, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-04-12T03:10:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54381, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591417759_7f395f3a859f6c1a679cd1aefc7dcf27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591501149_7fcdec701bdabac643789abb57e3eb9b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2399.931, "sourceLowPrice": 2391.55}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54381, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591417759_7f395f3a859f6c1a679cd1aefc7dcf27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780591501149_7fcdec701bdabac643789abb57e3eb9b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2399.931, "sourceLowPrice": 2391.55, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -21795,7 +21795,7 @@
         <v>37</v>
       </c>
       <c r="BL41" t="n">
-        <v>1782575759986</v>
+        <v>1782579163436</v>
       </c>
       <c r="BM41" t="n">
         <v>2390.235</v>
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54382, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338474113_9d83c277e7d56f7407aad0a07a7adabb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338712544_98d780d16910a003d755c4e7a35b10f0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2400.73, "sourceLowPrice": 2390.44}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54382, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338474113_9d83c277e7d56f7407aad0a07a7adabb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780338712544_98d780d16910a003d755c4e7a35b10f0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2400.73, "sourceLowPrice": 2390.44, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -22319,7 +22319,7 @@
         <v>37</v>
       </c>
       <c r="BL42" t="n">
-        <v>1782575759986</v>
+        <v>1782579163437</v>
       </c>
       <c r="BM42" t="n">
         <v>2391.883</v>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54383, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339104546_e889a3b2180090b2a9352366ae701c70.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339368388_2aa1f18a2700eda2691e07387763895a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.071, "sourceLowPrice": 2391.59}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54383, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339104546_e889a3b2180090b2a9352366ae701c70.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780339368388_2aa1f18a2700eda2691e07387763895a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2408.071, "sourceLowPrice": 2391.59, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -22843,7 +22843,7 @@
         <v>37</v>
       </c>
       <c r="BL43" t="n">
-        <v>1782575759987</v>
+        <v>1782579163437</v>
       </c>
       <c r="BM43" t="n">
         <v>2389.438</v>
@@ -23312,7 +23312,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54384, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267931057_538062c282463f33370f88570c7f5f84.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267985598_6ecf0abcb85090fb96bf94e144eb7855.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06556, "sourceLowPrice": 1.06228}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54384, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267931057_538062c282463f33370f88570c7f5f84.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781267985598_6ecf0abcb85090fb96bf94e144eb7855.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06556, "sourceLowPrice": 1.06228, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -23367,7 +23367,7 @@
         <v>37</v>
       </c>
       <c r="BL44" t="n">
-        <v>1782575759987</v>
+        <v>1782579163437</v>
       </c>
       <c r="BM44" t="n">
         <v>1.06604</v>
@@ -23836,7 +23836,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54389, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268357399_61876d40ecb889f51c6b37261b9e65c9.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268554956_e74684e0075c44f26dc4625496b368ef.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06653, "sourceLowPrice": 1.0631}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54389, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268357399_61876d40ecb889f51c6b37261b9e65c9.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268554956_e74684e0075c44f26dc4625496b368ef.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06653, "sourceLowPrice": 1.0631, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -23891,7 +23891,7 @@
         <v>37</v>
       </c>
       <c r="BL45" t="n">
-        <v>1782575759988</v>
+        <v>1782579163437</v>
       </c>
       <c r="BM45" t="n">
         <v>1.0666</v>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54390, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010234777_9225504a87a97d760fa3466ce407a207.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010307215_1c13c41407edec90ebf1f1b636f6e7f5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5170.132, "sourceLowPrice": 5162.614}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54390, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010234777_9225504a87a97d760fa3466ce407a207.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010307215_1c13c41407edec90ebf1f1b636f6e7f5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5170.132, "sourceLowPrice": 5162.614, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
@@ -24415,7 +24415,7 @@
         <v>37</v>
       </c>
       <c r="BL46" t="n">
-        <v>1782575759988</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM46" t="n">
         <v>5169.481</v>
@@ -24426,7 +24426,7 @@
         </is>
       </c>
       <c r="BO46" t="n">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="BP46" t="n">
         <v>1</v>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54391, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010504893_faf3b60862176067de33a46fa3e251b3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010620073_dcc5b7a295e0efc967e909758efb4304.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18177.354, "sourceLowPrice": 18066.682}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54391, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010504893_faf3b60862176067de33a46fa3e251b3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010620073_dcc5b7a295e0efc967e909758efb4304.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18177.354, "sourceLowPrice": 18066.682, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
@@ -24939,7 +24939,7 @@
         <v>37</v>
       </c>
       <c r="BL47" t="n">
-        <v>1782575759989</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM47" t="n">
         <v>18188.686</v>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54392, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010841873_eda18716561afc5dfddc0d7caccf2f14.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010990277_2f2bd4f7a881c2433f498feeae5be5b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18040.386, "sourceLowPrice": 17987.12}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54392, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010841873_eda18716561afc5dfddc0d7caccf2f14.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781010990277_2f2bd4f7a881c2433f498feeae5be5b5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18040.386, "sourceLowPrice": 17987.12, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -25463,7 +25463,7 @@
         <v>37</v>
       </c>
       <c r="BL48" t="n">
-        <v>1782575759989</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM48" t="n">
         <v>18077.865</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54393, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011137421_8cf0d420b280475328a584276a1bc137.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011150440_c29a79485c653b6e3c029d88ef8d65c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18053.964, "sourceLowPrice": 17987.12}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54393, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011137421_8cf0d420b280475328a584276a1bc137.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781011150440_c29a79485c653b6e3c029d88ef8d65c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 18053.964, "sourceLowPrice": 17987.12, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
@@ -25987,7 +25987,7 @@
         <v>37</v>
       </c>
       <c r="BL49" t="n">
-        <v>1782575759990</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM49" t="n">
         <v>18026.132</v>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54394, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268891505_6aebb65ffaac9757d774d1cc767686ee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268946963_f35cfb5e413ebc5e7e2d0ca3f28a3d5d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06229, "sourceLowPrice": 1.06024}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54394, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268891505_6aebb65ffaac9757d774d1cc767686ee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781268946963_f35cfb5e413ebc5e7e2d0ca3f28a3d5d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06229, "sourceLowPrice": 1.06024, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
@@ -26511,7 +26511,7 @@
         <v>37</v>
       </c>
       <c r="BL50" t="n">
-        <v>1782575759990</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM50" t="n">
         <v>1.06216</v>
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54395, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381490958_209d973e2fdd4bbd0d1599bf1aa32c80.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381587541_b0b4aac638fe0e056d080296d6807248.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2375.31, "sourceLowPrice": 2363.06}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54395, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381490958_209d973e2fdd4bbd0d1599bf1aa32c80.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780381587541_b0b4aac638fe0e056d080296d6807248.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2375.31, "sourceLowPrice": 2363.06, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -27035,7 +27035,7 @@
         <v>37</v>
       </c>
       <c r="BL51" t="n">
-        <v>1782575759991</v>
+        <v>1782579163438</v>
       </c>
       <c r="BM51" t="n">
         <v>2367.715</v>
@@ -27504,7 +27504,7 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54396, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024250905_75f5048276946756f26081b7fce75954.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024319121_483fcc9eb15b7df7c44c8e3f97b359d8.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17746.643, "sourceLowPrice": 17702.498}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54396, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024250905_75f5048276946756f26081b7fce75954.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781024319121_483fcc9eb15b7df7c44c8e3f97b359d8.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17746.643, "sourceLowPrice": 17702.498, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -27559,7 +27559,7 @@
         <v>37</v>
       </c>
       <c r="BL52" t="n">
-        <v>1782575759991</v>
+        <v>1782579163439</v>
       </c>
       <c r="BM52" t="n">
         <v>17726.642</v>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54402, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595139798_ff7f5995d5acee2bfff69fbe25341b63.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595310612_6f903b16326071d0e43f454f87e549d4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2394.38, "sourceLowPrice": 2378.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54402, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595139798_ff7f5995d5acee2bfff69fbe25341b63.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595310612_6f903b16326071d0e43f454f87e549d4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2394.38, "sourceLowPrice": 2378.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
@@ -28083,7 +28083,7 @@
         <v>37</v>
       </c>
       <c r="BL53" t="n">
-        <v>1782575759991</v>
+        <v>1782579163439</v>
       </c>
       <c r="BM53" t="n">
         <v>2371.755</v>
@@ -28552,7 +28552,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54403, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780389742774_ec6b57838fcd0d65b4a1f6b01f08d62e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390228080_2a70338c8625db934448dfcbfa1c7b09.png", "notes": "u have to look at xag maybe there is a add(test)\n\nmorelossading", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2390.41, "sourceLowPrice": 2384.59}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54403, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780389742774_ec6b57838fcd0d65b4a1f6b01f08d62e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390228080_2a70338c8625db934448dfcbfa1c7b09.png", "notes": "u have to look at xag maybe there is a add(test)\n\nmorelossading", "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2390.41, "sourceLowPrice": 2384.59, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -28607,7 +28607,7 @@
         <v>37</v>
       </c>
       <c r="BL54" t="n">
-        <v>1782575759992</v>
+        <v>1782579163439</v>
       </c>
       <c r="BM54" t="n">
         <v>2384.082</v>
@@ -28801,7 +28801,7 @@
       </c>
       <c r="DO54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2384.082, "new": 2383.535, "at": 1713337080000}]</t>
         </is>
       </c>
       <c r="DP54" t="n">
@@ -29077,7 +29077,7 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54404, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269593392_30df0756429eda87952ec8ac301a2c1b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269657332_f84740c78b4af74cd126d365773455b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06529, "sourceLowPrice": 1.06316}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54404, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269593392_30df0756429eda87952ec8ac301a2c1b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269657332_f84740c78b4af74cd126d365773455b3.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06529, "sourceLowPrice": 1.06316, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
@@ -29132,7 +29132,7 @@
         <v>37</v>
       </c>
       <c r="BL55" t="n">
-        <v>1782575759994</v>
+        <v>1782579163440</v>
       </c>
       <c r="BM55" t="n">
         <v>1.06502</v>
@@ -29313,11 +29313,11 @@
       </c>
       <c r="DL55" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN55" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
       </c>
       <c r="EF55" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG55" t="inlineStr">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54405, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390413043_8d5f6c2991cb08d9a633a0c7043a7362.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390479011_a43c0a023eeb6b07bdfea338ffc57068.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2386.21, "sourceLowPrice": 2383.15}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54405, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390413043_8d5f6c2991cb08d9a633a0c7043a7362.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390479011_a43c0a023eeb6b07bdfea338ffc57068.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2386.21, "sourceLowPrice": 2383.15, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
@@ -29656,7 +29656,7 @@
         <v>37</v>
       </c>
       <c r="BL56" t="n">
-        <v>1782575759994</v>
+        <v>1782579163440</v>
       </c>
       <c r="BM56" t="n">
         <v>2383.41</v>
@@ -29850,7 +29850,7 @@
       </c>
       <c r="DO56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2383.41, "new": 2383.104, "at": 1713342060000}]</t>
         </is>
       </c>
       <c r="DP56" t="n">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54406, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390697068_a6aba69394a8022b793614132c3dd1bb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596004419_5e766d5cb3ef169b7789ede0e739cb1f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2382.99}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54406, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780390697068_a6aba69394a8022b793614132c3dd1bb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596004419_5e766d5cb3ef169b7789ede0e739cb1f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2382.99, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -30180,7 +30180,7 @@
         <v>37</v>
       </c>
       <c r="BL57" t="n">
-        <v>1782575759995</v>
+        <v>1782579163440</v>
       </c>
       <c r="BM57" t="n">
         <v>2377.353</v>
@@ -30649,7 +30649,7 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54407, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595652278_719d5357aceed6d9a634d5951164c776.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595929387_d9a3494f27f529ea6c9ddb89c413b834.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2385.45}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54407, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595652278_719d5357aceed6d9a634d5951164c776.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780595929387_d9a3494f27f529ea6c9ddb89c413b834.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2385.45, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
@@ -30704,7 +30704,7 @@
         <v>37</v>
       </c>
       <c r="BL58" t="n">
-        <v>1782575759996</v>
+        <v>1782579163440</v>
       </c>
       <c r="BM58" t="n">
         <v>2384.91</v>
@@ -31173,7 +31173,7 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54408, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596175887_f528b35e645890efc4685722435e5e82.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596269061_9990ab4e8c6b3a0ae9a1577a07bcd87a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2386.19}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54408, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596175887_f528b35e645890efc4685722435e5e82.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596269061_9990ab4e8c6b3a0ae9a1577a07bcd87a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2395.64, "sourceLowPrice": 2386.19, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -31228,7 +31228,7 @@
         <v>37</v>
       </c>
       <c r="BL59" t="n">
-        <v>1782575759996</v>
+        <v>1782579163440</v>
       </c>
       <c r="BM59" t="n">
         <v>2386.02</v>
@@ -31697,7 +31697,7 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54410, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780392162560_35a16921edfb8c26cf6241d2e0b208aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596721094_721488dbd9c11944d78625cf41a4489e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.095}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54410, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780392162560_35a16921edfb8c26cf6241d2e0b208aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596721094_721488dbd9c11944d78625cf41a4489e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.095, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
@@ -31752,7 +31752,7 @@
         <v>37</v>
       </c>
       <c r="BL60" t="n">
-        <v>1782575759996</v>
+        <v>1782579163441</v>
       </c>
       <c r="BM60" t="n">
         <v>2374.009</v>
@@ -32221,7 +32221,7 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54411, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596564193_331854573e6172b2cd18b757187b2550.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596650921_3cd5b8fbf645dad05d68659f71e15b9f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.29}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54411, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596564193_331854573e6172b2cd18b757187b2550.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780596650921_3cd5b8fbf645dad05d68659f71e15b9f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2380.87, "sourceLowPrice": 2377.29, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
@@ -32276,7 +32276,7 @@
         <v>37</v>
       </c>
       <c r="BL61" t="n">
-        <v>1782575759997</v>
+        <v>1782579163441</v>
       </c>
       <c r="BM61" t="n">
         <v>2377.7</v>
@@ -32745,7 +32745,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54412, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269864242_9a11874377d2f800f00c8fb6cf0c68e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269927741_5cac49b0e7f70b8482c8b77d4e70fb53.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06797, "sourceLowPrice": 1.06496}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54412, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269864242_9a11874377d2f800f00c8fb6cf0c68e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781269927741_5cac49b0e7f70b8482c8b77d4e70fb53.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06797, "sourceLowPrice": 1.06496, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -32800,7 +32800,7 @@
         <v>37</v>
       </c>
       <c r="BL62" t="n">
-        <v>1782575759997</v>
+        <v>1782579163441</v>
       </c>
       <c r="BM62" t="n">
         <v>1.06801</v>
@@ -33269,7 +33269,7 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54413, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026834280_a20e85d8c00c40de0fb411e57a5a27ea.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026942673_18b9d1c5fc559062f1d5d248450a22b6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17559.787, "sourceLowPrice": 17501.462}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54413, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026834280_a20e85d8c00c40de0fb411e57a5a27ea.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781026942673_18b9d1c5fc559062f1d5d248450a22b6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17559.787, "sourceLowPrice": 17501.462, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -33324,7 +33324,7 @@
         <v>37</v>
       </c>
       <c r="BL63" t="n">
-        <v>1782575759998</v>
+        <v>1782579163441</v>
       </c>
       <c r="BM63" t="n">
         <v>17569.399</v>
@@ -33793,7 +33793,7 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54414, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393461953_5280432bc7ab04977c1644c3f8bbd1f0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393771935_41e7d6369a93b829dd3e4308ec8b03d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2392.86, "sourceLowPrice": 2380.77}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54414, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393461953_5280432bc7ab04977c1644c3f8bbd1f0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780393771935_41e7d6369a93b829dd3e4308ec8b03d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2392.86, "sourceLowPrice": 2380.77, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
@@ -33848,7 +33848,7 @@
         <v>37</v>
       </c>
       <c r="BL64" t="n">
-        <v>1782575759998</v>
+        <v>1782579163441</v>
       </c>
       <c r="BM64" t="n">
         <v>2378.057</v>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54415, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027167660_fc2d6f206b84ec8115f8b2060648fd39.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027387610_9fb91223f21055c2e3b1f84f1d6f62a5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17535.709, "sourceLowPrice": 17449.895}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54415, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027167660_fc2d6f206b84ec8115f8b2060648fd39.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781027387610_9fb91223f21055c2e3b1f84f1d6f62a5.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17535.709, "sourceLowPrice": 17449.895, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
@@ -34372,7 +34372,7 @@
         <v>37</v>
       </c>
       <c r="BL65" t="n">
-        <v>1782575759998</v>
+        <v>1782579163442</v>
       </c>
       <c r="BM65" t="n">
         <v>17547.399</v>
@@ -34841,7 +34841,7 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54416, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475215419_a413cc291367f1c13e80144a54293631.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597229374_a263da44cab5cda5a67defecfd2aa40b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2393.92, "sourceLowPrice": 2372.91}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54416, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475215419_a413cc291367f1c13e80144a54293631.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780597229374_a263da44cab5cda5a67defecfd2aa40b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2393.92, "sourceLowPrice": 2372.91, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -34896,7 +34896,7 @@
         <v>37</v>
       </c>
       <c r="BL66" t="n">
-        <v>1782575759999</v>
+        <v>1782579163442</v>
       </c>
       <c r="BM66" t="n">
         <v>2377.735</v>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54417, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475829519_a10c747effe8730da723db2c68b446d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475941444_93bfd6b36159c37273b1bc1eafdf6263.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.49, "sourceLowPrice": 2372.91}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54417, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475829519_a10c747effe8730da723db2c68b446d8.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780475941444_93bfd6b36159c37273b1bc1eafdf6263.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2384.49, "sourceLowPrice": 2372.91, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
@@ -35420,7 +35420,7 @@
         <v>37</v>
       </c>
       <c r="BL67" t="n">
-        <v>1782575760000</v>
+        <v>1782579163442</v>
       </c>
       <c r="BM67" t="n">
         <v>2378.966</v>
@@ -35601,11 +35601,11 @@
       </c>
       <c r="DL67" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN67" t="inlineStr">
         <is>
@@ -35679,12 +35679,12 @@
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 52, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-04-19T07:04:00.000Z"}, {"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 52, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-04-19T07:04:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54418, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028261141_363434f7d1729ba2a54b88eb60df9a15.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028501115_02e09b779fd55a78b821d30c814e030e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17313.443, "sourceLowPrice": 17051.323}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54418, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028261141_363434f7d1729ba2a54b88eb60df9a15.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028501115_02e09b779fd55a78b821d30c814e030e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17313.443, "sourceLowPrice": 17051.323, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -35944,7 +35944,7 @@
         <v>37</v>
       </c>
       <c r="BL68" t="n">
-        <v>1782575760000</v>
+        <v>1782579163442</v>
       </c>
       <c r="BM68" t="n">
         <v>17369.62</v>
@@ -36125,11 +36125,11 @@
       </c>
       <c r="DL68" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN68" t="inlineStr">
         <is>
@@ -36203,12 +36203,12 @@
       </c>
       <c r="EF68" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "manual", "state": "confirmed", "cost_R": 2.0, "cost_$": 100, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-04-19T11:26:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH68" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54419, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028596115_d290c96261982b8726740e00a9e4f65d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028668580_8986819606d157293db8fe4ed1fb8465.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17262.421, "sourceLowPrice": 17101.947}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54419, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028596115_d290c96261982b8726740e00a9e4f65d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028668580_8986819606d157293db8fe4ed1fb8465.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17262.421, "sourceLowPrice": 17101.947, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
@@ -36468,7 +36468,7 @@
         <v>37</v>
       </c>
       <c r="BL69" t="n">
-        <v>1782575760001</v>
+        <v>1782579163442</v>
       </c>
       <c r="BM69" t="n">
         <v>17275.186</v>
@@ -36937,7 +36937,7 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54420, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028734449_33fe9e9868ceaff3f8ed3fb9097046ec.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028795892_f6b0db224cb5a8c3f06af0e1d513b8bd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17225.197, "sourceLowPrice": 17139.087}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54420, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028734449_33fe9e9868ceaff3f8ed3fb9097046ec.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781028795892_f6b0db224cb5a8c3f06af0e1d513b8bd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17225.197, "sourceLowPrice": 17139.087, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
@@ -36992,7 +36992,7 @@
         <v>37</v>
       </c>
       <c r="BL70" t="n">
-        <v>1782575760002</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM70" t="n">
         <v>17240.521</v>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54421, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270824983_d03598517881d9f399d7f9aa75d1d307.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270912286_d91f6bdfceeaafb50571a4cc13bc6c2d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06552, "sourceLowPrice": 1.0624}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54421, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270824983_d03598517881d9f399d7f9aa75d1d307.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781270912286_d91f6bdfceeaafb50571a4cc13bc6c2d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06552, "sourceLowPrice": 1.0624, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
@@ -37516,7 +37516,7 @@
         <v>37</v>
       </c>
       <c r="BL71" t="n">
-        <v>1782575760002</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM71" t="n">
         <v>1.06634</v>
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54422, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030298318_522b6f63ee28c8a9acbef0b01c18318e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030409417_4f02383121693aead3ece77c0c61cd8e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17152.521, "sourceLowPrice": 17103.543}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54422, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030298318_522b6f63ee28c8a9acbef0b01c18318e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030409417_4f02383121693aead3ece77c0c61cd8e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17152.521, "sourceLowPrice": 17103.543, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -38040,7 +38040,7 @@
         <v>37</v>
       </c>
       <c r="BL72" t="n">
-        <v>1782575760003</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM72" t="n">
         <v>17163.598</v>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="DO72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 17163.598, "new": 17167.69, "at": 1713772200000}]</t>
         </is>
       </c>
       <c r="DP72" t="n">
@@ -38509,7 +38509,7 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54423, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030765617_8cd264a1bc581c6873d1e82e0c17c4cc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030920133_890abe4a36216c3671bfb3052b056e18.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17187.476, "sourceLowPrice": 17121.975}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54423, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030765617_8cd264a1bc581c6873d1e82e0c17c4cc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781030920133_890abe4a36216c3671bfb3052b056e18.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17187.476, "sourceLowPrice": 17121.975, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
@@ -38564,7 +38564,7 @@
         <v>37</v>
       </c>
       <c r="BL73" t="n">
-        <v>1782575760003</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM73" t="n">
         <v>17168.708</v>
@@ -38745,11 +38745,11 @@
       </c>
       <c r="DL73" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN73" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="EC73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED73" t="n">
         <v>2024</v>
@@ -38823,7 +38823,7 @@
       </c>
       <c r="EF73" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG73" t="inlineStr">
@@ -39033,7 +39033,7 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54424, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031085466_ef867640abb85cca497c0d4fc3dc7828.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031254620_e673e9c4fde5934dc7872511c80f4878.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17171.054, "sourceLowPrice": 17005.92}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54424, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031085466_ef867640abb85cca497c0d4fc3dc7828.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031254620_e673e9c4fde5934dc7872511c80f4878.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17171.054, "sourceLowPrice": 17005.92, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
@@ -39088,7 +39088,7 @@
         <v>37</v>
       </c>
       <c r="BL74" t="n">
-        <v>1782575760004</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM74" t="n">
         <v>17188.665</v>
@@ -39557,7 +39557,7 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54425, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031327010_e719a7c46e7e7f61c564abef0a058b7d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031338997_74cac452534fcfbfbd51b1039a57179d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17134.265, "sourceLowPrice": 17025.775}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54425, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031327010_e719a7c46e7e7f61c564abef0a058b7d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781031338997_74cac452534fcfbfbd51b1039a57179d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17134.265, "sourceLowPrice": 17025.775, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
@@ -39612,7 +39612,7 @@
         <v>37</v>
       </c>
       <c r="BL75" t="n">
-        <v>1782575760004</v>
+        <v>1782579163443</v>
       </c>
       <c r="BM75" t="n">
         <v>17154.776</v>
@@ -40081,7 +40081,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54427, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650581590_ce383b6e5d95442047eb77b65e90717a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650799344_20000e43a55cd1d064aa49ca6aed9add.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2304.73}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54427, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650581590_ce383b6e5d95442047eb77b65e90717a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650799344_20000e43a55cd1d064aa49ca6aed9add.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2304.73, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -40136,7 +40136,7 @@
         <v>37</v>
       </c>
       <c r="BL76" t="n">
-        <v>1782575760005</v>
+        <v>1782579163444</v>
       </c>
       <c r="BM76" t="n">
         <v>2297.925</v>
@@ -40605,7 +40605,7 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54428, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650934614_eb9c46b9329f2561fc9f6795009021fa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780651004593_afeebeac9e810a0166b07afe7ffef5dc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2305.76}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54428, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780650934614_eb9c46b9329f2561fc9f6795009021fa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780651004593_afeebeac9e810a0166b07afe7ffef5dc.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2311.31, "sourceLowPrice": 2305.76, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
@@ -40660,7 +40660,7 @@
         <v>37</v>
       </c>
       <c r="BL77" t="n">
-        <v>1782575760005</v>
+        <v>1782579163444</v>
       </c>
       <c r="BM77" t="n">
         <v>2308.285</v>
@@ -41129,7 +41129,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54429, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271232715_8829ebd89086dbf79c7137d930575416.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271361041_2ac8e5993f9c95012c237877365ce28f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06828, "sourceLowPrice": 1.06532}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54429, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271232715_8829ebd89086dbf79c7137d930575416.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271361041_2ac8e5993f9c95012c237877365ce28f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06828, "sourceLowPrice": 1.06532, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -41184,7 +41184,7 @@
         <v>37</v>
       </c>
       <c r="BL78" t="n">
-        <v>1782575760006</v>
+        <v>1782579163444</v>
       </c>
       <c r="BM78" t="n">
         <v>1.06964</v>
@@ -41653,7 +41653,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54430, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271479924_f3d0b05ace36fca84780275bc1d0bada.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271495525_1c0a85c474439df78657c65f49681fb1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0678, "sourceLowPrice": 1.06646}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54430, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271479924_f3d0b05ace36fca84780275bc1d0bada.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271495525_1c0a85c474439df78657c65f49681fb1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0678, "sourceLowPrice": 1.06646, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -41708,7 +41708,7 @@
         <v>37</v>
       </c>
       <c r="BL79" t="n">
-        <v>1782575760007</v>
+        <v>1782579163444</v>
       </c>
       <c r="BM79" t="n">
         <v>1.06732</v>
@@ -41889,11 +41889,11 @@
       </c>
       <c r="DL79" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN79" t="inlineStr">
         <is>
@@ -41967,12 +41967,12 @@
       </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "late_entry", "label": "Late Entry", "source": "manual", "state": "confirmed", "cost_R": 1.0, "cost_$": 50, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-04-23T07:55:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
@@ -42177,7 +42177,7 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54431, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271681549_e3eafb5aa23e7edb3a547ee814de1fd4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271757981_58680a436fed6273a7c0371ac37dcae9.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06912, "sourceLowPrice": 1.06601}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54431, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271681549_e3eafb5aa23e7edb3a547ee814de1fd4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271757981_58680a436fed6273a7c0371ac37dcae9.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.06912, "sourceLowPrice": 1.06601, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
@@ -42232,7 +42232,7 @@
         <v>37</v>
       </c>
       <c r="BL80" t="n">
-        <v>1782575760007</v>
+        <v>1782579163444</v>
       </c>
       <c r="BM80" t="n">
         <v>1.0679</v>
@@ -42426,7 +42426,7 @@
       </c>
       <c r="DO80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.0679, "new": 1.06806, "at": 1713861000000}]</t>
         </is>
       </c>
       <c r="DP80" t="n">
@@ -42701,7 +42701,7 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54433, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652206083_2d5f7e526d714b914aa041666679b662.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652457354_0d4530fc93baf439513bc55f9316a8a1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.547, "sourceLowPrice": 2312.17}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54433, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652206083_2d5f7e526d714b914aa041666679b662.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652457354_0d4530fc93baf439513bc55f9316a8a1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2329.547, "sourceLowPrice": 2312.17, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
@@ -42756,7 +42756,7 @@
         <v>37</v>
       </c>
       <c r="BL81" t="n">
-        <v>1782575760009</v>
+        <v>1782579163445</v>
       </c>
       <c r="BM81" t="n">
         <v>2310.815</v>
@@ -43225,7 +43225,7 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54434, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087598526_e9800cac8c13a5575c017835074459d2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087684329_79cbd1ee8e1ce5f5bcd8963e36aa3738.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17615.199, "sourceLowPrice": 17576.042}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54434, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087598526_e9800cac8c13a5575c017835074459d2.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087684329_79cbd1ee8e1ce5f5bcd8963e36aa3738.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 17615.199, "sourceLowPrice": 17576.042, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
@@ -43280,7 +43280,7 @@
         <v>37</v>
       </c>
       <c r="BL82" t="n">
-        <v>1782575760009</v>
+        <v>1782579163445</v>
       </c>
       <c r="BM82" t="n">
         <v>17597.899</v>
@@ -43461,11 +43461,11 @@
       </c>
       <c r="DL82" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN82" t="inlineStr">
         <is>
@@ -43539,12 +43539,12 @@
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 50, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2024-04-24T08:23:00.000Z"}, {"type": "size_up", "label": "Size Up", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 50, "evidence": "Position size exceeded the planned risk envelope.", "detected_at": "2024-04-24T08:23:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
@@ -43749,7 +43749,7 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54435, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087800905_e90d9fb19261e3d8e941171d3d6a1bf5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088027067_a8b2c70f766de65966200150eaca161f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5089.307, "sourceLowPrice": 5046.48}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54435, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781087800905_e90d9fb19261e3d8e941171d3d6a1bf5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088027067_a8b2c70f766de65966200150eaca161f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5089.307, "sourceLowPrice": 5046.48, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
@@ -43804,7 +43804,7 @@
         <v>37</v>
       </c>
       <c r="BL83" t="n">
-        <v>1782575760010</v>
+        <v>1782579163445</v>
       </c>
       <c r="BM83" t="n">
         <v>5089.687</v>
@@ -44273,7 +44273,7 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54436, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652605436_e7ceaa6e87b5983d03cb170921a0dbcb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652740475_ce8974483039dbf9c11c7fab479fe18a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.04, "sourceLowPrice": 2316.07}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54436, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652605436_e7ceaa6e87b5983d03cb170921a0dbcb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652740475_ce8974483039dbf9c11c7fab479fe18a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2326.04, "sourceLowPrice": 2316.07, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
@@ -44328,7 +44328,7 @@
         <v>37</v>
       </c>
       <c r="BL84" t="n">
-        <v>1782575760010</v>
+        <v>1782579163445</v>
       </c>
       <c r="BM84" t="n">
         <v>2316.37</v>
@@ -44797,7 +44797,7 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54437, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271986636_df37733a22627ee14b3bc05156272aed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272089738_257f9b3c4ad58e59b53f6572e7ad2154.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07067, "sourceLowPrice": 1.0681}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54437, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781271986636_df37733a22627ee14b3bc05156272aed.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272089738_257f9b3c4ad58e59b53f6572e7ad2154.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07067, "sourceLowPrice": 1.0681, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
@@ -44852,7 +44852,7 @@
         <v>37</v>
       </c>
       <c r="BL85" t="n">
-        <v>1782575760011</v>
+        <v>1782579163446</v>
       </c>
       <c r="BM85" t="n">
         <v>1.07036</v>
@@ -45321,7 +45321,7 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54438, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652931887_4b483900e26428d7b97b7f208b109418.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653108005_519113c47c608e272dab49cc54566372.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2333.597, "sourceLowPrice": 2318.44}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54438, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780652931887_4b483900e26428d7b97b7f208b109418.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653108005_519113c47c608e272dab49cc54566372.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2333.597, "sourceLowPrice": 2318.44, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -45376,7 +45376,7 @@
         <v>37</v>
       </c>
       <c r="BL86" t="n">
-        <v>1782575760012</v>
+        <v>1782579163446</v>
       </c>
       <c r="BM86" t="n">
         <v>2315.93</v>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54439, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272239600_91f7b1ae937bf84ac635af31fe3c9664.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272340133_88bb568d8e1b5f1f20dc68342fdfbbb7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07299, "sourceLowPrice": 1.07141}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54439, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272239600_91f7b1ae937bf84ac635af31fe3c9664.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781272340133_88bb568d8e1b5f1f20dc68342fdfbbb7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07299, "sourceLowPrice": 1.07141, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -45900,7 +45900,7 @@
         <v>37</v>
       </c>
       <c r="BL87" t="n">
-        <v>1782575760013</v>
+        <v>1782579163446</v>
       </c>
       <c r="BM87" t="n">
         <v>1.0732</v>
@@ -46369,7 +46369,7 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54440, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653723310_7474e526ff82ba41ed6994c16f9e10fe.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654198888_6c29d1e86372b8a9dde1984ff82b5063.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.81, "sourceLowPrice": 2312.87}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54440, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780653723310_7474e526ff82ba41ed6994c16f9e10fe.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654198888_6c29d1e86372b8a9dde1984ff82b5063.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2334.81, "sourceLowPrice": 2312.87, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
@@ -46424,7 +46424,7 @@
         <v>37</v>
       </c>
       <c r="BL88" t="n">
-        <v>1782575760013</v>
+        <v>1782579163446</v>
       </c>
       <c r="BM88" t="n">
         <v>2322.33</v>
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54441, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654291066_05ad6513f960d539f4dc94e22ce687c4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654527488_bde191c96a4a9b3e56d142dfa2e9a10a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.366, "sourceLowPrice": 2315.07}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54441, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654291066_05ad6513f960d539f4dc94e22ce687c4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654527488_bde191c96a4a9b3e56d142dfa2e9a10a.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2339.366, "sourceLowPrice": 2315.07, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
@@ -46948,7 +46948,7 @@
         <v>37</v>
       </c>
       <c r="BL89" t="n">
-        <v>1782575760014</v>
+        <v>1782579163446</v>
       </c>
       <c r="BM89" t="n">
         <v>2311.87</v>
@@ -47129,11 +47129,11 @@
       </c>
       <c r="DL89" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN89" t="inlineStr">
         <is>
@@ -47207,12 +47207,12 @@
       </c>
       <c r="EF89" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 100, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2024-04-25T10:32:00.000Z"}, {"type": "late_entry", "label": "Late Entry", "source": "auto", "state": "detected", "cost_R": 2.0, "cost_$": 100, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2024-04-25T10:32:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH89" t="inlineStr">
@@ -47417,7 +47417,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54442, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088443425_a24cf5b1d46b4b0b88b1d6670ada8ee5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088575298_da8f3b9cdcce0bbd1d82d1fd1e4604d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5022.673, "sourceLowPrice": 4988.411}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54442, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088443425_a24cf5b1d46b4b0b88b1d6670ada8ee5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088575298_da8f3b9cdcce0bbd1d82d1fd1e4604d6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5022.673, "sourceLowPrice": 4988.411, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -47472,7 +47472,7 @@
         <v>37</v>
       </c>
       <c r="BL90" t="n">
-        <v>1782575760014</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM90" t="n">
         <v>5008.429</v>
@@ -47941,7 +47941,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54443, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654609188_c2764965275ac78be910d14d43c40613.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654676062_c6b33018c028cb050c1c31d1ec69e0cd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.935, "sourceLowPrice": 2317.07}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54443, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654609188_c2764965275ac78be910d14d43c40613.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780654676062_c6b33018c028cb050c1c31d1ec69e0cd.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.935, "sourceLowPrice": 2317.07, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -47996,7 +47996,7 @@
         <v>37</v>
       </c>
       <c r="BL91" t="n">
-        <v>1782575760015</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM91" t="n">
         <v>2316.09</v>
@@ -48465,7 +48465,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54444, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663010173_d983f1a0c9e0968dce85c1860bfad3b5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663144425_30881a904ad57e3e4358dfe603f74b0f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.12, "sourceLowPrice": 2345.83}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54444, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663010173_d983f1a0c9e0968dce85c1860bfad3b5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663144425_30881a904ad57e3e4358dfe603f74b0f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2349.12, "sourceLowPrice": 2345.83, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -48520,7 +48520,7 @@
         <v>37</v>
       </c>
       <c r="BL92" t="n">
-        <v>1782575760015</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM92" t="n">
         <v>2346.24</v>
@@ -48714,7 +48714,7 @@
       </c>
       <c r="DO92" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2346.24, "new": 2345.828, "at": 1714112160000}]</t>
         </is>
       </c>
       <c r="DP92" t="n">
@@ -48989,7 +48989,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54445, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663391228_336c5b531cb51dfbe77807bff564c92b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663472599_40fc0c7e06f8dd6e9d62150d618e55c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.0, "sourceLowPrice": 2342.16}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54445, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663391228_336c5b531cb51dfbe77807bff564c92b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663472599_40fc0c7e06f8dd6e9d62150d618e55c4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2346.0, "sourceLowPrice": 2342.16, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -49044,7 +49044,7 @@
         <v>37</v>
       </c>
       <c r="BL93" t="n">
-        <v>1782575760016</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM93" t="n">
         <v>2342.47</v>
@@ -49513,7 +49513,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54446, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663583916_3b5098ae6bc5ebd3644c779723841484.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663652178_cfa0665487306c4c6fd6f12ab4c6c7af.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.65, "sourceLowPrice": 2342.52}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54446, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663583916_3b5098ae6bc5ebd3644c779723841484.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663652178_cfa0665487306c4c6fd6f12ab4c6c7af.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2351.65, "sourceLowPrice": 2342.52, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -49568,7 +49568,7 @@
         <v>37</v>
       </c>
       <c r="BL94" t="n">
-        <v>1782575760016</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM94" t="n">
         <v>2341.16</v>
@@ -50037,7 +50037,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54447, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088957273_a7ae1924cffd0e49af829845fc8c72a0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781089151908_42a13b50e584dcc081573f10e79e6f93.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5122.379, "sourceLowPrice": 5072.157}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54447, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781088957273_a7ae1924cffd0e49af829845fc8c72a0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781089151908_42a13b50e584dcc081573f10e79e6f93.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5122.379, "sourceLowPrice": 5072.157, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -50092,7 +50092,7 @@
         <v>37</v>
       </c>
       <c r="BL95" t="n">
-        <v>1782575760017</v>
+        <v>1782579163447</v>
       </c>
       <c r="BM95" t="n">
         <v>5108.242</v>
@@ -50561,7 +50561,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54448, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663875354_66e26edf5b46fc87a72866617b889a21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663971393_5d27b51fb3f0b2a304aa8a0eb38e4d4b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.32, "sourceLowPrice": 2328.77}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54448, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663875354_66e26edf5b46fc87a72866617b889a21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780663971393_5d27b51fb3f0b2a304aa8a0eb38e4d4b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2345.32, "sourceLowPrice": 2328.77, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -50616,7 +50616,7 @@
         <v>37</v>
       </c>
       <c r="BL96" t="n">
-        <v>1782575760017</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM96" t="n">
         <v>2335.98</v>
@@ -50810,7 +50810,7 @@
       </c>
       <c r="DO96" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2335.98, "new": 2335.353, "at": 1714125480000}]</t>
         </is>
       </c>
       <c r="DP96" t="n">
@@ -51085,7 +51085,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54449, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664081884_cb45e3cc4388dad70df15536aa081829.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664188275_b2b1c07e9becfb5172ac1be5424c8db4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.38, "sourceLowPrice": 2328.77}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54449, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664081884_cb45e3cc4388dad70df15536aa081829.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780664188275_b2b1c07e9becfb5172ac1be5424c8db4.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2335.38, "sourceLowPrice": 2328.77, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -51140,7 +51140,7 @@
         <v>37</v>
       </c>
       <c r="BL97" t="n">
-        <v>1782575760018</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM97" t="n">
         <v>2330.895</v>
@@ -51609,7 +51609,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54451, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668025077_3d99263fbe62b8a71cd37f6df2075963.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668264554_736bc8b9d2defb6d7a67d32d67c3e595.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2330.07}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54451, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668025077_3d99263fbe62b8a71cd37f6df2075963.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668264554_736bc8b9d2defb6d7a67d32d67c3e595.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2330.07, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -51664,7 +51664,7 @@
         <v>37</v>
       </c>
       <c r="BL98" t="n">
-        <v>1782575760018</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM98" t="n">
         <v>2326.515</v>
@@ -52133,7 +52133,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54452, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668351989_d6bf445a2fdff06f5d0ee351d6463fee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668445344_5fc1984f8afaf054f18c2436f81fa635.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2332.21}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54452, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668351989_d6bf445a2fdff06f5d0ee351d6463fee.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780668445344_5fc1984f8afaf054f18c2436f81fa635.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2344.44, "sourceLowPrice": 2332.21, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -52188,7 +52188,7 @@
         <v>37</v>
       </c>
       <c r="BL99" t="n">
-        <v>1782575760019</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM99" t="n">
         <v>2330.977</v>
@@ -52657,7 +52657,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54455, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780669739101_0fca517685f5e96886202a2fea57c110.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780670004542_2e3e8971b4d5c8b0cb854df1d3509b8b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.22, "sourceLowPrice": 2310.479}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54455, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780669739101_0fca517685f5e96886202a2fea57c110.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1780670004542_2e3e8971b4d5c8b0cb854df1d3509b8b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2323.22, "sourceLowPrice": 2310.479, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -52712,7 +52712,7 @@
         <v>37</v>
       </c>
       <c r="BL100" t="n">
-        <v>1782575760020</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM100" t="n">
         <v>2318.26</v>
@@ -53181,7 +53181,7 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54456, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274729984_e4830aa863fe9ddf79840f9909e0f87a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274878983_7479f0db39fc8974304d0741fbb3edd6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07296, "sourceLowPrice": 1.06749}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54456, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274729984_e4830aa863fe9ddf79840f9909e0f87a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781274878983_7479f0db39fc8974304d0741fbb3edd6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07296, "sourceLowPrice": 1.06749, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
@@ -53236,7 +53236,7 @@
         <v>37</v>
       </c>
       <c r="BL101" t="n">
-        <v>1782575760020</v>
+        <v>1782579163448</v>
       </c>
       <c r="BM101" t="n">
         <v>1.07365</v>
@@ -53705,7 +53705,7 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54457, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275007177_63fd6c85e0de519219fbef360c9df16a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275029549_85819c0a9f978e2e9a4ccce4283888e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0724, "sourceLowPrice": 1.06813}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54457, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275007177_63fd6c85e0de519219fbef360c9df16a.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781275029549_85819c0a9f978e2e9a4ccce4283888e1.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.0724, "sourceLowPrice": 1.06813, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
@@ -53760,7 +53760,7 @@
         <v>37</v>
       </c>
       <c r="BL102" t="n">
-        <v>1782575760021</v>
+        <v>1782579163449</v>
       </c>
       <c r="BM102" t="n">
         <v>1.07298</v>
@@ -53941,11 +53941,11 @@
       </c>
       <c r="DL102" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN102" t="inlineStr">
         <is>
@@ -54019,12 +54019,12 @@
       </c>
       <c r="EF102" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "manual", "state": "confirmed", "cost_R": 2.5, "cost_$": 125, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2024-04-30T08:35:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH102" t="inlineStr">
@@ -54229,7 +54229,7 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54460, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303685923_e409fc5fea77876cb76f943c77fc41ad.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303850406_b1db16e9494b4bbfa1009d8177c98939.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2865.095, "sourceLowPrice": 2859.0}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54460, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303685923_e409fc5fea77876cb76f943c77fc41ad.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781303850406_b1db16e9494b4bbfa1009d8177c98939.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2865.095, "sourceLowPrice": 2859.0, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
@@ -54284,7 +54284,7 @@
         <v>37</v>
       </c>
       <c r="BL103" t="n">
-        <v>1782575760021</v>
+        <v>1782579163449</v>
       </c>
       <c r="BM103" t="n">
         <v>2859.825</v>
@@ -54753,7 +54753,7 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54461, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304291666_93f30a6e9557eeca95c6f6a984492655.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304556954_6aec2831ce8ce5ff589863e918f6b7de.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2863.9}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54461, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304291666_93f30a6e9557eeca95c6f6a984492655.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304556954_6aec2831ce8ce5ff589863e918f6b7de.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2863.9, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
@@ -54808,7 +54808,7 @@
         <v>37</v>
       </c>
       <c r="BL104" t="n">
-        <v>1782575760022</v>
+        <v>1782579163449</v>
       </c>
       <c r="BM104" t="n">
         <v>2858</v>
@@ -55277,7 +55277,7 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54462, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304656708_551d250f69dcc0c5de738454c9756589.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304729790_697c446b79b5764885f38cb71821c2f7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2864.375}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54462, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304656708_551d250f69dcc0c5de738454c9756589.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304729790_697c446b79b5764885f38cb71821c2f7.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2871.565, "sourceLowPrice": 2864.375, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
@@ -55332,7 +55332,7 @@
         <v>37</v>
       </c>
       <c r="BL105" t="n">
-        <v>1782575760023</v>
+        <v>1782579163449</v>
       </c>
       <c r="BM105" t="n">
         <v>2866.72</v>
@@ -55801,7 +55801,7 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54463, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304874760_768304f93f6241d6e2a795362ef340b4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305110232_ce7d27e554c668843c6c376b9ca0506c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2881.075, "sourceLowPrice": 2866.915}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54463, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781304874760_768304f93f6241d6e2a795362ef340b4.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305110232_ce7d27e554c668843c6c376b9ca0506c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2881.075, "sourceLowPrice": 2866.915, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
@@ -55856,7 +55856,7 @@
         <v>37</v>
       </c>
       <c r="BL106" t="n">
-        <v>1782575760023</v>
+        <v>1782579163450</v>
       </c>
       <c r="BM106" t="n">
         <v>2863.375</v>
@@ -56325,7 +56325,7 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54464, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305427085_a81f92769d7821925e3f2754f3a6fcfc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305558509_e91c3b2a1d99505bd249ec61bcb3c9be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2877.775, "sourceLowPrice": 2868.76}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54464, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305427085_a81f92769d7821925e3f2754f3a6fcfc.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305558509_e91c3b2a1d99505bd249ec61bcb3c9be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2877.775, "sourceLowPrice": 2868.76, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
@@ -56380,7 +56380,7 @@
         <v>37</v>
       </c>
       <c r="BL107" t="n">
-        <v>1782575760024</v>
+        <v>1782579163450</v>
       </c>
       <c r="BM107" t="n">
         <v>2868.07</v>
@@ -56849,7 +56849,7 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54465, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305619233_eef8ed7bb4cf6796f8352152c1d8b395.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305666161_0f56886c8dd4977d54df3cf8f2fe61fa.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2875.871, "sourceLowPrice": 2871.39}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54465, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305619233_eef8ed7bb4cf6796f8352152c1d8b395.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781305666161_0f56886c8dd4977d54df3cf8f2fe61fa.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2875.871, "sourceLowPrice": 2871.39, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
@@ -56904,7 +56904,7 @@
         <v>37</v>
       </c>
       <c r="BL108" t="n">
-        <v>1782575760025</v>
+        <v>1782579163450</v>
       </c>
       <c r="BM108" t="n">
         <v>2870.59</v>
@@ -57373,7 +57373,7 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54467, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301281883_8d43596df4708f26a26d2cc1c92902e3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301493516_66fcf7fa768b576b421e1b56fb018471.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05606, "sourceLowPrice": 1.04863}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54467, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301281883_8d43596df4708f26a26d2cc1c92902e3.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781301493516_66fcf7fa768b576b421e1b56fb018471.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.05606, "sourceLowPrice": 1.04863, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
@@ -57428,7 +57428,7 @@
         <v>37</v>
       </c>
       <c r="BL109" t="n">
-        <v>1782575760025</v>
+        <v>1782579163450</v>
       </c>
       <c r="BM109" t="n">
         <v>1.048</v>
@@ -57897,7 +57897,7 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54468, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308656903_f7f106061695d7aa63fcc1098329b31d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308798367_b8c6a3c55b4c764b55aa235c0c986202.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.416, "sourceLowPrice": 2896.785}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54468, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308656903_f7f106061695d7aa63fcc1098329b31d.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781308798367_b8c6a3c55b4c764b55aa235c0c986202.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.416, "sourceLowPrice": 2896.785, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
@@ -57952,7 +57952,7 @@
         <v>37</v>
       </c>
       <c r="BL110" t="n">
-        <v>1782575760026</v>
+        <v>1782579163450</v>
       </c>
       <c r="BM110" t="n">
         <v>2895.39</v>
@@ -58146,7 +58146,7 @@
       </c>
       <c r="DO110" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 2895.39, "new": 2894.784, "at": 1741056600000}]</t>
         </is>
       </c>
       <c r="DP110" t="n">
@@ -58421,7 +58421,7 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54477, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310320388_334bed17f36e063a5fa84c0ba7ea4974.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310496527_40f2c80c8f92c717bba5c2090b675388.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2917.375, "sourceLowPrice": 2913.05}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54477, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310320388_334bed17f36e063a5fa84c0ba7ea4974.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310496527_40f2c80c8f92c717bba5c2090b675388.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2917.375, "sourceLowPrice": 2913.05, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
@@ -58476,7 +58476,7 @@
         <v>37</v>
       </c>
       <c r="BL111" t="n">
-        <v>1782575760027</v>
+        <v>1782579163451</v>
       </c>
       <c r="BM111" t="n">
         <v>2913.745</v>
@@ -58945,7 +58945,7 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54478, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310715203_d1d361b5382d819ccf102ce5b800c271.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310946254_223ec4e1f4785bd7d517e1fd2bd2ecd2.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2915.86}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54478, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310715203_d1d361b5382d819ccf102ce5b800c271.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781310946254_223ec4e1f4785bd7d517e1fd2bd2ecd2.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2915.86, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
@@ -59000,7 +59000,7 @@
         <v>37</v>
       </c>
       <c r="BL112" t="n">
-        <v>1782575760027</v>
+        <v>1782579163451</v>
       </c>
       <c r="BM112" t="n">
         <v>2912.05</v>
@@ -59469,7 +59469,7 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54479, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311020369_4e4750c0fe61cecdf8a5c7f9b09709b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311068841_5167c77814071dff66806aae9d95e09c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2913.44}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54479, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311020369_4e4750c0fe61cecdf8a5c7f9b09709b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311068841_5167c77814071dff66806aae9d95e09c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2922.675, "sourceLowPrice": 2913.44, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
@@ -59524,7 +59524,7 @@
         <v>37</v>
       </c>
       <c r="BL113" t="n">
-        <v>1782575760028</v>
+        <v>1782579163451</v>
       </c>
       <c r="BM113" t="n">
         <v>2916.755</v>
@@ -59993,7 +59993,7 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54480, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311281758_de9959ba074d8227db5f7b9db39b3e30.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311511444_a583ee11be73a1a9c146d4d45b32f991.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2919.39, "sourceLowPrice": 2912.055}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54480, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311281758_de9959ba074d8227db5f7b9db39b3e30.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311511444_a583ee11be73a1a9c146d4d45b32f991.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2919.39, "sourceLowPrice": 2912.055, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
@@ -60048,7 +60048,7 @@
         <v>37</v>
       </c>
       <c r="BL114" t="n">
-        <v>1782575760028</v>
+        <v>1782579163451</v>
       </c>
       <c r="BM114" t="n">
         <v>2908.1</v>
@@ -60059,7 +60059,7 @@
         </is>
       </c>
       <c r="BO114" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="BP114" t="n">
         <v>0.55</v>
@@ -60517,7 +60517,7 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54481, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302282070_ed72ec542d8415e414a82f33aeb2958f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302387524_4b21a6fcaef3ea710f246778e309ec73.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07925, "sourceLowPrice": 1.06869}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54481, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302282070_ed72ec542d8415e414a82f33aeb2958f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302387524_4b21a6fcaef3ea710f246778e309ec73.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07925, "sourceLowPrice": 1.06869, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
@@ -60572,7 +60572,7 @@
         <v>37</v>
       </c>
       <c r="BL115" t="n">
-        <v>1782575760029</v>
+        <v>1782579163451</v>
       </c>
       <c r="BM115" t="n">
         <v>1.06754</v>
@@ -60766,7 +60766,7 @@
       </c>
       <c r="DO115" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 1.06754, "new": 1.06707, "at": 1741159500000}]</t>
         </is>
       </c>
       <c r="DP115" t="n">
@@ -61041,7 +61041,7 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54482, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311576830_70d737a01840fe66c82325d95910d5d0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311678638_3c62b2e9efebf3c270124585058f64b0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.1, "sourceLowPrice": 2912.677}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54482, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311576830_70d737a01840fe66c82325d95910d5d0.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781311678638_3c62b2e9efebf3c270124585058f64b0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 2918.1, "sourceLowPrice": 2912.677, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
@@ -61096,7 +61096,7 @@
         <v>37</v>
       </c>
       <c r="BL116" t="n">
-        <v>1782575760030</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM116" t="n">
         <v>2915.84</v>
@@ -61565,7 +61565,7 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54483, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302441555_439642e81a2a2872d4d12eccb0b33f27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302489069_7df53640835f86ba82ae7c2735d3538d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07216}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54483, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302441555_439642e81a2a2872d4d12eccb0b33f27.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781302489069_7df53640835f86ba82ae7c2735d3538d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 1.07697, "sourceLowPrice": 1.07216, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
@@ -61620,7 +61620,7 @@
         <v>37</v>
       </c>
       <c r="BL117" t="n">
-        <v>1782575760030</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM117" t="n">
         <v>1.07032</v>
@@ -62089,7 +62089,7 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54484, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353421941_79cff43a6102b1b4cc2c846c3ecf1fa5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353568638_05bda76c68d69fe954c3d756ce6812e0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5795.614, "sourceLowPrice": 5742.079}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54484, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353421941_79cff43a6102b1b4cc2c846c3ecf1fa5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353568638_05bda76c68d69fe954c3d756ce6812e0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5795.614, "sourceLowPrice": 5742.079, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
@@ -62144,7 +62144,7 @@
         <v>37</v>
       </c>
       <c r="BL118" t="n">
-        <v>1782575760031</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM118" t="n">
         <v>5807.915</v>
@@ -62613,7 +62613,7 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54485, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353671315_1d99b670749f74056ab256517c04a7d7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353704848_7de0729f6a46fae04d6442e7fb78b0be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5786.506, "sourceLowPrice": 5742.079}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54485, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353671315_1d99b670749f74056ab256517c04a7d7.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781353704848_7de0729f6a46fae04d6442e7fb78b0be.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 5786.506, "sourceLowPrice": 5742.079, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
@@ -62668,7 +62668,7 @@
         <v>37</v>
       </c>
       <c r="BL119" t="n">
-        <v>1782575760032</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM119" t="n">
         <v>5763.529</v>
@@ -63137,7 +63137,7 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54486, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439233487_eef0a14a0519a9d53a79bbc0bb8c309e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440657327_fb9733aa9156f595e9d557c7660d15fb.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.35, "sourceLowPrice": 4382.975}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54486, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439233487_eef0a14a0519a9d53a79bbc0bb8c309e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440657327_fb9733aa9156f595e9d557c7660d15fb.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.35, "sourceLowPrice": 4382.975, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
@@ -63192,7 +63192,7 @@
         <v>37</v>
       </c>
       <c r="BL120" t="n">
-        <v>1782575760032</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM120" t="n">
         <v>4397.31</v>
@@ -63661,7 +63661,7 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54487, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440776187_b62d86c09e3090b0d7bf4349bb031182.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440803044_33bc271976b402786bf7d6071f190a0b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.145, "sourceLowPrice": 4386.49}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54487, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440776187_b62d86c09e3090b0d7bf4349bb031182.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781440803044_33bc271976b402786bf7d6071f190a0b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4395.145, "sourceLowPrice": 4386.49, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
@@ -63716,7 +63716,7 @@
         <v>37</v>
       </c>
       <c r="BL121" t="n">
-        <v>1782575760033</v>
+        <v>1782579163452</v>
       </c>
       <c r="BM121" t="n">
         <v>4393.75</v>
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54488, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439760945_a0606e9630178667f056606da8cff8e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439834992_c39ac848d91414524a2bf7943e4d849b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4404.33, "sourceLowPrice": 4389.8}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54488, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439760945_a0606e9630178667f056606da8cff8e5.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781439834992_c39ac848d91414524a2bf7943e4d849b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4404.33, "sourceLowPrice": 4389.8, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
@@ -64240,7 +64240,7 @@
         <v>37</v>
       </c>
       <c r="BL122" t="n">
-        <v>1782575760033</v>
+        <v>1782579163453</v>
       </c>
       <c r="BM122" t="n">
         <v>4400.195</v>
@@ -64709,7 +64709,7 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54491, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441037891_89af802c88456c34499420a0ce8e0235.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441105819_299be3609ea9f2d7f36d97f51845bda0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4526.2, "sourceLowPrice": 4510.695}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54491, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441037891_89af802c88456c34499420a0ce8e0235.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441105819_299be3609ea9f2d7f36d97f51845bda0.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4526.2, "sourceLowPrice": 4510.695, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
@@ -64764,7 +64764,7 @@
         <v>37</v>
       </c>
       <c r="BL123" t="n">
-        <v>1782575760034</v>
+        <v>1782579163453</v>
       </c>
       <c r="BM123" t="n">
         <v>4525.09</v>
@@ -65233,7 +65233,7 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54492, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/GvACQjVR/", "exitScreenshotUrl": "https://www.tradingview.com/x/8Xr8vSkG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30369.42, "sourceLowPrice": 30261.36}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54492, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/GvACQjVR/", "exitScreenshotUrl": "https://www.tradingview.com/x/8Xr8vSkG/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30369.42, "sourceLowPrice": 30261.36, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
@@ -65288,7 +65288,7 @@
         <v>37</v>
       </c>
       <c r="BL124" t="n">
-        <v>1782575760034</v>
+        <v>1782579163453</v>
       </c>
       <c r="BM124" t="n">
         <v>30247.61</v>
@@ -65482,7 +65482,7 @@
       </c>
       <c r="DO124" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 30247.61, "new": 30241.93, "at": 1780044180000}]</t>
         </is>
       </c>
       <c r="DP124" t="n">
@@ -65757,7 +65757,7 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54493, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KnYLbmBZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/AcWYB0Cv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30399.27, "sourceLowPrice": 30243.44}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54493, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/KnYLbmBZ/", "exitScreenshotUrl": "https://www.tradingview.com/x/AcWYB0Cv/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30399.27, "sourceLowPrice": 30243.44, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
@@ -65812,7 +65812,7 @@
         <v>37</v>
       </c>
       <c r="BL125" t="n">
-        <v>1782575760035</v>
+        <v>1782579163453</v>
       </c>
       <c r="BM125" t="n">
         <v>30220.89</v>
@@ -66281,7 +66281,7 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54494, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441839312_1d39c529782c85841d6aa8e067bc16bd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781442000674_37114c4f1d119bd74bd377f01e745201.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4511.08, "sourceLowPrice": 4483.035}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54494, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781441839312_1d39c529782c85841d6aa8e067bc16bd.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781442000674_37114c4f1d119bd74bd377f01e745201.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4511.08, "sourceLowPrice": 4483.035, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
@@ -66336,7 +66336,7 @@
         <v>37</v>
       </c>
       <c r="BL126" t="n">
-        <v>1782575760036</v>
+        <v>1782579163453</v>
       </c>
       <c r="BM126" t="n">
         <v>4514.08</v>
@@ -66805,7 +66805,7 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54495, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OWR3I5Ua/", "exitScreenshotUrl": "https://www.tradingview.com/x/cnxCjKvH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7607.64, "sourceLowPrice": 7594.78}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54495, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/OWR3I5Ua/", "exitScreenshotUrl": "https://www.tradingview.com/x/cnxCjKvH/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7607.64, "sourceLowPrice": 7594.78, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
@@ -66860,7 +66860,7 @@
         <v>37</v>
       </c>
       <c r="BL127" t="n">
-        <v>1782575760036</v>
+        <v>1782579163454</v>
       </c>
       <c r="BM127" t="n">
         <v>7599.05</v>
@@ -67329,7 +67329,7 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54496, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460606718_ae635194e7ab72a81f01abd021934e20.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460685557_fc8014807b37edbe8dc47be018eec600.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4472.375, "sourceLowPrice": 4455.39}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54496, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460606718_ae635194e7ab72a81f01abd021934e20.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781460685557_fc8014807b37edbe8dc47be018eec600.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4472.375, "sourceLowPrice": 4455.39, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
@@ -67384,7 +67384,7 @@
         <v>37</v>
       </c>
       <c r="BL128" t="n">
-        <v>1782575760037</v>
+        <v>1782579163454</v>
       </c>
       <c r="BM128" t="n">
         <v>4472.06</v>
@@ -67853,7 +67853,7 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54497, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461047997_211ed43f16c631c32fb4184e946e5c6b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461109260_e0bce7b2f349723b4f894f8a96301d0e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.05, "sourceLowPrice": 4440.365}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54497, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461047997_211ed43f16c631c32fb4184e946e5c6b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461109260_e0bce7b2f349723b4f894f8a96301d0e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.05, "sourceLowPrice": 4440.365, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
@@ -67908,7 +67908,7 @@
         <v>37</v>
       </c>
       <c r="BL129" t="n">
-        <v>1782575760038</v>
+        <v>1782579163454</v>
       </c>
       <c r="BM129" t="n">
         <v>4460.495</v>
@@ -68377,7 +68377,7 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54498, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461204254_b8345ba0f02eb80b55dac9630715d877.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461373812_5645374331f7bc2d7c84176cebaef940.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.19, "sourceLowPrice": 4439.09}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54498, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461204254_b8345ba0f02eb80b55dac9630715d877.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461373812_5645374331f7bc2d7c84176cebaef940.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.19, "sourceLowPrice": 4439.09, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
@@ -68432,7 +68432,7 @@
         <v>37</v>
       </c>
       <c r="BL130" t="n">
-        <v>1782575760038</v>
+        <v>1782579163454</v>
       </c>
       <c r="BM130" t="n">
         <v>4460.135</v>
@@ -68901,7 +68901,7 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54499, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461544247_84d71b024e8873288004ad42d22923b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461949380_d1a9f53372902615cb3ee9567ea2d577.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.745, "sourceLowPrice": 4424.019}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54499, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461544247_84d71b024e8873288004ad42d22923b1.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461949380_d1a9f53372902615cb3ee9567ea2d577.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4459.745, "sourceLowPrice": 4424.019, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
@@ -68956,7 +68956,7 @@
         <v>37</v>
       </c>
       <c r="BL131" t="n">
-        <v>1782575760039</v>
+        <v>1782579163454</v>
       </c>
       <c r="BM131" t="n">
         <v>4468.255</v>
@@ -69425,7 +69425,7 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54500, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/k9ad4cJg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S4wBBKKA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7589.67, "sourceLowPrice": 7573.45}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54500, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/k9ad4cJg/", "exitScreenshotUrl": "https://www.tradingview.com/x/S4wBBKKA/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 7589.67, "sourceLowPrice": 7573.45, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
@@ -69480,7 +69480,7 @@
         <v>37</v>
       </c>
       <c r="BL132" t="n">
-        <v>1782575760040</v>
+        <v>1782579163455</v>
       </c>
       <c r="BM132" t="n">
         <v>7593.41</v>
@@ -69949,7 +69949,7 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54501, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461999378_831cbaea472990c4075d3dd84326969b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462052555_260d88a4c58804ca85bc3d6732b3144b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4452.32, "sourceLowPrice": 4424.019}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54501, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781461999378_831cbaea472990c4075d3dd84326969b.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462052555_260d88a4c58804ca85bc3d6732b3144b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4452.32, "sourceLowPrice": 4424.019, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
@@ -70004,7 +70004,7 @@
         <v>37</v>
       </c>
       <c r="BL133" t="n">
-        <v>1782575760040</v>
+        <v>1782579163455</v>
       </c>
       <c r="BM133" t="n">
         <v>4452.68</v>
@@ -70185,11 +70185,11 @@
       </c>
       <c r="DL133" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN133" t="inlineStr">
         <is>
@@ -70263,12 +70263,12 @@
       </c>
       <c r="EF133" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG133" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "auto", "state": "detected", "cost_R": 2.1, "cost_$": 105, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2026-06-03T18:15:00.000Z"}, {"type": "late_entry", "label": "Late Entry", "source": "auto", "state": "detected", "cost_R": 2.1, "cost_$": 105, "evidence": "Entered after the optimal entry window had passed.", "detected_at": "2026-06-03T18:15:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH133" t="inlineStr">
@@ -70473,7 +70473,7 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54502, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462412304_f70b2896e8123a6776dc55ce41c87e1f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462560066_9ce2ef58a5ec31f69c33594b63777e03.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4482.976, "sourceLowPrice": 4461.035}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54502, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462412304_f70b2896e8123a6776dc55ce41c87e1f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462560066_9ce2ef58a5ec31f69c33594b63777e03.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4482.976, "sourceLowPrice": 4461.035, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
@@ -70528,7 +70528,7 @@
         <v>37</v>
       </c>
       <c r="BL134" t="n">
-        <v>1782575760041</v>
+        <v>1782579163455</v>
       </c>
       <c r="BM134" t="n">
         <v>4470.595</v>
@@ -70997,7 +70997,7 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54503, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462693805_09f7cd07274089cdd38058211e9a1f1e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462787684_f531a0924f42c85131a928a281c27b3c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4488.354, "sourceLowPrice": 4473.54}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54503, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462693805_09f7cd07274089cdd38058211e9a1f1e.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781462787684_f531a0924f42c85131a928a281c27b3c.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4488.354, "sourceLowPrice": 4473.54, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
@@ -71052,7 +71052,7 @@
         <v>37</v>
       </c>
       <c r="BL135" t="n">
-        <v>1782575760042</v>
+        <v>1782579163455</v>
       </c>
       <c r="BM135" t="n">
         <v>4479.87</v>
@@ -71521,7 +71521,7 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54509, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463536745_df3c43117506f308a7366417a5cada9c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463632349_eed7dd4e351b3048fa194c6331403a3d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4469.465, "sourceLowPrice": 4458.895}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54509, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463536745_df3c43117506f308a7366417a5cada9c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463632349_eed7dd4e351b3048fa194c6331403a3d.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4469.465, "sourceLowPrice": 4458.895, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
@@ -71576,7 +71576,7 @@
         <v>37</v>
       </c>
       <c r="BL136" t="n">
-        <v>1782575760042</v>
+        <v>1782579163455</v>
       </c>
       <c r="BM136" t="n">
         <v>4469.355</v>
@@ -71757,11 +71757,11 @@
       </c>
       <c r="DL136" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN136" t="inlineStr">
         <is>
@@ -71835,12 +71835,12 @@
       </c>
       <c r="EF136" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG136" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "overtrade", "label": "Overtrading", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 50, "evidence": "Took an extra trade outside the planned session window.", "detected_at": "2026-06-05T05:15:00.000Z"}, {"type": "fomo", "label": "FOMO", "source": "auto", "state": "detected", "cost_R": 1.0, "cost_$": 50, "evidence": "Entered after the move was already extended without a fresh setup.", "detected_at": "2026-06-05T05:15:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH136" t="inlineStr">
@@ -72045,7 +72045,7 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54510, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463742050_14e6e5e9265b43ec082f402286e39772.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463858899_dc421abe368df463fc04b493778f9d4e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.96, "sourceLowPrice": 4459.305}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54510, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463742050_14e6e5e9265b43ec082f402286e39772.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781463858899_dc421abe368df463fc04b493778f9d4e.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4468.96, "sourceLowPrice": 4459.305, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
@@ -72100,7 +72100,7 @@
         <v>37</v>
       </c>
       <c r="BL137" t="n">
-        <v>1782575760043</v>
+        <v>1782579163456</v>
       </c>
       <c r="BM137" t="n">
         <v>4470.465</v>
@@ -72569,7 +72569,7 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54511, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781464006050_b9ae9fb4af1afcee05d47506273aa74f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781465195928_dab8a5991bec66ac4117372bbffa7a10.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4475.885, "sourceLowPrice": 4458.28}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54511, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781464006050_b9ae9fb4af1afcee05d47506273aa74f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781465195928_dab8a5991bec66ac4117372bbffa7a10.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4475.885, "sourceLowPrice": 4458.28, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
@@ -72624,7 +72624,7 @@
         <v>37</v>
       </c>
       <c r="BL138" t="n">
-        <v>1782575760043</v>
+        <v>1782579163456</v>
       </c>
       <c r="BM138" t="n">
         <v>4469.315</v>
@@ -73093,7 +73093,7 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54512, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qnI0VDAP/", "exitScreenshotUrl": "https://www.tradingview.com/x/WLDhKg3O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30061.68, "sourceLowPrice": 29706.99}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54512, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/qnI0VDAP/", "exitScreenshotUrl": "https://www.tradingview.com/x/WLDhKg3O/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "missed-trade", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30061.68, "sourceLowPrice": 29706.99, "rule_outcome": "missed", "reason": "Missed trade", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
@@ -73148,7 +73148,7 @@
         <v>37</v>
       </c>
       <c r="BL139" t="n">
-        <v>1782575760044</v>
+        <v>1782579163456</v>
       </c>
       <c r="BM139" t="n">
         <v>30098.03</v>
@@ -73329,11 +73329,11 @@
       </c>
       <c r="DL139" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "missed-trade"}</t>
         </is>
       </c>
       <c r="DM139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN139" t="inlineStr">
         <is>
@@ -73395,7 +73395,7 @@
         </is>
       </c>
       <c r="EC139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED139" t="n">
         <v>2026</v>
@@ -73407,7 +73407,7 @@
       </c>
       <c r="EF139" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>missed-trade</t>
         </is>
       </c>
       <c r="EG139" t="inlineStr">
@@ -73617,7 +73617,7 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54513, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468059676_dc1d99e33491dee5977740e2247c93eb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468158740_09157e1f0c23533d5d77db299724ece6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4311.956, "sourceLowPrice": 4273.165}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54513, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468059676_dc1d99e33491dee5977740e2247c93eb.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781468158740_09157e1f0c23533d5d77db299724ece6.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4311.956, "sourceLowPrice": 4273.165, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
@@ -73672,7 +73672,7 @@
         <v>37</v>
       </c>
       <c r="BL140" t="n">
-        <v>1782575760044</v>
+        <v>1782579163456</v>
       </c>
       <c r="BM140" t="n">
         <v>4294.92</v>
@@ -74141,7 +74141,7 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54514, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469193286_5651542d75ebb45a455417ddd3003a1c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469307424_656b525bab889df9df912874b80def96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4319.498, "sourceLowPrice": 4296.92}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54514, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469193286_5651542d75ebb45a455417ddd3003a1c.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781469307424_656b525bab889df9df912874b80def96.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4319.498, "sourceLowPrice": 4296.92, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
@@ -74196,7 +74196,7 @@
         <v>37</v>
       </c>
       <c r="BL141" t="n">
-        <v>1782575760044</v>
+        <v>1782579163456</v>
       </c>
       <c r="BM141" t="n">
         <v>4306.941</v>
@@ -74377,11 +74377,11 @@
       </c>
       <c r="DL141" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN141" t="inlineStr">
         <is>
@@ -74455,12 +74455,12 @@
       </c>
       <c r="EF141" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"type": "revenge", "label": "Revenge Trading", "source": "manual", "state": "confirmed", "cost_R": 1.0, "cost_$": 50, "evidence": "Increased aggression after a prior loss in the session.", "detected_at": "2026-06-08T07:11:00.000Z"}]</t>
         </is>
       </c>
       <c r="EH141" t="inlineStr">
@@ -74665,7 +74665,7 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54516, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781472975283_121987fb8605c81036be6bbb977b3e6f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473145242_1cdabbf45d8dc46c735f8cd01c78fa28.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4324.19}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54516, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781472975283_121987fb8605c81036be6bbb977b3e6f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473145242_1cdabbf45d8dc46c735f8cd01c78fa28.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4324.19, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
@@ -74720,7 +74720,7 @@
         <v>37</v>
       </c>
       <c r="BL142" t="n">
-        <v>1782575760045</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM142" t="n">
         <v>4338.02</v>
@@ -74914,7 +74914,7 @@
       </c>
       <c r="DO142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 4338.02, "new": 4340.05, "at": 1780980960000}]</t>
         </is>
       </c>
       <c r="DP142" t="n">
@@ -75189,7 +75189,7 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54517, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473295670_21d74969f3059f574d9eaf694d0e904f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473366648_57617edc0ef6a366982cf12aee3c9476.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4337.475}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54517, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473295670_21d74969f3059f574d9eaf694d0e904f.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781473366648_57617edc0ef6a366982cf12aee3c9476.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4344.09, "sourceLowPrice": 4337.475, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
@@ -75244,7 +75244,7 @@
         <v>37</v>
       </c>
       <c r="BL143" t="n">
-        <v>1782575760045</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM143" t="n">
         <v>4341.965</v>
@@ -75255,7 +75255,7 @@
         </is>
       </c>
       <c r="BO143" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="BP143" t="n">
         <v>1</v>
@@ -75713,7 +75713,7 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54520, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533495202_896f7d04ccac2c18b6902075aaeeba21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533678012_ec07648d6ac856da3ef339f487803e44.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4209.88, "sourceLowPrice": 4144.268}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54520, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533495202_896f7d04ccac2c18b6902075aaeeba21.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533678012_ec07648d6ac856da3ef339f487803e44.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4209.88, "sourceLowPrice": 4144.268, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
@@ -75768,7 +75768,7 @@
         <v>37</v>
       </c>
       <c r="BL144" t="n">
-        <v>1782575760046</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM144" t="n">
         <v>4223.005</v>
@@ -76237,7 +76237,7 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54521, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533714542_589108ab73f44f8e09e5815fa031e759.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533806485_ffc6f911a10f0ef0bbb65a53de36e311.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4195.31, "sourceLowPrice": 4157.248}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54521, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533714542_589108ab73f44f8e09e5815fa031e759.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781533806485_ffc6f911a10f0ef0bbb65a53de36e311.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4195.31, "sourceLowPrice": 4157.248, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
@@ -76292,7 +76292,7 @@
         <v>37</v>
       </c>
       <c r="BL145" t="n">
-        <v>1782575760047</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM145" t="n">
         <v>4197.77</v>
@@ -76761,7 +76761,7 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54524, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781539972331_048e65ca18a8b4f52e31d6068683e140.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540125579_109f267fc4807e8215a5dd009208713f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4096.07, "sourceLowPrice": 4062.767}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54524, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781539972331_048e65ca18a8b4f52e31d6068683e140.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540125579_109f267fc4807e8215a5dd009208713f.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "out-of-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4096.07, "sourceLowPrice": 4062.767, "rule_outcome": "violated", "reason": "Out of plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
@@ -76816,7 +76816,7 @@
         <v>37</v>
       </c>
       <c r="BL146" t="n">
-        <v>1782575760047</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM146" t="n">
         <v>4097.54</v>
@@ -76997,11 +76997,11 @@
       </c>
       <c r="DL146" t="inlineStr">
         <is>
-          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "according-to-plan"}</t>
+          <t>{"mentorSource": "laith 3.xlsx", "planAdherence": "out-of-plan"}</t>
         </is>
       </c>
       <c r="DM146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN146" t="inlineStr">
         <is>
@@ -77075,7 +77075,7 @@
       </c>
       <c r="EF146" t="inlineStr">
         <is>
-          <t>according-to-plan</t>
+          <t>out-of-plan</t>
         </is>
       </c>
       <c r="EG146" t="inlineStr">
@@ -77285,7 +77285,7 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54525, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540198593_182059ebb741237b006a35e9d228d3aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540209654_2bf1f13802938b902ca280b4a63c624b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4086.68, "sourceLowPrice": 4067.638}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54525, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540198593_182059ebb741237b006a35e9d228d3aa.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540209654_2bf1f13802938b902ca280b4a63c624b.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4086.68, "sourceLowPrice": 4067.638, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
@@ -77340,7 +77340,7 @@
         <v>37</v>
       </c>
       <c r="BL147" t="n">
-        <v>1782575760048</v>
+        <v>1782579163457</v>
       </c>
       <c r="BM147" t="n">
         <v>4088.54</v>
@@ -77809,7 +77809,7 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54526, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540400171_440149fe2263f6ee7d3aba448a8e8ca6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540570241_112727011df2180cc462d7cde1804b89.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4092.92, "sourceLowPrice": 4067.285}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54526, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540400171_440149fe2263f6ee7d3aba448a8e8ca6.png", "exitScreenshotUrl": "https://fxr-snapshots-asia.s3.amazonaws.com/1781540570241_112727011df2180cc462d7cde1804b89.png", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 4092.92, "sourceLowPrice": 4067.285, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
@@ -77864,7 +77864,7 @@
         <v>37</v>
       </c>
       <c r="BL148" t="n">
-        <v>1782575760049</v>
+        <v>1782579163458</v>
       </c>
       <c r="BM148" t="n">
         <v>4086.325</v>
@@ -78058,7 +78058,7 @@
       </c>
       <c r="DO148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"field": "SL", "trigger": "MANUAL", "old": 4086.325, "new": 4087.893, "at": 1781168520000}]</t>
         </is>
       </c>
       <c r="DP148" t="n">
@@ -78333,7 +78333,7 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54527, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9SgUNL9j/", "exitScreenshotUrl": "https://www.tradingview.com/x/ypgXv0qj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30301.65, "sourceLowPrice": 30225.28}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54527, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/9SgUNL9j/", "exitScreenshotUrl": "https://www.tradingview.com/x/ypgXv0qj/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "No"}], "planAdherence": "according-to-plan", "excursionSanitized": false, "excursionSanitizeReason": null, "sourceHighPrice": 30301.65, "sourceLowPrice": 30225.28, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
@@ -78388,7 +78388,7 @@
         <v>37</v>
       </c>
       <c r="BL149" t="n">
-        <v>1782575760049</v>
+        <v>1782579163458</v>
       </c>
       <c r="BM149" t="n">
         <v>30255.28</v>
@@ -78857,7 +78857,7 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>{"mentorImport": true, "mentorTradeId": 54528, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gTtR53lU/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkjiCYeO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": true, "excursionSanitizeReason": "missing_high_low", "sourceHighPrice": 4369.665, "sourceLowPrice": null}</t>
+          <t>{"mentorImport": true, "mentorTradeId": 54528, "mentorFile": "laith 3.xlsx", "entryScreenshotUrl": "https://www.tradingview.com/x/gTtR53lU/", "exitScreenshotUrl": "https://www.tradingview.com/x/AkjiCYeO/", "notes": null, "postStrategyVariables": [{"id": "outcome_review", "name": "Outcome review", "vtype": "yesno", "value": "Yes"}], "planAdherence": "according-to-plan", "excursionSanitized": true, "excursionSanitizeReason": "missing_high_low", "sourceHighPrice": 4369.665, "sourceLowPrice": null, "rule_outcome": "followed", "reason": "According to plan", "syntheticDiscipline": true}</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
@@ -78912,7 +78912,7 @@
         <v>37</v>
       </c>
       <c r="BL150" t="n">
-        <v>1782575760050</v>
+        <v>1782579163458</v>
       </c>
       <c r="BM150" t="n">
         <v>4370.085</v>
